--- a/Översikt LINKÖPING.xlsx
+++ b/Översikt LINKÖPING.xlsx
@@ -601,7 +601,7 @@
         <v>45756</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -741,7 +741,7 @@
         <v>45644</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>44679</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>45293</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>46090</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>44855</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
         <v>45278</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1505,7 +1505,7 @@
         <v>44368</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1621,7 +1621,7 @@
         <v>46275</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1749,7 +1749,7 @@
         <v>46090</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1862,7 +1862,7 @@
         <v>45720</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1974,7 +1974,7 @@
         <v>45720</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
         <v>46055</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2206,7 +2206,7 @@
         <v>46206</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2325,7 +2325,7 @@
         <v>45860</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2436,7 +2436,7 @@
         <v>45804</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2551,7 +2551,7 @@
         <v>45280</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2667,7 +2667,7 @@
         <v>45756</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2781,7 +2781,7 @@
         <v>46090</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2891,7 +2891,7 @@
         <v>45972</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3009,7 +3009,7 @@
         <v>46275</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3127,7 +3127,7 @@
         <v>45068</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3241,7 +3241,7 @@
         <v>46146</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3350,7 +3350,7 @@
         <v>44949</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3459,7 +3459,7 @@
         <v>44588</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3572,7 +3572,7 @@
         <v>44679</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3686,7 +3686,7 @@
         <v>43997</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3795,7 +3795,7 @@
         <v>44679</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3912,7 +3912,7 @@
         <v>44745</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4020,7 +4020,7 @@
         <v>45714</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4133,7 +4133,7 @@
         <v>45932</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4246,7 +4246,7 @@
         <v>45943</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4354,7 +4354,7 @@
         <v>44479</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4467,7 +4467,7 @@
         <v>45555</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4580,7 +4580,7 @@
         <v>46050</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4688,7 +4688,7 @@
         <v>46079</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4796,7 +4796,7 @@
         <v>46107</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4913,7 +4913,7 @@
         <v>45089</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5021,7 +5021,7 @@
         <v>44834</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5129,7 +5129,7 @@
         <v>44679</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5241,7 +5241,7 @@
         <v>44679</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5353,7 +5353,7 @@
         <v>44479</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5465,7 +5465,7 @@
         <v>44855</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5576,7 +5576,7 @@
         <v>44930</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5692,7 +5692,7 @@
         <v>45153</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5804,7 +5804,7 @@
         <v>44830</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5911,7 +5911,7 @@
         <v>44916</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6023,7 +6023,7 @@
         <v>46146</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6134,7 +6134,7 @@
         <v>45941</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         <v>45236</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6356,7 +6356,7 @@
         <v>45294</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6463,7 +6463,7 @@
         <v>45989</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6570,7 +6570,7 @@
         <v>46087</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6681,7 +6681,7 @@
         <v>45163</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6788,7 +6788,7 @@
         <v>45217</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6900,7 +6900,7 @@
         <v>45774</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7011,7 +7011,7 @@
         <v>46206</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7118,7 +7118,7 @@
         <v>45621</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7225,7 +7225,7 @@
         <v>45664</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7332,7 +7332,7 @@
         <v>44848</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7438,7 +7438,7 @@
         <v>44498</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7548,7 +7548,7 @@
         <v>45191</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7659,7 +7659,7 @@
         <v>45216</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7765,7 +7765,7 @@
         <v>44909</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7875,7 +7875,7 @@
         <v>45071</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7986,7 +7986,7 @@
         <v>45712</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8097,7 +8097,7 @@
         <v>45572</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8203,7 +8203,7 @@
         <v>44597</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8309,7 +8309,7 @@
         <v>44936</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8415,7 +8415,7 @@
         <v>45745</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8525,7 +8525,7 @@
         <v>45932</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8636,7 +8636,7 @@
         <v>44487</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8747,7 +8747,7 @@
         <v>44487</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8858,7 +8858,7 @@
         <v>45461</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8964,7 +8964,7 @@
         <v>45140</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9074,7 +9074,7 @@
         <v>46107</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9185,7 +9185,7 @@
         <v>45595</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9291,7 +9291,7 @@
         <v>45554</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9406,7 +9406,7 @@
         <v>46153</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9512,7 +9512,7 @@
         <v>45547</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9622,7 +9622,7 @@
         <v>45774</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9728,7 +9728,7 @@
         <v>46043</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9843,7 +9843,7 @@
         <v>46178</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9949,7 +9949,7 @@
         <v>45244</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10060,7 +10060,7 @@
         <v>44930</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10171,7 +10171,7 @@
         <v>45639</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10277,7 +10277,7 @@
         <v>45176</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10383,7 +10383,7 @@
         <v>45148</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10489,7 +10489,7 @@
         <v>45621</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10595,7 +10595,7 @@
         <v>45774</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10705,7 +10705,7 @@
         <v>45804</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10811,7 +10811,7 @@
         <v>44159</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10922,7 +10922,7 @@
         <v>44537</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11032,7 +11032,7 @@
         <v>44938</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11137,7 +11137,7 @@
         <v>45665</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11247,7 +11247,7 @@
         <v>44768</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11352,7 +11352,7 @@
         <v>45141</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11457,7 +11457,7 @@
         <v>45463</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11562,7 +11562,7 @@
         <v>45541</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11667,7 +11667,7 @@
         <v>45222</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11781,7 +11781,7 @@
         <v>45243</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11891,7 +11891,7 @@
         <v>45604</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12001,7 +12001,7 @@
         <v>44929</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12106,7 +12106,7 @@
         <v>45554</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12216,7 +12216,7 @@
         <v>45965</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12326,7 +12326,7 @@
         <v>45246</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12436,7 +12436,7 @@
         <v>45915</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12546,7 +12546,7 @@
         <v>45579</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12651,7 +12651,7 @@
         <v>45244</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12761,7 +12761,7 @@
         <v>44889</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12866,7 +12866,7 @@
         <v>45941</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12971,7 +12971,7 @@
         <v>45604</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13081,7 +13081,7 @@
         <v>45968</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13186,7 +13186,7 @@
         <v>45988</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13296,7 +13296,7 @@
         <v>45071</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13406,7 +13406,7 @@
         <v>46175</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13511,7 +13511,7 @@
         <v>45308</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13621,7 +13621,7 @@
         <v>45442</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13730,7 +13730,7 @@
         <v>46178</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13835,7 +13835,7 @@
         <v>44945</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13940,7 +13940,7 @@
         <v>46079</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14045,7 +14045,7 @@
         <v>45412</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14150,7 +14150,7 @@
         <v>45244</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14260,7 +14260,7 @@
         <v>44945</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14365,7 +14365,7 @@
         <v>44881</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14470,7 +14470,7 @@
         <v>45460</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14575,7 +14575,7 @@
         <v>45994</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14680,7 +14680,7 @@
         <v>44950</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14785,7 +14785,7 @@
         <v>45294</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14895,7 +14895,7 @@
         <v>45266</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -15000,7 +15000,7 @@
         <v>45111</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -15105,7 +15105,7 @@
         <v>44949</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15210,7 +15210,7 @@
         <v>46259</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15320,7 +15320,7 @@
         <v>45491</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15425,7 +15425,7 @@
         <v>46264</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15530,7 +15530,7 @@
         <v>44496</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -15640,7 +15640,7 @@
         <v>45176</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -15745,7 +15745,7 @@
         <v>45369</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -15850,7 +15850,7 @@
         <v>46206</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -15955,7 +15955,7 @@
         <v>45812</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -16060,7 +16060,7 @@
         <v>45816</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -16165,7 +16165,7 @@
         <v>45153</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -16275,7 +16275,7 @@
         <v>44478</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -16353,7 +16353,7 @@
         <v>44523</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -16426,7 +16426,7 @@
         <v>44608</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -16499,7 +16499,7 @@
         <v>44510</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -16572,7 +16572,7 @@
         <v>44488</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -16645,7 +16645,7 @@
         <v>44764</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -16718,7 +16718,7 @@
         <v>44855</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -16796,7 +16796,7 @@
         <v>44573</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -16869,7 +16869,7 @@
         <v>44846</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -16942,7 +16942,7 @@
         <v>44496</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -17015,7 +17015,7 @@
         <v>44853</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -17088,7 +17088,7 @@
         <v>44782</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -17161,7 +17161,7 @@
         <v>44466</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -17234,7 +17234,7 @@
         <v>44679</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -17312,7 +17312,7 @@
         <v>44777</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -17385,7 +17385,7 @@
         <v>44753</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -17463,7 +17463,7 @@
         <v>44510</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -17536,7 +17536,7 @@
         <v>44487</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -17614,7 +17614,7 @@
         <v>44467</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -17687,7 +17687,7 @@
         <v>44487</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -17765,7 +17765,7 @@
         <v>44469</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -17838,7 +17838,7 @@
         <v>44823</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -17911,7 +17911,7 @@
         <v>44467</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -17984,7 +17984,7 @@
         <v>44515</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -18062,7 +18062,7 @@
         <v>44767</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -18135,7 +18135,7 @@
         <v>44719</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -18213,7 +18213,7 @@
         <v>44487</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -18291,7 +18291,7 @@
         <v>44776</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -18364,7 +18364,7 @@
         <v>44692</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -18437,7 +18437,7 @@
         <v>44882</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -18515,7 +18515,7 @@
         <v>44803</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -18588,7 +18588,7 @@
         <v>44588</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -18661,7 +18661,7 @@
         <v>44743</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -18734,7 +18734,7 @@
         <v>44574</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -18807,7 +18807,7 @@
         <v>44571</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -18880,7 +18880,7 @@
         <v>44841</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -18953,7 +18953,7 @@
         <v>44537</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -19026,7 +19026,7 @@
         <v>44809</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -19099,7 +19099,7 @@
         <v>44884</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -19172,7 +19172,7 @@
         <v>44884</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -19245,7 +19245,7 @@
         <v>44628</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -19318,7 +19318,7 @@
         <v>44525</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -19391,7 +19391,7 @@
         <v>44525</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -19464,7 +19464,7 @@
         <v>44627</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -19537,7 +19537,7 @@
         <v>44785</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -19610,7 +19610,7 @@
         <v>44643</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -19683,7 +19683,7 @@
         <v>44720</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -19756,7 +19756,7 @@
         <v>44595</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -19834,7 +19834,7 @@
         <v>44481</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -19907,7 +19907,7 @@
         <v>44743</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -19980,7 +19980,7 @@
         <v>44497</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -20053,7 +20053,7 @@
         <v>44848</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -20126,7 +20126,7 @@
         <v>44776</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -20199,7 +20199,7 @@
         <v>44826</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -20272,7 +20272,7 @@
         <v>44791</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -20345,7 +20345,7 @@
         <v>44498</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -20418,7 +20418,7 @@
         <v>44638</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -20491,7 +20491,7 @@
         <v>44812</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -20564,7 +20564,7 @@
         <v>44796</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -20642,7 +20642,7 @@
         <v>44794</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -20715,7 +20715,7 @@
         <v>45274</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -20788,7 +20788,7 @@
         <v>45236</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -20866,7 +20866,7 @@
         <v>45477</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -20944,7 +20944,7 @@
         <v>44945</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -21017,7 +21017,7 @@
         <v>45457</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -21090,7 +21090,7 @@
         <v>45728</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -21163,7 +21163,7 @@
         <v>45089</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -21241,7 +21241,7 @@
         <v>45140</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -21314,7 +21314,7 @@
         <v>44767</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -21387,7 +21387,7 @@
         <v>44767</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -21460,7 +21460,7 @@
         <v>44897</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -21538,7 +21538,7 @@
         <v>44939</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -21611,7 +21611,7 @@
         <v>45217</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -21684,7 +21684,7 @@
         <v>45217</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -21757,7 +21757,7 @@
         <v>45182</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -21830,7 +21830,7 @@
         <v>45238</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -21903,7 +21903,7 @@
         <v>45225</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -21976,7 +21976,7 @@
         <v>45225</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -22049,7 +22049,7 @@
         <v>45142</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -22122,7 +22122,7 @@
         <v>45623</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -22195,7 +22195,7 @@
         <v>45302</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -22268,7 +22268,7 @@
         <v>45225</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -22346,7 +22346,7 @@
         <v>45435</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -22419,7 +22419,7 @@
         <v>45294</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -22492,7 +22492,7 @@
         <v>45275</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -22565,7 +22565,7 @@
         <v>45133</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -22638,7 +22638,7 @@
         <v>44460</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -22711,7 +22711,7 @@
         <v>44498</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -22784,7 +22784,7 @@
         <v>44498</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -22857,7 +22857,7 @@
         <v>44903</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -22930,7 +22930,7 @@
         <v>45545</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -23003,7 +23003,7 @@
         <v>45030</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -23076,7 +23076,7 @@
         <v>44909</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -23149,7 +23149,7 @@
         <v>44909</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -23222,7 +23222,7 @@
         <v>45161</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -23295,7 +23295,7 @@
         <v>44930</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -23373,7 +23373,7 @@
         <v>45309</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -23446,7 +23446,7 @@
         <v>45111</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -23519,7 +23519,7 @@
         <v>45160</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -23592,7 +23592,7 @@
         <v>45755</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -23665,7 +23665,7 @@
         <v>45624</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -23738,7 +23738,7 @@
         <v>45294</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -23811,7 +23811,7 @@
         <v>45111</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -23884,7 +23884,7 @@
         <v>45491</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -23957,7 +23957,7 @@
         <v>44894</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -24030,7 +24030,7 @@
         <v>45678</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -24103,7 +24103,7 @@
         <v>45750</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -24176,7 +24176,7 @@
         <v>44683</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -24249,7 +24249,7 @@
         <v>45274</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -24322,7 +24322,7 @@
         <v>45146</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -24400,7 +24400,7 @@
         <v>45275</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -24473,7 +24473,7 @@
         <v>44487</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -24551,7 +24551,7 @@
         <v>44888</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -24624,7 +24624,7 @@
         <v>45456</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -24697,7 +24697,7 @@
         <v>45623</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -24770,7 +24770,7 @@
         <v>45623</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -24843,7 +24843,7 @@
         <v>44949</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -24916,7 +24916,7 @@
         <v>45013</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -24989,7 +24989,7 @@
         <v>44558</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -25062,7 +25062,7 @@
         <v>44743</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -25135,7 +25135,7 @@
         <v>45125</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -25208,7 +25208,7 @@
         <v>45610</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -25281,7 +25281,7 @@
         <v>44865</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -25354,7 +25354,7 @@
         <v>45230</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -25427,7 +25427,7 @@
         <v>45208</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -25500,7 +25500,7 @@
         <v>45147</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -25573,7 +25573,7 @@
         <v>44600</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -25646,7 +25646,7 @@
         <v>45202</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -25719,7 +25719,7 @@
         <v>45281</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -25797,7 +25797,7 @@
         <v>44783</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -25870,7 +25870,7 @@
         <v>45729</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -25943,7 +25943,7 @@
         <v>45359</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -26016,7 +26016,7 @@
         <v>45021</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -26089,7 +26089,7 @@
         <v>44928</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -26162,7 +26162,7 @@
         <v>44933</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -26235,7 +26235,7 @@
         <v>44768</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -26308,7 +26308,7 @@
         <v>45712</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -26381,7 +26381,7 @@
         <v>44909</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -26454,7 +26454,7 @@
         <v>46099</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -26527,7 +26527,7 @@
         <v>44862</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -26600,7 +26600,7 @@
         <v>44889</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -26678,7 +26678,7 @@
         <v>45203</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -26751,7 +26751,7 @@
         <v>44665</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -26829,7 +26829,7 @@
         <v>44860</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -26902,7 +26902,7 @@
         <v>44945</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -26975,7 +26975,7 @@
         <v>44498</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -27048,7 +27048,7 @@
         <v>44509</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -27126,7 +27126,7 @@
         <v>44795</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -27199,7 +27199,7 @@
         <v>44475</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -27272,7 +27272,7 @@
         <v>44933</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -27345,7 +27345,7 @@
         <v>44942</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -27418,7 +27418,7 @@
         <v>45293</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -27491,7 +27491,7 @@
         <v>45195</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -27564,7 +27564,7 @@
         <v>45111</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -27637,7 +27637,7 @@
         <v>45555</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -27715,7 +27715,7 @@
         <v>45082</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -27788,7 +27788,7 @@
         <v>45082</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -27861,7 +27861,7 @@
         <v>45590</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -27934,7 +27934,7 @@
         <v>45244</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -28012,7 +28012,7 @@
         <v>45905</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -28085,7 +28085,7 @@
         <v>44936</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -28158,7 +28158,7 @@
         <v>44931</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -28231,7 +28231,7 @@
         <v>45678</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -28304,7 +28304,7 @@
         <v>44623</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -28377,7 +28377,7 @@
         <v>45901</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -28450,7 +28450,7 @@
         <v>45111</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -28528,7 +28528,7 @@
         <v>46086</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -28601,7 +28601,7 @@
         <v>46057</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -28674,7 +28674,7 @@
         <v>44923</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -28752,7 +28752,7 @@
         <v>45489</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -28825,7 +28825,7 @@
         <v>45121</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -28898,7 +28898,7 @@
         <v>45106</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -28971,7 +28971,7 @@
         <v>45106</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -29044,7 +29044,7 @@
         <v>45296</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -29117,7 +29117,7 @@
         <v>45069</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -29190,7 +29190,7 @@
         <v>44501</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -29263,7 +29263,7 @@
         <v>45392</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -29336,7 +29336,7 @@
         <v>45555</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -29414,7 +29414,7 @@
         <v>45915</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -29487,7 +29487,7 @@
         <v>45912</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -29565,7 +29565,7 @@
         <v>45912</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -29643,7 +29643,7 @@
         <v>45912</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -29721,7 +29721,7 @@
         <v>45644</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -29794,7 +29794,7 @@
         <v>44944</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -29867,7 +29867,7 @@
         <v>45919</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -29940,7 +29940,7 @@
         <v>45922</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -30018,7 +30018,7 @@
         <v>45261</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -30091,7 +30091,7 @@
         <v>45237</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -30164,7 +30164,7 @@
         <v>45140</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -30237,7 +30237,7 @@
         <v>44803</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -30310,7 +30310,7 @@
         <v>44498</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -30383,7 +30383,7 @@
         <v>45086</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -30456,7 +30456,7 @@
         <v>45928</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -30529,7 +30529,7 @@
         <v>45930</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -30602,7 +30602,7 @@
         <v>44987</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -30675,7 +30675,7 @@
         <v>44459</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -30748,7 +30748,7 @@
         <v>45932</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -30826,7 +30826,7 @@
         <v>44565</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -30899,7 +30899,7 @@
         <v>46147</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -30977,7 +30977,7 @@
         <v>44690</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -31050,7 +31050,7 @@
         <v>44768</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -31123,7 +31123,7 @@
         <v>46147</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -31201,7 +31201,7 @@
         <v>44888</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -31274,7 +31274,7 @@
         <v>44986</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -31347,7 +31347,7 @@
         <v>46145</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -31420,7 +31420,7 @@
         <v>45941</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -31493,7 +31493,7 @@
         <v>45945</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -31566,7 +31566,7 @@
         <v>44967</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -31644,7 +31644,7 @@
         <v>45177</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -31717,7 +31717,7 @@
         <v>45116</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -31790,7 +31790,7 @@
         <v>45146</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -31868,7 +31868,7 @@
         <v>45153</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -31946,7 +31946,7 @@
         <v>45952</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -32019,7 +32019,7 @@
         <v>45105</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -32097,7 +32097,7 @@
         <v>45230</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -32170,7 +32170,7 @@
         <v>45957</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -32243,7 +32243,7 @@
         <v>45306</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -32316,7 +32316,7 @@
         <v>44862</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -32389,7 +32389,7 @@
         <v>45470</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -32467,7 +32467,7 @@
         <v>45957</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -32540,7 +32540,7 @@
         <v>45957</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -32613,7 +32613,7 @@
         <v>46153</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -32686,7 +32686,7 @@
         <v>44911</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -32759,7 +32759,7 @@
         <v>45187</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -32837,7 +32837,7 @@
         <v>44930</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -32915,7 +32915,7 @@
         <v>44994</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -32988,7 +32988,7 @@
         <v>45044</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -33061,7 +33061,7 @@
         <v>45300</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -33139,7 +33139,7 @@
         <v>46154</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -33217,7 +33217,7 @@
         <v>44475</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -33290,7 +33290,7 @@
         <v>45392</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -33368,7 +33368,7 @@
         <v>45655</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -33441,7 +33441,7 @@
         <v>46154</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -33519,7 +33519,7 @@
         <v>45086</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -33592,7 +33592,7 @@
         <v>45968</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -33665,7 +33665,7 @@
         <v>45968</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -33738,7 +33738,7 @@
         <v>44483</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -33811,7 +33811,7 @@
         <v>45968</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -33884,7 +33884,7 @@
         <v>46154</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -33962,7 +33962,7 @@
         <v>45755</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -34035,7 +34035,7 @@
         <v>45755</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -34108,7 +34108,7 @@
         <v>45755</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -34181,7 +34181,7 @@
         <v>45973</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -34254,7 +34254,7 @@
         <v>45973</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -34327,7 +34327,7 @@
         <v>45117</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -34400,7 +34400,7 @@
         <v>46154</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -34478,7 +34478,7 @@
         <v>45977</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -34556,7 +34556,7 @@
         <v>45374</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -34629,7 +34629,7 @@
         <v>44498</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -34702,7 +34702,7 @@
         <v>45337</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -34775,7 +34775,7 @@
         <v>46154</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -34853,7 +34853,7 @@
         <v>45294</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -34931,7 +34931,7 @@
         <v>46154</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -35009,7 +35009,7 @@
         <v>45625</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -35082,7 +35082,7 @@
         <v>44993</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -35155,7 +35155,7 @@
         <v>44508</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -35228,7 +35228,7 @@
         <v>45741</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -35301,7 +35301,7 @@
         <v>45320</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -35374,7 +35374,7 @@
         <v>45266</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -35452,7 +35452,7 @@
         <v>45695</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -35525,7 +35525,7 @@
         <v>45231</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -35598,7 +35598,7 @@
         <v>44949</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -35671,7 +35671,7 @@
         <v>45989</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -35744,7 +35744,7 @@
         <v>44882</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -35817,7 +35817,7 @@
         <v>44882</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -35890,7 +35890,7 @@
         <v>45993</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -35963,7 +35963,7 @@
         <v>45737</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -36036,7 +36036,7 @@
         <v>44930</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -36114,7 +36114,7 @@
         <v>45268</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -36187,7 +36187,7 @@
         <v>45005</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -36260,7 +36260,7 @@
         <v>45729</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -36338,7 +36338,7 @@
         <v>45379</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -36411,7 +36411,7 @@
         <v>45092</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -36484,7 +36484,7 @@
         <v>45774</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -36557,7 +36557,7 @@
         <v>45833</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -36630,7 +36630,7 @@
         <v>45275</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -36703,7 +36703,7 @@
         <v>45996</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -36781,7 +36781,7 @@
         <v>45275</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -36859,7 +36859,7 @@
         <v>45275</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -36937,7 +36937,7 @@
         <v>46000</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -37015,7 +37015,7 @@
         <v>45411</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -37088,7 +37088,7 @@
         <v>44658</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -37161,7 +37161,7 @@
         <v>45217</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -37234,7 +37234,7 @@
         <v>44873</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -37312,7 +37312,7 @@
         <v>45096</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -37390,7 +37390,7 @@
         <v>46010</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -37463,7 +37463,7 @@
         <v>45741</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -37536,7 +37536,7 @@
         <v>44775</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -37609,7 +37609,7 @@
         <v>45655</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -37682,7 +37682,7 @@
         <v>45037</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -37760,7 +37760,7 @@
         <v>45271</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -37833,7 +37833,7 @@
         <v>45177</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -37906,7 +37906,7 @@
         <v>45161</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -37979,7 +37979,7 @@
         <v>46030</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -38052,7 +38052,7 @@
         <v>46030</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -38125,7 +38125,7 @@
         <v>44958</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -38198,7 +38198,7 @@
         <v>44936</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -38271,7 +38271,7 @@
         <v>46030</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -38344,7 +38344,7 @@
         <v>46030</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -38422,7 +38422,7 @@
         <v>46030</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -38500,7 +38500,7 @@
         <v>46030</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -38573,7 +38573,7 @@
         <v>46030</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -38646,7 +38646,7 @@
         <v>46035</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -38719,7 +38719,7 @@
         <v>44638</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -38792,7 +38792,7 @@
         <v>46035</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -38865,7 +38865,7 @@
         <v>45453</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -38938,7 +38938,7 @@
         <v>45293</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -39011,7 +39011,7 @@
         <v>44599</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -39084,7 +39084,7 @@
         <v>46038</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -39157,7 +39157,7 @@
         <v>44776</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -39230,7 +39230,7 @@
         <v>46038</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -39303,7 +39303,7 @@
         <v>44970</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -39381,7 +39381,7 @@
         <v>45120</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -39454,7 +39454,7 @@
         <v>44608</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -39532,7 +39532,7 @@
         <v>45475</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -39605,7 +39605,7 @@
         <v>46055</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -39678,7 +39678,7 @@
         <v>44824</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -39751,7 +39751,7 @@
         <v>46055</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -39824,7 +39824,7 @@
         <v>45604</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -39902,7 +39902,7 @@
         <v>44865</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -39980,7 +39980,7 @@
         <v>45268</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -40053,7 +40053,7 @@
         <v>45106</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -40126,7 +40126,7 @@
         <v>45090</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -40199,7 +40199,7 @@
         <v>44937</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -40272,7 +40272,7 @@
         <v>45111</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -40350,7 +40350,7 @@
         <v>44994</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -40423,7 +40423,7 @@
         <v>44945</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -40496,7 +40496,7 @@
         <v>46181</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -40569,7 +40569,7 @@
         <v>45596</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -40642,7 +40642,7 @@
         <v>45077</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -40715,7 +40715,7 @@
         <v>45579</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -40788,7 +40788,7 @@
         <v>46181</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -40861,7 +40861,7 @@
         <v>44469</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -40934,7 +40934,7 @@
         <v>46077</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -41007,7 +41007,7 @@
         <v>44966</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -41080,7 +41080,7 @@
         <v>46079</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -41153,7 +41153,7 @@
         <v>45147</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -41226,7 +41226,7 @@
         <v>45579</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -41299,7 +41299,7 @@
         <v>46087</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -41372,7 +41372,7 @@
         <v>45155</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -41445,7 +41445,7 @@
         <v>45231</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -41518,7 +41518,7 @@
         <v>45230</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -41591,7 +41591,7 @@
         <v>45231</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -41664,7 +41664,7 @@
         <v>46087</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -41737,7 +41737,7 @@
         <v>44509</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -41815,7 +41815,7 @@
         <v>45341</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -41888,7 +41888,7 @@
         <v>46085</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -41961,7 +41961,7 @@
         <v>45483</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -42034,7 +42034,7 @@
         <v>46098</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -42107,7 +42107,7 @@
         <v>46049</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -42180,7 +42180,7 @@
         <v>46094</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -42253,7 +42253,7 @@
         <v>46099</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -42331,7 +42331,7 @@
         <v>45229</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -42404,7 +42404,7 @@
         <v>44740</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -42477,7 +42477,7 @@
         <v>45082</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -42550,7 +42550,7 @@
         <v>45655</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -42623,7 +42623,7 @@
         <v>44988</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -42701,7 +42701,7 @@
         <v>46107</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -42779,7 +42779,7 @@
         <v>45568</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -42852,7 +42852,7 @@
         <v>45568</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -42925,7 +42925,7 @@
         <v>45485</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -42998,7 +42998,7 @@
         <v>45579</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -43071,7 +43071,7 @@
         <v>45748</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -43144,7 +43144,7 @@
         <v>45492</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -43217,7 +43217,7 @@
         <v>45230</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -43290,7 +43290,7 @@
         <v>46114</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -43368,7 +43368,7 @@
         <v>44475</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -43441,7 +43441,7 @@
         <v>46199</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -43514,7 +43514,7 @@
         <v>44986</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -43587,7 +43587,7 @@
         <v>44953</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -43660,7 +43660,7 @@
         <v>46120</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -43733,7 +43733,7 @@
         <v>45092</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -43806,7 +43806,7 @@
         <v>46245</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -43879,7 +43879,7 @@
         <v>45142</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -43952,7 +43952,7 @@
         <v>45300</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -44030,7 +44030,7 @@
         <v>46203</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -44103,7 +44103,7 @@
         <v>44509</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -44176,7 +44176,7 @@
         <v>45152</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -44249,7 +44249,7 @@
         <v>45209</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -44322,7 +44322,7 @@
         <v>46245</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -44395,7 +44395,7 @@
         <v>46154</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -44473,7 +44473,7 @@
         <v>44858</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -44546,7 +44546,7 @@
         <v>45275</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -44624,7 +44624,7 @@
         <v>45639</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -44697,7 +44697,7 @@
         <v>45774</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -44770,7 +44770,7 @@
         <v>45427</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -44843,7 +44843,7 @@
         <v>44628</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -44916,7 +44916,7 @@
         <v>46134</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -44989,7 +44989,7 @@
         <v>45774</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -45062,7 +45062,7 @@
         <v>44986</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -45135,7 +45135,7 @@
         <v>45967</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -45208,7 +45208,7 @@
         <v>46086</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -45281,7 +45281,7 @@
         <v>46086</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -45354,7 +45354,7 @@
         <v>44944</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -45427,7 +45427,7 @@
         <v>45655</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -45500,7 +45500,7 @@
         <v>45655</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -45573,7 +45573,7 @@
         <v>45938</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -45651,7 +45651,7 @@
         <v>46008</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -45724,7 +45724,7 @@
         <v>46248</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -45802,7 +45802,7 @@
         <v>45597</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -45875,7 +45875,7 @@
         <v>46248</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -45953,7 +45953,7 @@
         <v>46248</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -46031,7 +46031,7 @@
         <v>45219</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -46109,7 +46109,7 @@
         <v>46206</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -46182,7 +46182,7 @@
         <v>44994</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -46255,7 +46255,7 @@
         <v>46205</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -46328,7 +46328,7 @@
         <v>45555</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -46401,7 +46401,7 @@
         <v>46206</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -46474,7 +46474,7 @@
         <v>46206</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -46547,7 +46547,7 @@
         <v>46248</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -46625,7 +46625,7 @@
         <v>46248</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -46703,7 +46703,7 @@
         <v>46206</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -46776,7 +46776,7 @@
         <v>45703</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -46849,7 +46849,7 @@
         <v>46206</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -46922,7 +46922,7 @@
         <v>46248</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -47000,7 +47000,7 @@
         <v>45205</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -47073,7 +47073,7 @@
         <v>46206</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -47146,7 +47146,7 @@
         <v>44641</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -47224,7 +47224,7 @@
         <v>45655</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -47297,7 +47297,7 @@
         <v>46206</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -47370,7 +47370,7 @@
         <v>46206</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -47443,7 +47443,7 @@
         <v>46206</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -47516,7 +47516,7 @@
         <v>44767</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -47589,7 +47589,7 @@
         <v>44909</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -47662,7 +47662,7 @@
         <v>44909</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -47735,7 +47735,7 @@
         <v>45230</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -47808,7 +47808,7 @@
         <v>45265</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -47881,7 +47881,7 @@
         <v>45294</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -47954,7 +47954,7 @@
         <v>45429</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -48027,7 +48027,7 @@
         <v>45299</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -48100,7 +48100,7 @@
         <v>45491</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -48173,7 +48173,7 @@
         <v>45274</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -48246,7 +48246,7 @@
         <v>46254</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -48319,7 +48319,7 @@
         <v>45266</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -48392,7 +48392,7 @@
         <v>45268</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -48465,7 +48465,7 @@
         <v>45300</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -48543,7 +48543,7 @@
         <v>45245</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -48621,7 +48621,7 @@
         <v>46259</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -48699,7 +48699,7 @@
         <v>45342</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -48772,7 +48772,7 @@
         <v>45364</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -48850,7 +48850,7 @@
         <v>45275</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -48923,7 +48923,7 @@
         <v>45275</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -49001,7 +49001,7 @@
         <v>45275</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -49074,7 +49074,7 @@
         <v>45153</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -49152,7 +49152,7 @@
         <v>45397</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -49225,7 +49225,7 @@
         <v>46259</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -49303,7 +49303,7 @@
         <v>46259</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -49381,7 +49381,7 @@
         <v>45404</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -49454,7 +49454,7 @@
         <v>44810</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -49527,7 +49527,7 @@
         <v>45491</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -49600,7 +49600,7 @@
         <v>44812</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -49673,7 +49673,7 @@
         <v>44794</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -49746,7 +49746,7 @@
         <v>44643</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -49819,7 +49819,7 @@
         <v>45299</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -49892,7 +49892,7 @@
         <v>45049</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -49965,7 +49965,7 @@
         <v>45048</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -50038,7 +50038,7 @@
         <v>46265</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -50111,7 +50111,7 @@
         <v>45774</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -50184,7 +50184,7 @@
         <v>46265</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -50257,7 +50257,7 @@
         <v>46147</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -50335,7 +50335,7 @@
         <v>46267</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -50413,7 +50413,7 @@
         <v>46264</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -50486,7 +50486,7 @@
         <v>46266</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -50559,7 +50559,7 @@
         <v>46266</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -50632,7 +50632,7 @@
         <v>44859</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -50710,7 +50710,7 @@
         <v>46267</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -50788,7 +50788,7 @@
         <v>46267</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -50866,7 +50866,7 @@
         <v>46267</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -50944,7 +50944,7 @@
         <v>46267</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -51022,7 +51022,7 @@
         <v>46269</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -51100,7 +51100,7 @@
         <v>46269</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -51178,7 +51178,7 @@
         <v>45275</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -51256,7 +51256,7 @@
         <v>46269</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -51334,7 +51334,7 @@
         <v>46269</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -51412,7 +51412,7 @@
         <v>46269</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -51490,7 +51490,7 @@
         <v>46269</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -51568,7 +51568,7 @@
         <v>45671</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -51641,7 +51641,7 @@
         <v>46269</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -51719,7 +51719,7 @@
         <v>46272</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -51797,7 +51797,7 @@
         <v>46272</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -51875,7 +51875,7 @@
         <v>45779</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -51948,7 +51948,7 @@
         <v>45779</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -52021,7 +52021,7 @@
         <v>46272</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -52099,7 +52099,7 @@
         <v>46275</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -52172,7 +52172,7 @@
         <v>46274</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -52250,7 +52250,7 @@
         <v>46275</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -52323,7 +52323,7 @@
         <v>46275</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -52396,7 +52396,7 @@
         <v>45785</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -52469,7 +52469,7 @@
         <v>46272</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -52547,7 +52547,7 @@
         <v>45359</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -52620,7 +52620,7 @@
         <v>45342</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -52693,7 +52693,7 @@
         <v>45573</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -52766,7 +52766,7 @@
         <v>46272</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -52844,7 +52844,7 @@
         <v>46279</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -52917,7 +52917,7 @@
         <v>46275</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -52990,7 +52990,7 @@
         <v>45664</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -53063,7 +53063,7 @@
         <v>45546</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -53136,7 +53136,7 @@
         <v>45246</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -53209,7 +53209,7 @@
         <v>45483</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -53282,7 +53282,7 @@
         <v>45793</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -53355,7 +53355,7 @@
         <v>45593</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -53428,7 +53428,7 @@
         <v>46239</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -53501,7 +53501,7 @@
         <v>46239</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -53574,7 +53574,7 @@
         <v>46240</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -53652,7 +53652,7 @@
         <v>46272</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -53730,7 +53730,7 @@
         <v>45737</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -53803,7 +53803,7 @@
         <v>45573</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -53876,7 +53876,7 @@
         <v>45804</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -53949,7 +53949,7 @@
         <v>45816</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -54022,7 +54022,7 @@
         <v>45821</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -54095,7 +54095,7 @@
         <v>45614</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -54168,7 +54168,7 @@
         <v>45655</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -54241,7 +54241,7 @@
         <v>45852</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -54314,7 +54314,7 @@
         <v>45860</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -54387,7 +54387,7 @@
         <v>45860</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -54460,7 +54460,7 @@
         <v>45804</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -54533,7 +54533,7 @@
         <v>45541</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -54606,7 +54606,7 @@
         <v>44855</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -54679,7 +54679,7 @@
         <v>45133</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -54752,7 +54752,7 @@
         <v>45541</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -54825,7 +54825,7 @@
         <v>45699</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -54898,7 +54898,7 @@
         <v>46040</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -54971,7 +54971,7 @@
         <v>46108</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -55044,7 +55044,7 @@
         <v>46183</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>

--- a/Översikt LINKÖPING.xlsx
+++ b/Översikt LINKÖPING.xlsx
@@ -601,7 +601,7 @@
         <v>45756</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -741,7 +741,7 @@
         <v>45644</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>44679</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>46090</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>45293</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>44855</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
         <v>45278</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1505,7 +1505,7 @@
         <v>44368</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1621,7 +1621,7 @@
         <v>46275</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1749,7 +1749,7 @@
         <v>46090</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1862,7 +1862,7 @@
         <v>45720</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1974,7 +1974,7 @@
         <v>45720</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
         <v>46055</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2206,7 +2206,7 @@
         <v>45860</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2317,7 +2317,7 @@
         <v>45804</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2432,7 +2432,7 @@
         <v>46206</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2551,7 +2551,7 @@
         <v>45280</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2667,7 +2667,7 @@
         <v>46090</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2777,7 +2777,7 @@
         <v>45756</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2891,7 +2891,7 @@
         <v>46275</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3009,7 +3009,7 @@
         <v>45972</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3127,7 +3127,7 @@
         <v>44679</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3241,7 +3241,7 @@
         <v>44588</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3354,7 +3354,7 @@
         <v>46146</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3463,7 +3463,7 @@
         <v>44949</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3572,7 +3572,7 @@
         <v>45068</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3686,7 +3686,7 @@
         <v>43997</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3795,7 +3795,7 @@
         <v>44679</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3912,7 +3912,7 @@
         <v>46050</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4020,7 +4020,7 @@
         <v>46079</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4128,7 +4128,7 @@
         <v>45943</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4236,7 +4236,7 @@
         <v>44745</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4344,7 +4344,7 @@
         <v>46107</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4461,7 +4461,7 @@
         <v>45932</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4574,7 +4574,7 @@
         <v>45714</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4687,7 +4687,7 @@
         <v>44479</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4800,7 +4800,7 @@
         <v>45555</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4913,7 +4913,7 @@
         <v>45089</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5021,7 +5021,7 @@
         <v>44834</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5129,7 +5129,7 @@
         <v>44679</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5241,7 +5241,7 @@
         <v>44679</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5353,7 +5353,7 @@
         <v>44479</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5465,7 +5465,7 @@
         <v>44855</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5576,7 +5576,7 @@
         <v>44930</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5692,7 +5692,7 @@
         <v>46087</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5803,7 +5803,7 @@
         <v>45941</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5914,7 +5914,7 @@
         <v>45217</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6026,7 +6026,7 @@
         <v>45774</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6137,7 +6137,7 @@
         <v>45989</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6244,7 +6244,7 @@
         <v>44916</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6356,7 +6356,7 @@
         <v>46146</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6467,7 +6467,7 @@
         <v>45153</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6579,7 +6579,7 @@
         <v>45236</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6690,7 +6690,7 @@
         <v>45163</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6797,7 +6797,7 @@
         <v>44830</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6904,7 +6904,7 @@
         <v>46206</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7011,7 +7011,7 @@
         <v>46289</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7131,7 +7131,7 @@
         <v>45621</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7238,7 +7238,7 @@
         <v>45294</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7345,7 +7345,7 @@
         <v>45664</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7452,7 +7452,7 @@
         <v>44848</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7558,7 +7558,7 @@
         <v>44498</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7668,7 +7668,7 @@
         <v>45774</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7774,7 +7774,7 @@
         <v>45595</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7880,7 +7880,7 @@
         <v>44487</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7991,7 +7991,7 @@
         <v>46043</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8106,7 +8106,7 @@
         <v>45572</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8212,7 +8212,7 @@
         <v>45244</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8323,7 +8323,7 @@
         <v>44936</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8429,7 +8429,7 @@
         <v>45639</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8535,7 +8535,7 @@
         <v>45745</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8645,7 +8645,7 @@
         <v>45932</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8756,7 +8756,7 @@
         <v>44597</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8862,7 +8862,7 @@
         <v>46107</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8973,7 +8973,7 @@
         <v>46153</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9079,7 +9079,7 @@
         <v>45547</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9189,7 +9189,7 @@
         <v>45804</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9295,7 +9295,7 @@
         <v>45140</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9405,7 +9405,7 @@
         <v>45191</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9516,7 +9516,7 @@
         <v>45774</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9626,7 +9626,7 @@
         <v>45148</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9732,7 +9732,7 @@
         <v>44487</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9843,7 +9843,7 @@
         <v>45071</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9954,7 +9954,7 @@
         <v>46259</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10065,7 +10065,7 @@
         <v>44909</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10175,7 +10175,7 @@
         <v>45176</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10281,7 +10281,7 @@
         <v>45712</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10392,7 +10392,7 @@
         <v>45554</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10507,7 +10507,7 @@
         <v>46178</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10613,7 +10613,7 @@
         <v>45461</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10719,7 +10719,7 @@
         <v>45621</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10825,7 +10825,7 @@
         <v>44930</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10936,7 +10936,7 @@
         <v>45216</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11042,7 +11042,7 @@
         <v>44159</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11153,7 +11153,7 @@
         <v>44537</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11263,7 +11263,7 @@
         <v>45222</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11377,7 +11377,7 @@
         <v>45412</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11482,7 +11482,7 @@
         <v>45554</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11592,7 +11592,7 @@
         <v>45460</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11697,7 +11697,7 @@
         <v>44929</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11802,7 +11802,7 @@
         <v>45604</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11912,7 +11912,7 @@
         <v>44881</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12017,7 +12017,7 @@
         <v>45915</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12127,7 +12127,7 @@
         <v>46079</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12232,7 +12232,7 @@
         <v>44945</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12337,7 +12337,7 @@
         <v>45941</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12442,7 +12442,7 @@
         <v>45812</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12547,7 +12547,7 @@
         <v>44950</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12652,7 +12652,7 @@
         <v>45968</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12757,7 +12757,7 @@
         <v>44496</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12867,7 +12867,7 @@
         <v>45294</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12977,7 +12977,7 @@
         <v>45141</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13082,7 +13082,7 @@
         <v>44768</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13187,7 +13187,7 @@
         <v>45994</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13292,7 +13292,7 @@
         <v>45246</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13402,7 +13402,7 @@
         <v>45965</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13512,7 +13512,7 @@
         <v>45988</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13622,7 +13622,7 @@
         <v>45816</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13727,7 +13727,7 @@
         <v>45111</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13832,7 +13832,7 @@
         <v>44889</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13937,7 +13937,7 @@
         <v>45491</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14042,7 +14042,7 @@
         <v>45153</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14152,7 +14152,7 @@
         <v>46175</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14257,7 +14257,7 @@
         <v>45579</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14362,7 +14362,7 @@
         <v>45541</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14467,7 +14467,7 @@
         <v>45244</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14577,7 +14577,7 @@
         <v>46259</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14687,7 +14687,7 @@
         <v>45243</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14797,7 +14797,7 @@
         <v>46264</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14902,7 +14902,7 @@
         <v>45266</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -15007,7 +15007,7 @@
         <v>45244</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -15117,7 +15117,7 @@
         <v>46206</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15222,7 +15222,7 @@
         <v>44945</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15327,7 +15327,7 @@
         <v>46289</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15437,7 +15437,7 @@
         <v>45071</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15547,7 +15547,7 @@
         <v>44938</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -15652,7 +15652,7 @@
         <v>45665</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -15762,7 +15762,7 @@
         <v>45308</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -15872,7 +15872,7 @@
         <v>44949</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -15977,7 +15977,7 @@
         <v>45442</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -16086,7 +16086,7 @@
         <v>45463</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -16191,7 +16191,7 @@
         <v>45604</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -16301,7 +16301,7 @@
         <v>45369</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -16406,7 +16406,7 @@
         <v>45176</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -16511,7 +16511,7 @@
         <v>44478</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -16589,7 +16589,7 @@
         <v>44523</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -16662,7 +16662,7 @@
         <v>44608</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -16735,7 +16735,7 @@
         <v>44510</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -16808,7 +16808,7 @@
         <v>44488</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -16881,7 +16881,7 @@
         <v>44764</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -16954,7 +16954,7 @@
         <v>44855</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -17032,7 +17032,7 @@
         <v>44573</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -17105,7 +17105,7 @@
         <v>44846</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -17178,7 +17178,7 @@
         <v>44496</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -17251,7 +17251,7 @@
         <v>44782</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -17324,7 +17324,7 @@
         <v>44853</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -17397,7 +17397,7 @@
         <v>44466</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -17470,7 +17470,7 @@
         <v>44679</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -17548,7 +17548,7 @@
         <v>44777</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -17621,7 +17621,7 @@
         <v>44753</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -17699,7 +17699,7 @@
         <v>44510</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -17772,7 +17772,7 @@
         <v>44487</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -17850,7 +17850,7 @@
         <v>44469</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -17923,7 +17923,7 @@
         <v>44487</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -18001,7 +18001,7 @@
         <v>44467</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -18074,7 +18074,7 @@
         <v>44823</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -18147,7 +18147,7 @@
         <v>44467</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -18220,7 +18220,7 @@
         <v>44515</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -18298,7 +18298,7 @@
         <v>44767</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -18371,7 +18371,7 @@
         <v>44719</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -18449,7 +18449,7 @@
         <v>44487</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -18527,7 +18527,7 @@
         <v>44776</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -18600,7 +18600,7 @@
         <v>44692</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -18673,7 +18673,7 @@
         <v>44803</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -18746,7 +18746,7 @@
         <v>44882</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -18824,7 +18824,7 @@
         <v>44588</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -18897,7 +18897,7 @@
         <v>44743</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -18970,7 +18970,7 @@
         <v>44574</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -19043,7 +19043,7 @@
         <v>44571</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -19116,7 +19116,7 @@
         <v>44841</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -19189,7 +19189,7 @@
         <v>44537</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -19262,7 +19262,7 @@
         <v>44809</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -19335,7 +19335,7 @@
         <v>44884</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -19408,7 +19408,7 @@
         <v>44884</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -19481,7 +19481,7 @@
         <v>44628</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -19554,7 +19554,7 @@
         <v>44525</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -19627,7 +19627,7 @@
         <v>44525</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -19700,7 +19700,7 @@
         <v>44627</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -19773,7 +19773,7 @@
         <v>44785</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -19846,7 +19846,7 @@
         <v>44643</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -19919,7 +19919,7 @@
         <v>44720</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -19992,7 +19992,7 @@
         <v>44595</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -20070,7 +20070,7 @@
         <v>44481</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -20143,7 +20143,7 @@
         <v>44743</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -20216,7 +20216,7 @@
         <v>44497</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -20289,7 +20289,7 @@
         <v>44848</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -20362,7 +20362,7 @@
         <v>44776</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -20435,7 +20435,7 @@
         <v>44826</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -20508,7 +20508,7 @@
         <v>44791</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -20581,7 +20581,7 @@
         <v>44638</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -20654,7 +20654,7 @@
         <v>44498</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -20727,7 +20727,7 @@
         <v>44812</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -20800,7 +20800,7 @@
         <v>44796</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -20878,7 +20878,7 @@
         <v>45728</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -20951,7 +20951,7 @@
         <v>45275</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -21029,7 +21029,7 @@
         <v>45275</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -21107,7 +21107,7 @@
         <v>45275</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -21180,7 +21180,7 @@
         <v>44794</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -21253,7 +21253,7 @@
         <v>45359</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -21326,7 +21326,7 @@
         <v>44882</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -21399,7 +21399,7 @@
         <v>44860</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -21472,7 +21472,7 @@
         <v>44469</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -21545,7 +21545,7 @@
         <v>45427</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -21618,7 +21618,7 @@
         <v>45374</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -21691,7 +21691,7 @@
         <v>45755</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -21764,7 +21764,7 @@
         <v>45755</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -21837,7 +21837,7 @@
         <v>45755</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -21910,7 +21910,7 @@
         <v>45411</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -21983,7 +21983,7 @@
         <v>44768</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -22056,7 +22056,7 @@
         <v>45457</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -22129,7 +22129,7 @@
         <v>44865</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -22207,7 +22207,7 @@
         <v>45268</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -22280,7 +22280,7 @@
         <v>45230</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -22353,7 +22353,7 @@
         <v>44903</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -22426,7 +22426,7 @@
         <v>45579</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -22499,7 +22499,7 @@
         <v>44933</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -22572,7 +22572,7 @@
         <v>44945</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -22645,7 +22645,7 @@
         <v>44970</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -22723,7 +22723,7 @@
         <v>45593</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -22796,7 +22796,7 @@
         <v>45320</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -22869,7 +22869,7 @@
         <v>44475</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -22942,7 +22942,7 @@
         <v>45271</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -23015,7 +23015,7 @@
         <v>44475</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -23088,7 +23088,7 @@
         <v>45274</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -23161,7 +23161,7 @@
         <v>45293</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -23234,7 +23234,7 @@
         <v>44498</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -23307,7 +23307,7 @@
         <v>44509</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -23385,7 +23385,7 @@
         <v>46030</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -23458,7 +23458,7 @@
         <v>46030</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -23531,7 +23531,7 @@
         <v>46030</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -23604,7 +23604,7 @@
         <v>45737</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -23677,7 +23677,7 @@
         <v>45342</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -23750,7 +23750,7 @@
         <v>45299</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -23823,7 +23823,7 @@
         <v>45793</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -23896,7 +23896,7 @@
         <v>45300</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -23974,7 +23974,7 @@
         <v>44873</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -24052,7 +24052,7 @@
         <v>45485</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -24125,7 +24125,7 @@
         <v>45294</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -24198,7 +24198,7 @@
         <v>45294</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -24271,7 +24271,7 @@
         <v>46030</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -24344,7 +24344,7 @@
         <v>46030</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -24422,7 +24422,7 @@
         <v>46030</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -24500,7 +24500,7 @@
         <v>46030</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -24573,7 +24573,7 @@
         <v>44894</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -24646,7 +24646,7 @@
         <v>46035</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -24719,7 +24719,7 @@
         <v>46035</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -24792,7 +24792,7 @@
         <v>44936</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -24865,7 +24865,7 @@
         <v>44475</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -24938,7 +24938,7 @@
         <v>44599</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -25011,7 +25011,7 @@
         <v>45086</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -25084,7 +25084,7 @@
         <v>46038</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -25157,7 +25157,7 @@
         <v>46038</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -25230,7 +25230,7 @@
         <v>44487</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -25308,7 +25308,7 @@
         <v>45573</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -25381,7 +25381,7 @@
         <v>45610</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -25454,7 +25454,7 @@
         <v>44945</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -25527,7 +25527,7 @@
         <v>45901</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -25600,7 +25600,7 @@
         <v>44888</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -25673,7 +25673,7 @@
         <v>45491</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -25746,7 +25746,7 @@
         <v>46055</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -25819,7 +25819,7 @@
         <v>46055</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -25892,7 +25892,7 @@
         <v>44628</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -25965,7 +25965,7 @@
         <v>45912</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -26043,7 +26043,7 @@
         <v>45912</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -26121,7 +26121,7 @@
         <v>45912</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -26199,7 +26199,7 @@
         <v>45915</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -26272,7 +26272,7 @@
         <v>44897</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -26350,7 +26350,7 @@
         <v>45741</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -26423,7 +26423,7 @@
         <v>45804</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -26496,7 +26496,7 @@
         <v>44889</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -26574,7 +26574,7 @@
         <v>45555</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -26652,7 +26652,7 @@
         <v>45919</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -26725,7 +26725,7 @@
         <v>45922</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -26803,7 +26803,7 @@
         <v>46077</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -26876,7 +26876,7 @@
         <v>45930</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -26949,7 +26949,7 @@
         <v>46079</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -27022,7 +27022,7 @@
         <v>45928</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -27095,7 +27095,7 @@
         <v>45932</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -27173,7 +27173,7 @@
         <v>45392</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -27246,7 +27246,7 @@
         <v>46087</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -27319,7 +27319,7 @@
         <v>46087</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -27392,7 +27392,7 @@
         <v>45397</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -27465,7 +27465,7 @@
         <v>44944</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -27538,7 +27538,7 @@
         <v>45230</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -27611,7 +27611,7 @@
         <v>45202</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -27684,7 +27684,7 @@
         <v>45229</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -27757,7 +27757,7 @@
         <v>45244</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -27835,7 +27835,7 @@
         <v>45555</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -27908,7 +27908,7 @@
         <v>44945</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -27981,7 +27981,7 @@
         <v>45623</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -28054,7 +28054,7 @@
         <v>46094</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -28127,7 +28127,7 @@
         <v>44939</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -28200,7 +28200,7 @@
         <v>44944</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -28273,7 +28273,7 @@
         <v>44986</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -28346,7 +28346,7 @@
         <v>45142</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -28419,7 +28419,7 @@
         <v>45941</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -28492,7 +28492,7 @@
         <v>46098</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -28565,7 +28565,7 @@
         <v>46099</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -28643,7 +28643,7 @@
         <v>45945</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -28716,7 +28716,7 @@
         <v>45596</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -28789,7 +28789,7 @@
         <v>44776</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -28862,7 +28862,7 @@
         <v>45952</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -28935,7 +28935,7 @@
         <v>44942</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -29008,7 +29008,7 @@
         <v>44690</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -29081,7 +29081,7 @@
         <v>45957</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -29154,7 +29154,7 @@
         <v>45957</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -29227,7 +29227,7 @@
         <v>45957</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -29300,7 +29300,7 @@
         <v>45092</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -29373,7 +29373,7 @@
         <v>46120</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -29446,7 +29446,7 @@
         <v>45624</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -29519,7 +29519,7 @@
         <v>44933</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -29592,7 +29592,7 @@
         <v>45089</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -29670,7 +29670,7 @@
         <v>44909</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -29743,7 +29743,7 @@
         <v>44994</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -29816,7 +29816,7 @@
         <v>45968</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -29889,7 +29889,7 @@
         <v>45968</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -29962,7 +29962,7 @@
         <v>45968</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -30035,7 +30035,7 @@
         <v>45973</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -30108,7 +30108,7 @@
         <v>44936</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -30181,7 +30181,7 @@
         <v>44967</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -30259,7 +30259,7 @@
         <v>45300</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -30337,7 +30337,7 @@
         <v>45973</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -30410,7 +30410,7 @@
         <v>45275</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -30483,7 +30483,7 @@
         <v>45977</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -30561,7 +30561,7 @@
         <v>45153</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -30639,7 +30639,7 @@
         <v>45096</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -30717,7 +30717,7 @@
         <v>46134</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -30790,7 +30790,7 @@
         <v>45225</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -30868,7 +30868,7 @@
         <v>45142</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -30941,7 +30941,7 @@
         <v>45774</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -31014,7 +31014,7 @@
         <v>45967</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -31087,7 +31087,7 @@
         <v>46086</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -31160,7 +31160,7 @@
         <v>45712</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -31233,7 +31233,7 @@
         <v>45989</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -31306,7 +31306,7 @@
         <v>45905</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -31379,7 +31379,7 @@
         <v>45938</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -31457,7 +31457,7 @@
         <v>46008</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -31530,7 +31530,7 @@
         <v>45639</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -31603,7 +31603,7 @@
         <v>46057</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -31676,7 +31676,7 @@
         <v>45086</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -31749,7 +31749,7 @@
         <v>46099</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -31822,7 +31822,7 @@
         <v>45147</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -31895,7 +31895,7 @@
         <v>46086</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -31968,7 +31968,7 @@
         <v>46086</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -32041,7 +32041,7 @@
         <v>44767</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -32114,7 +32114,7 @@
         <v>45774</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -32187,7 +32187,7 @@
         <v>45993</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -32260,7 +32260,7 @@
         <v>45996</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -32338,7 +32338,7 @@
         <v>45816</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -32411,7 +32411,7 @@
         <v>44498</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -32484,7 +32484,7 @@
         <v>46000</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -32562,7 +32562,7 @@
         <v>45187</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -32640,7 +32640,7 @@
         <v>44509</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -32718,7 +32718,7 @@
         <v>44824</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -32791,7 +32791,7 @@
         <v>46010</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -32864,7 +32864,7 @@
         <v>45821</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -32937,7 +32937,7 @@
         <v>45013</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -33010,7 +33010,7 @@
         <v>45729</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -33083,7 +33083,7 @@
         <v>45121</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -33156,7 +33156,7 @@
         <v>45568</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -33229,7 +33229,7 @@
         <v>45755</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -33302,7 +33302,7 @@
         <v>44862</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -33375,7 +33375,7 @@
         <v>45069</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -33448,7 +33448,7 @@
         <v>45111</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -33526,7 +33526,7 @@
         <v>45077</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -33599,7 +33599,7 @@
         <v>44565</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -33672,7 +33672,7 @@
         <v>46145</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -33745,7 +33745,7 @@
         <v>45090</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -33818,7 +33818,7 @@
         <v>46147</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -33896,7 +33896,7 @@
         <v>45133</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -33969,7 +33969,7 @@
         <v>46147</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -34047,7 +34047,7 @@
         <v>45082</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -34120,7 +34120,7 @@
         <v>46154</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -34198,7 +34198,7 @@
         <v>46154</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -34276,7 +34276,7 @@
         <v>45209</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -34349,7 +34349,7 @@
         <v>46154</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -34427,7 +34427,7 @@
         <v>46154</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -34505,7 +34505,7 @@
         <v>45105</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -34583,7 +34583,7 @@
         <v>46154</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -34661,7 +34661,7 @@
         <v>44812</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -34734,7 +34734,7 @@
         <v>44862</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -34807,7 +34807,7 @@
         <v>46154</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -34885,7 +34885,7 @@
         <v>46153</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -34958,7 +34958,7 @@
         <v>45555</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -35036,7 +35036,7 @@
         <v>44928</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -35109,7 +35109,7 @@
         <v>45092</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -35182,7 +35182,7 @@
         <v>45275</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -35255,7 +35255,7 @@
         <v>45729</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -35333,7 +35333,7 @@
         <v>45379</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -35406,7 +35406,7 @@
         <v>45774</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -35479,7 +35479,7 @@
         <v>45737</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -35552,7 +35552,7 @@
         <v>45491</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -35625,7 +35625,7 @@
         <v>45231</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -35698,7 +35698,7 @@
         <v>44966</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -35771,7 +35771,7 @@
         <v>45568</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -35844,7 +35844,7 @@
         <v>45833</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -35917,7 +35917,7 @@
         <v>45655</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -35990,7 +35990,7 @@
         <v>44501</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -36063,7 +36063,7 @@
         <v>44949</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -36136,7 +36136,7 @@
         <v>45294</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -36209,7 +36209,7 @@
         <v>45341</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -36282,7 +36282,7 @@
         <v>45614</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -36355,7 +36355,7 @@
         <v>45231</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -36428,7 +36428,7 @@
         <v>45852</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -36501,7 +36501,7 @@
         <v>44909</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -36574,7 +36574,7 @@
         <v>45217</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -36647,7 +36647,7 @@
         <v>45195</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -36720,7 +36720,7 @@
         <v>45860</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -36793,7 +36793,7 @@
         <v>45860</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -36866,7 +36866,7 @@
         <v>45275</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -36939,7 +36939,7 @@
         <v>45489</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -37012,7 +37012,7 @@
         <v>45337</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -37085,7 +37085,7 @@
         <v>45404</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -37158,7 +37158,7 @@
         <v>45111</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -37236,7 +37236,7 @@
         <v>44558</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -37309,7 +37309,7 @@
         <v>45275</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -37382,7 +37382,7 @@
         <v>45453</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -37455,7 +37455,7 @@
         <v>45483</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -37528,7 +37528,7 @@
         <v>45106</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -37601,7 +37601,7 @@
         <v>45106</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -37674,7 +37674,7 @@
         <v>45106</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -37747,7 +37747,7 @@
         <v>45456</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -37820,7 +37820,7 @@
         <v>44509</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -37893,7 +37893,7 @@
         <v>45037</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -37971,7 +37971,7 @@
         <v>45120</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -38044,7 +38044,7 @@
         <v>46181</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -38117,7 +38117,7 @@
         <v>44937</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -38190,7 +38190,7 @@
         <v>46181</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -38263,7 +38263,7 @@
         <v>45030</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -38336,7 +38336,7 @@
         <v>45644</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -38409,7 +38409,7 @@
         <v>45117</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -38482,7 +38482,7 @@
         <v>45750</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -38555,7 +38555,7 @@
         <v>45140</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -38628,7 +38628,7 @@
         <v>45125</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -38701,7 +38701,7 @@
         <v>45678</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -38774,7 +38774,7 @@
         <v>45116</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -38847,7 +38847,7 @@
         <v>45470</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -38925,7 +38925,7 @@
         <v>45155</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -38998,7 +38998,7 @@
         <v>44993</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -39071,7 +39071,7 @@
         <v>45177</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -39144,7 +39144,7 @@
         <v>46085</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -39217,7 +39217,7 @@
         <v>44783</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -39290,7 +39290,7 @@
         <v>45005</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -39363,7 +39363,7 @@
         <v>45274</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -39436,7 +39436,7 @@
         <v>45275</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -39514,7 +39514,7 @@
         <v>45275</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -39592,7 +39592,7 @@
         <v>44608</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -39670,7 +39670,7 @@
         <v>45152</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -39743,7 +39743,7 @@
         <v>45804</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -39816,7 +39816,7 @@
         <v>45625</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -39889,7 +39889,7 @@
         <v>46199</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -39962,7 +39962,7 @@
         <v>46154</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -40040,7 +40040,7 @@
         <v>44643</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -40113,7 +40113,7 @@
         <v>46203</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -40186,7 +40186,7 @@
         <v>44803</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -40259,7 +40259,7 @@
         <v>46205</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -40332,7 +40332,7 @@
         <v>46206</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -40405,7 +40405,7 @@
         <v>44859</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -40483,7 +40483,7 @@
         <v>46206</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -40556,7 +40556,7 @@
         <v>44600</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -40629,7 +40629,7 @@
         <v>44795</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -40702,7 +40702,7 @@
         <v>46206</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -40775,7 +40775,7 @@
         <v>45225</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -40848,7 +40848,7 @@
         <v>46206</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -40921,7 +40921,7 @@
         <v>46206</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -40994,7 +40994,7 @@
         <v>46206</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -41067,7 +41067,7 @@
         <v>45230</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -41140,7 +41140,7 @@
         <v>46206</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -41213,7 +41213,7 @@
         <v>46206</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -41286,7 +41286,7 @@
         <v>46206</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -41359,7 +41359,7 @@
         <v>46254</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -41432,7 +41432,7 @@
         <v>44683</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -41505,7 +41505,7 @@
         <v>45655</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -41578,7 +41578,7 @@
         <v>44638</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -41651,7 +41651,7 @@
         <v>44623</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -41724,7 +41724,7 @@
         <v>45703</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -41797,7 +41797,7 @@
         <v>45146</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -41875,7 +41875,7 @@
         <v>45111</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -41948,7 +41948,7 @@
         <v>45774</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -42021,7 +42021,7 @@
         <v>46259</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -42099,7 +42099,7 @@
         <v>46259</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -42177,7 +42177,7 @@
         <v>45245</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -42255,7 +42255,7 @@
         <v>45231</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -42328,7 +42328,7 @@
         <v>45230</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -42401,7 +42401,7 @@
         <v>45160</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -42474,7 +42474,7 @@
         <v>46147</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -42552,7 +42552,7 @@
         <v>44743</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -42625,7 +42625,7 @@
         <v>45205</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -42698,7 +42698,7 @@
         <v>46266</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -42771,7 +42771,7 @@
         <v>46266</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -42844,7 +42844,7 @@
         <v>46265</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -42917,7 +42917,7 @@
         <v>44909</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -42990,7 +42990,7 @@
         <v>45306</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -43063,7 +43063,7 @@
         <v>46265</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -43136,7 +43136,7 @@
         <v>44768</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -43209,7 +43209,7 @@
         <v>44767</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -43282,7 +43282,7 @@
         <v>46267</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -43360,7 +43360,7 @@
         <v>44858</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -43433,7 +43433,7 @@
         <v>45477</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -43511,7 +43511,7 @@
         <v>46267</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -43589,7 +43589,7 @@
         <v>46267</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -43667,7 +43667,7 @@
         <v>46264</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -43740,7 +43740,7 @@
         <v>46267</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -43818,7 +43818,7 @@
         <v>46267</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -43896,7 +43896,7 @@
         <v>46269</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -43974,7 +43974,7 @@
         <v>44775</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -44047,7 +44047,7 @@
         <v>46269</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -44125,7 +44125,7 @@
         <v>44930</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -44203,7 +44203,7 @@
         <v>46269</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -44281,7 +44281,7 @@
         <v>46269</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -44359,7 +44359,7 @@
         <v>46272</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -44437,7 +44437,7 @@
         <v>44865</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -44510,7 +44510,7 @@
         <v>46269</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -44588,7 +44588,7 @@
         <v>44888</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -44661,7 +44661,7 @@
         <v>46269</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -44739,7 +44739,7 @@
         <v>46272</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -44817,7 +44817,7 @@
         <v>46269</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -44895,7 +44895,7 @@
         <v>45275</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -44973,7 +44973,7 @@
         <v>45153</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -45051,7 +45051,7 @@
         <v>45044</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -45124,7 +45124,7 @@
         <v>44930</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -45202,7 +45202,7 @@
         <v>46274</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -45280,7 +45280,7 @@
         <v>46272</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -45358,7 +45358,7 @@
         <v>45309</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -45431,7 +45431,7 @@
         <v>46272</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -45509,7 +45509,7 @@
         <v>45293</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -45582,7 +45582,7 @@
         <v>46275</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -45655,7 +45655,7 @@
         <v>46275</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -45728,7 +45728,7 @@
         <v>45238</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -45801,7 +45801,7 @@
         <v>46272</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -45879,7 +45879,7 @@
         <v>46275</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -45952,7 +45952,7 @@
         <v>45048</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -46025,7 +46025,7 @@
         <v>45225</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -46098,7 +46098,7 @@
         <v>46279</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -46171,7 +46171,7 @@
         <v>45268</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -46244,7 +46244,7 @@
         <v>45161</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -46317,7 +46317,7 @@
         <v>46239</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -46390,7 +46390,7 @@
         <v>46239</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -46463,7 +46463,7 @@
         <v>44994</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -46536,7 +46536,7 @@
         <v>44987</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -46609,7 +46609,7 @@
         <v>46272</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -46687,7 +46687,7 @@
         <v>46240</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -46765,7 +46765,7 @@
         <v>44498</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -46838,7 +46838,7 @@
         <v>44498</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -46911,7 +46911,7 @@
         <v>44909</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -46984,7 +46984,7 @@
         <v>45492</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -47057,7 +47057,7 @@
         <v>44958</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -47130,7 +47130,7 @@
         <v>44810</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -47203,7 +47203,7 @@
         <v>46245</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -47276,7 +47276,7 @@
         <v>46245</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -47349,7 +47349,7 @@
         <v>46288</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -47422,7 +47422,7 @@
         <v>46288</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -47495,7 +47495,7 @@
         <v>44949</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -47568,7 +47568,7 @@
         <v>44911</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -47641,7 +47641,7 @@
         <v>44641</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -47719,7 +47719,7 @@
         <v>46288</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -47792,7 +47792,7 @@
         <v>46288</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -47865,7 +47865,7 @@
         <v>46248</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -47943,7 +47943,7 @@
         <v>45579</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -48016,7 +48016,7 @@
         <v>44483</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -48089,7 +48089,7 @@
         <v>46289</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -48167,7 +48167,7 @@
         <v>45147</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -48240,7 +48240,7 @@
         <v>46248</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -48318,7 +48318,7 @@
         <v>44994</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -48391,7 +48391,7 @@
         <v>44882</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -48464,7 +48464,7 @@
         <v>46290</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -48537,7 +48537,7 @@
         <v>46290</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -48610,7 +48610,7 @@
         <v>46248</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -48688,7 +48688,7 @@
         <v>46275</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -48761,7 +48761,7 @@
         <v>46248</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -48839,7 +48839,7 @@
         <v>45111</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -48912,7 +48912,7 @@
         <v>46289</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -48990,7 +48990,7 @@
         <v>46289</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -49068,7 +49068,7 @@
         <v>44740</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -49141,7 +49141,7 @@
         <v>44658</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -49214,7 +49214,7 @@
         <v>46248</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -49292,7 +49292,7 @@
         <v>45237</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -49365,7 +49365,7 @@
         <v>46248</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -49443,7 +49443,7 @@
         <v>44930</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -49521,7 +49521,7 @@
         <v>45281</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -49599,7 +49599,7 @@
         <v>45274</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -49672,7 +49672,7 @@
         <v>45435</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -49745,7 +49745,7 @@
         <v>45111</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -49818,7 +49818,7 @@
         <v>45392</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -49896,7 +49896,7 @@
         <v>44508</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -49969,7 +49969,7 @@
         <v>45049</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -50042,7 +50042,7 @@
         <v>45146</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -50120,7 +50120,7 @@
         <v>44665</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -50198,7 +50198,7 @@
         <v>45597</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -50271,7 +50271,7 @@
         <v>45236</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -50349,7 +50349,7 @@
         <v>44767</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -50422,7 +50422,7 @@
         <v>44931</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -50495,7 +50495,7 @@
         <v>45475</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -50568,7 +50568,7 @@
         <v>44988</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -50646,7 +50646,7 @@
         <v>45579</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -50719,7 +50719,7 @@
         <v>45266</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -50792,7 +50792,7 @@
         <v>45302</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -50865,7 +50865,7 @@
         <v>45082</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -50938,7 +50938,7 @@
         <v>45590</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -51011,7 +51011,7 @@
         <v>44498</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -51084,7 +51084,7 @@
         <v>45364</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -51162,7 +51162,7 @@
         <v>45655</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -51235,7 +51235,7 @@
         <v>45655</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -51308,7 +51308,7 @@
         <v>45655</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -51381,7 +51381,7 @@
         <v>44909</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -51454,7 +51454,7 @@
         <v>45678</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -51527,7 +51527,7 @@
         <v>45140</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -51600,7 +51600,7 @@
         <v>44794</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -51673,7 +51673,7 @@
         <v>45294</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -51751,7 +51751,7 @@
         <v>45021</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -51824,7 +51824,7 @@
         <v>45491</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -51897,7 +51897,7 @@
         <v>45217</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -51970,7 +51970,7 @@
         <v>45217</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -52043,7 +52043,7 @@
         <v>45429</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -52116,7 +52116,7 @@
         <v>45177</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -52189,7 +52189,7 @@
         <v>45299</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -52262,7 +52262,7 @@
         <v>44986</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -52335,7 +52335,7 @@
         <v>45623</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -52408,7 +52408,7 @@
         <v>45623</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -52481,7 +52481,7 @@
         <v>45203</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -52554,7 +52554,7 @@
         <v>45604</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -52632,7 +52632,7 @@
         <v>44923</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -52710,7 +52710,7 @@
         <v>45748</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -52783,7 +52783,7 @@
         <v>44953</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -52856,7 +52856,7 @@
         <v>45161</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -52929,7 +52929,7 @@
         <v>45741</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -53002,7 +53002,7 @@
         <v>45265</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -53075,7 +53075,7 @@
         <v>45261</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -53148,7 +53148,7 @@
         <v>45296</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -53221,7 +53221,7 @@
         <v>45219</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -53299,7 +53299,7 @@
         <v>45230</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -53372,7 +53372,7 @@
         <v>45082</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -53445,7 +53445,7 @@
         <v>45268</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -53518,7 +53518,7 @@
         <v>44986</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -53591,7 +53591,7 @@
         <v>45655</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -53664,7 +53664,7 @@
         <v>45266</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -53742,7 +53742,7 @@
         <v>45300</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -53820,7 +53820,7 @@
         <v>45182</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -53893,7 +53893,7 @@
         <v>45695</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -53966,7 +53966,7 @@
         <v>45655</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -54039,7 +54039,7 @@
         <v>45545</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -54112,7 +54112,7 @@
         <v>45208</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -54185,7 +54185,7 @@
         <v>45671</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -54258,7 +54258,7 @@
         <v>45779</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -54331,7 +54331,7 @@
         <v>45779</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -54404,7 +54404,7 @@
         <v>45246</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -54477,7 +54477,7 @@
         <v>45359</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -54550,7 +54550,7 @@
         <v>45785</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -54623,7 +54623,7 @@
         <v>45342</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -54696,7 +54696,7 @@
         <v>45546</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -54769,7 +54769,7 @@
         <v>45664</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -54842,7 +54842,7 @@
         <v>45573</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -54915,7 +54915,7 @@
         <v>45483</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -54988,7 +54988,7 @@
         <v>45541</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -55061,7 +55061,7 @@
         <v>44855</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -55134,7 +55134,7 @@
         <v>45133</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -55207,7 +55207,7 @@
         <v>45541</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -55280,7 +55280,7 @@
         <v>45699</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -55353,7 +55353,7 @@
         <v>46040</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -55426,7 +55426,7 @@
         <v>46108</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -55499,7 +55499,7 @@
         <v>46183</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>

--- a/Översikt LINKÖPING.xlsx
+++ b/Översikt LINKÖPING.xlsx
@@ -601,7 +601,7 @@
         <v>45756</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -741,7 +741,7 @@
         <v>45644</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>44679</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>46090</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>45293</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>44855</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
         <v>45278</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1505,7 +1505,7 @@
         <v>46275</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1634,7 +1634,7 @@
         <v>44368</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1750,7 +1750,7 @@
         <v>46090</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1863,7 +1863,7 @@
         <v>45720</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1975,7 +1975,7 @@
         <v>45720</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         <v>46055</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2207,7 +2207,7 @@
         <v>45860</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2318,7 +2318,7 @@
         <v>45804</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2433,7 +2433,7 @@
         <v>46206</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2552,7 +2552,7 @@
         <v>45280</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2668,7 +2668,7 @@
         <v>46090</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2778,7 +2778,7 @@
         <v>45756</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2892,7 +2892,7 @@
         <v>46275</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3010,7 +3010,7 @@
         <v>45068</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
         <v>46146</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3233,7 +3233,7 @@
         <v>44949</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
         <v>44588</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3455,7 +3455,7 @@
         <v>44679</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3569,7 +3569,7 @@
         <v>43997</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3678,7 +3678,7 @@
         <v>44679</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3795,7 +3795,7 @@
         <v>44745</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3903,7 +3903,7 @@
         <v>46050</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4011,7 +4011,7 @@
         <v>45714</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4124,7 +4124,7 @@
         <v>45943</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4232,7 +4232,7 @@
         <v>46079</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4340,7 +4340,7 @@
         <v>46107</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4457,7 +4457,7 @@
         <v>45932</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4570,7 +4570,7 @@
         <v>44479</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4683,7 +4683,7 @@
         <v>45555</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4796,7 +4796,7 @@
         <v>45089</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4904,7 +4904,7 @@
         <v>44834</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5012,7 +5012,7 @@
         <v>44679</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5124,7 +5124,7 @@
         <v>44679</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5236,7 +5236,7 @@
         <v>44479</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5348,7 +5348,7 @@
         <v>44855</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5459,7 +5459,7 @@
         <v>44930</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5575,7 +5575,7 @@
         <v>45664</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5682,7 +5682,7 @@
         <v>45153</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5794,7 +5794,7 @@
         <v>45941</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5905,7 +5905,7 @@
         <v>46087</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6016,7 +6016,7 @@
         <v>44830</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6123,7 +6123,7 @@
         <v>45989</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6230,7 +6230,7 @@
         <v>44916</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6342,7 +6342,7 @@
         <v>45774</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6453,7 +6453,7 @@
         <v>46146</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6564,7 +6564,7 @@
         <v>45236</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6675,7 +6675,7 @@
         <v>45294</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6782,7 +6782,7 @@
         <v>46206</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6889,7 +6889,7 @@
         <v>46289</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7009,7 +7009,7 @@
         <v>45163</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7116,7 +7116,7 @@
         <v>45217</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7228,7 +7228,7 @@
         <v>45621</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7335,7 +7335,7 @@
         <v>44848</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7441,7 +7441,7 @@
         <v>44498</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7551,7 +7551,7 @@
         <v>45191</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7662,7 +7662,7 @@
         <v>45216</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7768,7 +7768,7 @@
         <v>44909</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7878,7 +7878,7 @@
         <v>46043</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7993,7 +7993,7 @@
         <v>45572</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8099,7 +8099,7 @@
         <v>45071</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8210,7 +8210,7 @@
         <v>45712</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8321,7 +8321,7 @@
         <v>44597</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8427,7 +8427,7 @@
         <v>44936</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8533,7 +8533,7 @@
         <v>45639</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8639,7 +8639,7 @@
         <v>44487</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8750,7 +8750,7 @@
         <v>45804</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8856,7 +8856,7 @@
         <v>45745</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8966,7 +8966,7 @@
         <v>45932</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9077,7 +9077,7 @@
         <v>45461</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9183,7 +9183,7 @@
         <v>45140</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9293,7 +9293,7 @@
         <v>45595</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9399,7 +9399,7 @@
         <v>45554</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9514,7 +9514,7 @@
         <v>46107</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9625,7 +9625,7 @@
         <v>46153</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9731,7 +9731,7 @@
         <v>45547</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9841,7 +9841,7 @@
         <v>44487</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9952,7 +9952,7 @@
         <v>45774</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10058,7 +10058,7 @@
         <v>46259</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10169,7 +10169,7 @@
         <v>45244</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10280,7 +10280,7 @@
         <v>44930</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10391,7 +10391,7 @@
         <v>46178</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10497,7 +10497,7 @@
         <v>45176</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10603,7 +10603,7 @@
         <v>45148</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10709,7 +10709,7 @@
         <v>45621</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10815,7 +10815,7 @@
         <v>45774</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10925,7 +10925,7 @@
         <v>44159</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11036,7 +11036,7 @@
         <v>44537</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11146,7 +11146,7 @@
         <v>45665</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11256,7 +11256,7 @@
         <v>44938</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11361,7 +11361,7 @@
         <v>45176</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11466,7 +11466,7 @@
         <v>45369</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11571,7 +11571,7 @@
         <v>44768</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11676,7 +11676,7 @@
         <v>45141</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11781,7 +11781,7 @@
         <v>45915</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11891,7 +11891,7 @@
         <v>45463</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11996,7 +11996,7 @@
         <v>45541</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12101,7 +12101,7 @@
         <v>45222</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12215,7 +12215,7 @@
         <v>45941</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12320,7 +12320,7 @@
         <v>46079</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12425,7 +12425,7 @@
         <v>45812</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12530,7 +12530,7 @@
         <v>45243</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12640,7 +12640,7 @@
         <v>45816</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12745,7 +12745,7 @@
         <v>45968</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12850,7 +12850,7 @@
         <v>45604</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12960,7 +12960,7 @@
         <v>45988</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13070,7 +13070,7 @@
         <v>44929</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13175,7 +13175,7 @@
         <v>45554</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13285,7 +13285,7 @@
         <v>45994</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13390,7 +13390,7 @@
         <v>45153</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13500,7 +13500,7 @@
         <v>45579</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13605,7 +13605,7 @@
         <v>45244</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13715,7 +13715,7 @@
         <v>45965</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13825,7 +13825,7 @@
         <v>45246</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13935,7 +13935,7 @@
         <v>44889</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14040,7 +14040,7 @@
         <v>45604</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14150,7 +14150,7 @@
         <v>46175</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14255,7 +14255,7 @@
         <v>45071</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14365,7 +14365,7 @@
         <v>46259</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14475,7 +14475,7 @@
         <v>45308</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14585,7 +14585,7 @@
         <v>46264</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14690,7 +14690,7 @@
         <v>45442</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14799,7 +14799,7 @@
         <v>44945</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14904,7 +14904,7 @@
         <v>45412</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -15009,7 +15009,7 @@
         <v>45244</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -15119,7 +15119,7 @@
         <v>46206</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15224,7 +15224,7 @@
         <v>44945</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15329,7 +15329,7 @@
         <v>44881</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15434,7 +15434,7 @@
         <v>46289</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15544,7 +15544,7 @@
         <v>45460</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -15649,7 +15649,7 @@
         <v>44950</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -15754,7 +15754,7 @@
         <v>45294</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -15864,7 +15864,7 @@
         <v>45266</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -15969,7 +15969,7 @@
         <v>45111</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -16074,7 +16074,7 @@
         <v>44949</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -16179,7 +16179,7 @@
         <v>45491</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -16284,7 +16284,7 @@
         <v>44496</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -16394,7 +16394,7 @@
         <v>44478</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -16472,7 +16472,7 @@
         <v>44523</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -16545,7 +16545,7 @@
         <v>44608</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -16618,7 +16618,7 @@
         <v>44510</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -16691,7 +16691,7 @@
         <v>44488</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -16764,7 +16764,7 @@
         <v>44764</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -16837,7 +16837,7 @@
         <v>44855</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -16915,7 +16915,7 @@
         <v>44846</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -16988,7 +16988,7 @@
         <v>44573</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -17061,7 +17061,7 @@
         <v>44496</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -17134,7 +17134,7 @@
         <v>44853</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -17207,7 +17207,7 @@
         <v>44782</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -17280,7 +17280,7 @@
         <v>44679</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -17358,7 +17358,7 @@
         <v>44777</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -17431,7 +17431,7 @@
         <v>44753</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -17509,7 +17509,7 @@
         <v>44510</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -17582,7 +17582,7 @@
         <v>44487</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -17660,7 +17660,7 @@
         <v>44487</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -17738,7 +17738,7 @@
         <v>44823</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -17811,7 +17811,7 @@
         <v>44515</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -17889,7 +17889,7 @@
         <v>44767</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -17962,7 +17962,7 @@
         <v>44719</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -18040,7 +18040,7 @@
         <v>44487</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -18118,7 +18118,7 @@
         <v>44776</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -18191,7 +18191,7 @@
         <v>44692</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -18264,7 +18264,7 @@
         <v>44882</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -18342,7 +18342,7 @@
         <v>44803</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -18415,7 +18415,7 @@
         <v>44588</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -18488,7 +18488,7 @@
         <v>44743</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -18561,7 +18561,7 @@
         <v>44574</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -18634,7 +18634,7 @@
         <v>44571</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -18707,7 +18707,7 @@
         <v>44841</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -18780,7 +18780,7 @@
         <v>44537</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -18853,7 +18853,7 @@
         <v>44809</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -18926,7 +18926,7 @@
         <v>44884</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -18999,7 +18999,7 @@
         <v>44884</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -19072,7 +19072,7 @@
         <v>44628</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -19145,7 +19145,7 @@
         <v>44525</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -19218,7 +19218,7 @@
         <v>44525</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -19291,7 +19291,7 @@
         <v>44627</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -19364,7 +19364,7 @@
         <v>44785</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -19437,7 +19437,7 @@
         <v>44643</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -19510,7 +19510,7 @@
         <v>44720</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -19583,7 +19583,7 @@
         <v>44595</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -19661,7 +19661,7 @@
         <v>44481</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -19734,7 +19734,7 @@
         <v>44743</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -19807,7 +19807,7 @@
         <v>44497</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -19880,7 +19880,7 @@
         <v>44848</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -19953,7 +19953,7 @@
         <v>44776</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -20026,7 +20026,7 @@
         <v>44826</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -20099,7 +20099,7 @@
         <v>44791</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -20172,7 +20172,7 @@
         <v>44498</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -20245,7 +20245,7 @@
         <v>44638</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -20318,7 +20318,7 @@
         <v>44796</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -20396,7 +20396,7 @@
         <v>44812</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -20469,7 +20469,7 @@
         <v>44794</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -20542,7 +20542,7 @@
         <v>45274</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -20615,7 +20615,7 @@
         <v>44945</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -20688,7 +20688,7 @@
         <v>45728</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -20761,7 +20761,7 @@
         <v>45477</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -20839,7 +20839,7 @@
         <v>45236</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -20917,7 +20917,7 @@
         <v>44767</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -20990,7 +20990,7 @@
         <v>45435</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -21063,7 +21063,7 @@
         <v>45294</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -21136,7 +21136,7 @@
         <v>45457</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -21209,7 +21209,7 @@
         <v>45089</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -21287,7 +21287,7 @@
         <v>45140</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -21360,7 +21360,7 @@
         <v>44767</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -21433,7 +21433,7 @@
         <v>44897</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -21511,7 +21511,7 @@
         <v>44939</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -21584,7 +21584,7 @@
         <v>45217</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -21657,7 +21657,7 @@
         <v>45217</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -21730,7 +21730,7 @@
         <v>45142</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -21803,7 +21803,7 @@
         <v>45302</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -21876,7 +21876,7 @@
         <v>45225</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -21954,7 +21954,7 @@
         <v>45182</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -22027,7 +22027,7 @@
         <v>45238</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -22100,7 +22100,7 @@
         <v>45225</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -22173,7 +22173,7 @@
         <v>45225</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -22246,7 +22246,7 @@
         <v>45623</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -22319,7 +22319,7 @@
         <v>45664</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -22392,7 +22392,7 @@
         <v>45546</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -22465,7 +22465,7 @@
         <v>44498</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -22538,7 +22538,7 @@
         <v>44498</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -22611,7 +22611,7 @@
         <v>45275</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -22684,7 +22684,7 @@
         <v>45246</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -22757,7 +22757,7 @@
         <v>45133</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -22830,7 +22830,7 @@
         <v>45545</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -22903,7 +22903,7 @@
         <v>45483</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -22976,7 +22976,7 @@
         <v>44903</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -23049,7 +23049,7 @@
         <v>44945</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -23122,7 +23122,7 @@
         <v>46010</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -23195,7 +23195,7 @@
         <v>45030</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -23268,7 +23268,7 @@
         <v>44909</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -23341,7 +23341,7 @@
         <v>44909</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -23414,7 +23414,7 @@
         <v>44930</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -23492,7 +23492,7 @@
         <v>45161</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -23565,7 +23565,7 @@
         <v>46030</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -23638,7 +23638,7 @@
         <v>46030</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -23711,7 +23711,7 @@
         <v>46030</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -23784,7 +23784,7 @@
         <v>46030</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -23862,7 +23862,7 @@
         <v>46030</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -23940,7 +23940,7 @@
         <v>46030</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -24013,7 +24013,7 @@
         <v>46030</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -24086,7 +24086,7 @@
         <v>45309</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -24159,7 +24159,7 @@
         <v>46035</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -24232,7 +24232,7 @@
         <v>45901</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -24305,7 +24305,7 @@
         <v>45111</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -24378,7 +24378,7 @@
         <v>45793</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -24451,7 +24451,7 @@
         <v>46035</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -24524,7 +24524,7 @@
         <v>45160</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -24597,7 +24597,7 @@
         <v>45755</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -24670,7 +24670,7 @@
         <v>46038</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -24743,7 +24743,7 @@
         <v>45593</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -24816,7 +24816,7 @@
         <v>45624</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -24889,7 +24889,7 @@
         <v>45915</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -24962,7 +24962,7 @@
         <v>45912</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -25040,7 +25040,7 @@
         <v>45912</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -25118,7 +25118,7 @@
         <v>45912</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -25196,7 +25196,7 @@
         <v>45737</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -25269,7 +25269,7 @@
         <v>45111</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -25342,7 +25342,7 @@
         <v>45573</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -25415,7 +25415,7 @@
         <v>45294</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -25488,7 +25488,7 @@
         <v>45919</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -25561,7 +25561,7 @@
         <v>45804</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -25634,7 +25634,7 @@
         <v>45491</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -25707,7 +25707,7 @@
         <v>45922</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -25785,7 +25785,7 @@
         <v>44894</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -25858,7 +25858,7 @@
         <v>46055</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -25931,7 +25931,7 @@
         <v>46055</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -26004,7 +26004,7 @@
         <v>45928</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -26077,7 +26077,7 @@
         <v>45930</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -26150,7 +26150,7 @@
         <v>45678</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -26223,7 +26223,7 @@
         <v>45932</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -26301,7 +26301,7 @@
         <v>45750</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -26374,7 +26374,7 @@
         <v>44683</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -26447,7 +26447,7 @@
         <v>45274</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -26520,7 +26520,7 @@
         <v>45146</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -26598,7 +26598,7 @@
         <v>45941</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -26671,7 +26671,7 @@
         <v>45945</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -26744,7 +26744,7 @@
         <v>44888</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -26817,7 +26817,7 @@
         <v>45275</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -26890,7 +26890,7 @@
         <v>44487</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -26968,7 +26968,7 @@
         <v>46077</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -27041,7 +27041,7 @@
         <v>46079</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -27114,7 +27114,7 @@
         <v>45623</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -27187,7 +27187,7 @@
         <v>45623</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -27260,7 +27260,7 @@
         <v>44949</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -27333,7 +27333,7 @@
         <v>45456</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -27406,7 +27406,7 @@
         <v>45952</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -27479,7 +27479,7 @@
         <v>45957</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -27552,7 +27552,7 @@
         <v>45957</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -27625,7 +27625,7 @@
         <v>45957</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -27698,7 +27698,7 @@
         <v>46087</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -27771,7 +27771,7 @@
         <v>45013</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -27844,7 +27844,7 @@
         <v>44558</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -27917,7 +27917,7 @@
         <v>44743</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -27990,7 +27990,7 @@
         <v>45230</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -28063,7 +28063,7 @@
         <v>45816</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -28136,7 +28136,7 @@
         <v>45125</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -28209,7 +28209,7 @@
         <v>45610</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -28282,7 +28282,7 @@
         <v>46098</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -28355,7 +28355,7 @@
         <v>45968</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -28428,7 +28428,7 @@
         <v>45968</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -28501,7 +28501,7 @@
         <v>45968</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -28574,7 +28574,7 @@
         <v>46094</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -28647,7 +28647,7 @@
         <v>44865</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -28720,7 +28720,7 @@
         <v>46099</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -28798,7 +28798,7 @@
         <v>45359</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -28871,7 +28871,7 @@
         <v>45973</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -28944,7 +28944,7 @@
         <v>45973</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -29017,7 +29017,7 @@
         <v>45208</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -29090,7 +29090,7 @@
         <v>45147</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -29163,7 +29163,7 @@
         <v>45977</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -29241,7 +29241,7 @@
         <v>44600</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -29314,7 +29314,7 @@
         <v>45202</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -29387,7 +29387,7 @@
         <v>45729</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -29460,7 +29460,7 @@
         <v>45021</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -29533,7 +29533,7 @@
         <v>45821</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -29606,7 +29606,7 @@
         <v>45281</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -29684,7 +29684,7 @@
         <v>44783</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -29757,7 +29757,7 @@
         <v>45989</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -29830,7 +29830,7 @@
         <v>46120</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -29903,7 +29903,7 @@
         <v>44928</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -29976,7 +29976,7 @@
         <v>44933</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -30049,7 +30049,7 @@
         <v>44768</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -30122,7 +30122,7 @@
         <v>44909</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -30195,7 +30195,7 @@
         <v>44862</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -30268,7 +30268,7 @@
         <v>44889</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -30346,7 +30346,7 @@
         <v>45203</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -30419,7 +30419,7 @@
         <v>45996</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -30497,7 +30497,7 @@
         <v>44665</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -30575,7 +30575,7 @@
         <v>44860</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -30648,7 +30648,7 @@
         <v>46000</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -30726,7 +30726,7 @@
         <v>45774</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -30799,7 +30799,7 @@
         <v>44795</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -30872,7 +30872,7 @@
         <v>44933</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -30945,7 +30945,7 @@
         <v>44942</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -31018,7 +31018,7 @@
         <v>45293</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -31091,7 +31091,7 @@
         <v>45195</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -31164,7 +31164,7 @@
         <v>45111</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -31237,7 +31237,7 @@
         <v>45555</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -31315,7 +31315,7 @@
         <v>46134</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -31388,7 +31388,7 @@
         <v>45774</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -31461,7 +31461,7 @@
         <v>45082</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -31534,7 +31534,7 @@
         <v>45082</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -31607,7 +31607,7 @@
         <v>45967</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -31680,7 +31680,7 @@
         <v>46086</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -31753,7 +31753,7 @@
         <v>45590</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -31826,7 +31826,7 @@
         <v>46086</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -31899,7 +31899,7 @@
         <v>45244</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -31977,7 +31977,7 @@
         <v>44936</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -32050,7 +32050,7 @@
         <v>44931</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -32123,7 +32123,7 @@
         <v>45938</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -32201,7 +32201,7 @@
         <v>46008</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -32274,7 +32274,7 @@
         <v>45678</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -32347,7 +32347,7 @@
         <v>44623</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -32420,7 +32420,7 @@
         <v>45111</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -32498,7 +32498,7 @@
         <v>44923</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -32576,7 +32576,7 @@
         <v>45614</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -32649,7 +32649,7 @@
         <v>45489</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -32722,7 +32722,7 @@
         <v>45655</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -32795,7 +32795,7 @@
         <v>45712</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -32868,7 +32868,7 @@
         <v>46099</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -32941,7 +32941,7 @@
         <v>45106</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -33014,7 +33014,7 @@
         <v>45106</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -33087,7 +33087,7 @@
         <v>45296</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -33160,7 +33160,7 @@
         <v>45069</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -33233,7 +33233,7 @@
         <v>44501</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -33306,7 +33306,7 @@
         <v>45392</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -33379,7 +33379,7 @@
         <v>45555</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -33457,7 +33457,7 @@
         <v>45644</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -33530,7 +33530,7 @@
         <v>45852</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -33603,7 +33603,7 @@
         <v>44944</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -33676,7 +33676,7 @@
         <v>45261</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -33749,7 +33749,7 @@
         <v>45237</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -33822,7 +33822,7 @@
         <v>45140</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -33895,7 +33895,7 @@
         <v>45905</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -33968,7 +33968,7 @@
         <v>44803</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -34041,7 +34041,7 @@
         <v>46086</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -34114,7 +34114,7 @@
         <v>46057</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -34187,7 +34187,7 @@
         <v>45086</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -34260,7 +34260,7 @@
         <v>45860</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -34333,7 +34333,7 @@
         <v>45860</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -34406,7 +34406,7 @@
         <v>44987</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -34479,7 +34479,7 @@
         <v>45121</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -34552,7 +34552,7 @@
         <v>44565</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -34625,7 +34625,7 @@
         <v>44690</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -34698,7 +34698,7 @@
         <v>44768</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -34771,7 +34771,7 @@
         <v>44888</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -34844,7 +34844,7 @@
         <v>44986</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -34917,7 +34917,7 @@
         <v>44498</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -34990,7 +34990,7 @@
         <v>44967</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -35068,7 +35068,7 @@
         <v>45177</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -35141,7 +35141,7 @@
         <v>45116</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -35214,7 +35214,7 @@
         <v>46147</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -35292,7 +35292,7 @@
         <v>45146</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -35370,7 +35370,7 @@
         <v>46147</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -35448,7 +35448,7 @@
         <v>45153</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -35526,7 +35526,7 @@
         <v>46145</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -35599,7 +35599,7 @@
         <v>45230</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -35672,7 +35672,7 @@
         <v>45306</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -35745,7 +35745,7 @@
         <v>44862</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -35818,7 +35818,7 @@
         <v>45470</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -35896,7 +35896,7 @@
         <v>44911</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -35969,7 +35969,7 @@
         <v>45105</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -36047,7 +36047,7 @@
         <v>45187</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -36125,7 +36125,7 @@
         <v>46153</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -36198,7 +36198,7 @@
         <v>44930</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -36276,7 +36276,7 @@
         <v>44994</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -36349,7 +36349,7 @@
         <v>46154</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -36427,7 +36427,7 @@
         <v>45044</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -36500,7 +36500,7 @@
         <v>46154</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -36578,7 +36578,7 @@
         <v>46154</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -36656,7 +36656,7 @@
         <v>45300</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -36734,7 +36734,7 @@
         <v>44475</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -36807,7 +36807,7 @@
         <v>46154</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -36885,7 +36885,7 @@
         <v>46154</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -36963,7 +36963,7 @@
         <v>46154</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -37041,7 +37041,7 @@
         <v>45392</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -37119,7 +37119,7 @@
         <v>45655</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -37192,7 +37192,7 @@
         <v>45086</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -37265,7 +37265,7 @@
         <v>44483</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -37338,7 +37338,7 @@
         <v>45755</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -37411,7 +37411,7 @@
         <v>45737</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -37484,7 +37484,7 @@
         <v>45755</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -37557,7 +37557,7 @@
         <v>45755</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -37630,7 +37630,7 @@
         <v>45729</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -37708,7 +37708,7 @@
         <v>45379</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -37781,7 +37781,7 @@
         <v>45774</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -37854,7 +37854,7 @@
         <v>45117</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -37927,7 +37927,7 @@
         <v>45833</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -38000,7 +38000,7 @@
         <v>45374</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -38073,7 +38073,7 @@
         <v>44498</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -38146,7 +38146,7 @@
         <v>45337</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -38219,7 +38219,7 @@
         <v>45294</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -38297,7 +38297,7 @@
         <v>45625</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -38370,7 +38370,7 @@
         <v>44993</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -38443,7 +38443,7 @@
         <v>44508</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -38516,7 +38516,7 @@
         <v>45741</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -38589,7 +38589,7 @@
         <v>45320</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -38662,7 +38662,7 @@
         <v>45266</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -38740,7 +38740,7 @@
         <v>45695</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -38813,7 +38813,7 @@
         <v>45231</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -38886,7 +38886,7 @@
         <v>44949</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -38959,7 +38959,7 @@
         <v>44882</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -39032,7 +39032,7 @@
         <v>44882</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -39105,7 +39105,7 @@
         <v>45804</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -39178,7 +39178,7 @@
         <v>44930</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -39256,7 +39256,7 @@
         <v>45268</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -39329,7 +39329,7 @@
         <v>45005</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -39402,7 +39402,7 @@
         <v>44498</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -39475,7 +39475,7 @@
         <v>45092</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -39548,7 +39548,7 @@
         <v>44509</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -39626,7 +39626,7 @@
         <v>44475</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -39699,7 +39699,7 @@
         <v>46181</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -39772,7 +39772,7 @@
         <v>46181</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -39845,7 +39845,7 @@
         <v>45275</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -39918,7 +39918,7 @@
         <v>45275</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -39996,7 +39996,7 @@
         <v>45275</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -40074,7 +40074,7 @@
         <v>45411</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -40147,7 +40147,7 @@
         <v>46085</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -40220,7 +40220,7 @@
         <v>44658</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -40293,7 +40293,7 @@
         <v>45217</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -40366,7 +40366,7 @@
         <v>44873</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -40444,7 +40444,7 @@
         <v>45096</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -40522,7 +40522,7 @@
         <v>45741</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -40595,7 +40595,7 @@
         <v>44775</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -40668,7 +40668,7 @@
         <v>45655</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -40741,7 +40741,7 @@
         <v>45037</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -40819,7 +40819,7 @@
         <v>45271</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -40892,7 +40892,7 @@
         <v>46199</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -40965,7 +40965,7 @@
         <v>45177</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -41038,7 +41038,7 @@
         <v>46203</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -41111,7 +41111,7 @@
         <v>46154</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -41189,7 +41189,7 @@
         <v>45161</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -41262,7 +41262,7 @@
         <v>44958</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -41335,7 +41335,7 @@
         <v>44936</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -41408,7 +41408,7 @@
         <v>46206</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -41481,7 +41481,7 @@
         <v>46205</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -41554,7 +41554,7 @@
         <v>46206</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -41627,7 +41627,7 @@
         <v>46206</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -41700,7 +41700,7 @@
         <v>44638</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -41773,7 +41773,7 @@
         <v>46206</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -41846,7 +41846,7 @@
         <v>46206</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -41919,7 +41919,7 @@
         <v>46206</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -41992,7 +41992,7 @@
         <v>46206</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -42065,7 +42065,7 @@
         <v>46206</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -42138,7 +42138,7 @@
         <v>46206</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -42211,7 +42211,7 @@
         <v>45453</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -42284,7 +42284,7 @@
         <v>45293</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -42357,7 +42357,7 @@
         <v>44599</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -42430,7 +42430,7 @@
         <v>44776</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -42503,7 +42503,7 @@
         <v>45245</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -42581,7 +42581,7 @@
         <v>46259</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -42659,7 +42659,7 @@
         <v>46259</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -42737,7 +42737,7 @@
         <v>44970</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -42815,7 +42815,7 @@
         <v>45120</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -42888,7 +42888,7 @@
         <v>44608</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -42966,7 +42966,7 @@
         <v>45475</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -43039,7 +43039,7 @@
         <v>44824</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -43112,7 +43112,7 @@
         <v>45604</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -43190,7 +43190,7 @@
         <v>44865</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -43268,7 +43268,7 @@
         <v>45268</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -43341,7 +43341,7 @@
         <v>46265</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -43414,7 +43414,7 @@
         <v>45106</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -43487,7 +43487,7 @@
         <v>46265</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -43560,7 +43560,7 @@
         <v>46147</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -43638,7 +43638,7 @@
         <v>46267</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -43716,7 +43716,7 @@
         <v>46264</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -43789,7 +43789,7 @@
         <v>45090</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -43862,7 +43862,7 @@
         <v>44937</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -43935,7 +43935,7 @@
         <v>45111</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -44013,7 +44013,7 @@
         <v>46266</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -44086,7 +44086,7 @@
         <v>46266</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -44159,7 +44159,7 @@
         <v>44994</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -44232,7 +44232,7 @@
         <v>44945</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -44305,7 +44305,7 @@
         <v>46267</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -44383,7 +44383,7 @@
         <v>45596</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -44456,7 +44456,7 @@
         <v>46267</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -44534,7 +44534,7 @@
         <v>46267</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -44612,7 +44612,7 @@
         <v>46267</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -44690,7 +44690,7 @@
         <v>45077</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -44763,7 +44763,7 @@
         <v>46269</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -44841,7 +44841,7 @@
         <v>46269</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -44919,7 +44919,7 @@
         <v>46269</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -44997,7 +44997,7 @@
         <v>46269</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -45075,7 +45075,7 @@
         <v>46269</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -45153,7 +45153,7 @@
         <v>46269</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -45231,7 +45231,7 @@
         <v>45579</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -45304,7 +45304,7 @@
         <v>46269</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -45382,7 +45382,7 @@
         <v>46272</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -45460,7 +45460,7 @@
         <v>46272</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -45538,7 +45538,7 @@
         <v>46272</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -45616,7 +45616,7 @@
         <v>44966</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -45689,7 +45689,7 @@
         <v>46275</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -45762,7 +45762,7 @@
         <v>46274</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -45840,7 +45840,7 @@
         <v>45147</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -45913,7 +45913,7 @@
         <v>46275</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -45986,7 +45986,7 @@
         <v>46275</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -46059,7 +46059,7 @@
         <v>46272</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -46137,7 +46137,7 @@
         <v>46272</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -46215,7 +46215,7 @@
         <v>46279</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -46288,7 +46288,7 @@
         <v>45579</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -46361,7 +46361,7 @@
         <v>45155</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -46434,7 +46434,7 @@
         <v>45231</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -46507,7 +46507,7 @@
         <v>45230</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -46580,7 +46580,7 @@
         <v>45231</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -46653,7 +46653,7 @@
         <v>44509</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -46731,7 +46731,7 @@
         <v>45341</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -46804,7 +46804,7 @@
         <v>46239</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -46877,7 +46877,7 @@
         <v>45483</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -46950,7 +46950,7 @@
         <v>46239</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -47023,7 +47023,7 @@
         <v>46240</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -47101,7 +47101,7 @@
         <v>45229</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -47174,7 +47174,7 @@
         <v>44740</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -47247,7 +47247,7 @@
         <v>45082</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -47320,7 +47320,7 @@
         <v>45655</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -47393,7 +47393,7 @@
         <v>46272</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -47471,7 +47471,7 @@
         <v>44988</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -47549,7 +47549,7 @@
         <v>45568</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -47622,7 +47622,7 @@
         <v>45568</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -47695,7 +47695,7 @@
         <v>45485</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -47768,7 +47768,7 @@
         <v>45579</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -47841,7 +47841,7 @@
         <v>45748</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -47914,7 +47914,7 @@
         <v>45492</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -47987,7 +47987,7 @@
         <v>45230</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -48060,7 +48060,7 @@
         <v>46245</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -48133,7 +48133,7 @@
         <v>46289</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -48211,7 +48211,7 @@
         <v>46289</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -48289,7 +48289,7 @@
         <v>44475</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -48362,7 +48362,7 @@
         <v>46288</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -48435,7 +48435,7 @@
         <v>44986</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -48508,7 +48508,7 @@
         <v>44953</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -48581,7 +48581,7 @@
         <v>46288</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -48654,7 +48654,7 @@
         <v>46289</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -48732,7 +48732,7 @@
         <v>45092</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -48805,7 +48805,7 @@
         <v>46288</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -48878,7 +48878,7 @@
         <v>46245</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -48951,7 +48951,7 @@
         <v>45142</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -49024,7 +49024,7 @@
         <v>45300</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -49102,7 +49102,7 @@
         <v>44509</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -49175,7 +49175,7 @@
         <v>46288</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -49248,7 +49248,7 @@
         <v>45152</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -49321,7 +49321,7 @@
         <v>45209</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -49394,7 +49394,7 @@
         <v>46248</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -49472,7 +49472,7 @@
         <v>46248</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -49550,7 +49550,7 @@
         <v>46248</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -49628,7 +49628,7 @@
         <v>46275</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -49701,7 +49701,7 @@
         <v>46248</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -49779,7 +49779,7 @@
         <v>46290</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -49852,7 +49852,7 @@
         <v>46290</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -49925,7 +49925,7 @@
         <v>44858</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -49998,7 +49998,7 @@
         <v>45275</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -50076,7 +50076,7 @@
         <v>45639</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -50149,7 +50149,7 @@
         <v>46248</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -50227,7 +50227,7 @@
         <v>46248</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -50305,7 +50305,7 @@
         <v>45427</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -50378,7 +50378,7 @@
         <v>44628</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -50451,7 +50451,7 @@
         <v>46294</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -50529,7 +50529,7 @@
         <v>46294</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -50607,7 +50607,7 @@
         <v>46294</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -50685,7 +50685,7 @@
         <v>46294</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -50758,7 +50758,7 @@
         <v>44986</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -50831,7 +50831,7 @@
         <v>46294</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -50909,7 +50909,7 @@
         <v>44944</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -50982,7 +50982,7 @@
         <v>45655</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -51055,7 +51055,7 @@
         <v>45655</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -51128,7 +51128,7 @@
         <v>46294</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -51206,7 +51206,7 @@
         <v>46254</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -51279,7 +51279,7 @@
         <v>45597</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -51352,7 +51352,7 @@
         <v>45219</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -51430,7 +51430,7 @@
         <v>44994</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -51503,7 +51503,7 @@
         <v>45555</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -51576,7 +51576,7 @@
         <v>45703</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -51649,7 +51649,7 @@
         <v>45205</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -51722,7 +51722,7 @@
         <v>46293</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -51795,7 +51795,7 @@
         <v>44641</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -51873,7 +51873,7 @@
         <v>45655</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -51946,7 +51946,7 @@
         <v>44767</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -52019,7 +52019,7 @@
         <v>44909</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -52092,7 +52092,7 @@
         <v>44909</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -52165,7 +52165,7 @@
         <v>45230</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -52238,7 +52238,7 @@
         <v>45265</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -52311,7 +52311,7 @@
         <v>45294</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -52384,7 +52384,7 @@
         <v>45429</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -52457,7 +52457,7 @@
         <v>45299</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -52530,7 +52530,7 @@
         <v>45491</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -52603,7 +52603,7 @@
         <v>45274</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -52676,7 +52676,7 @@
         <v>45266</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -52749,7 +52749,7 @@
         <v>45268</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -52822,7 +52822,7 @@
         <v>45300</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -52900,7 +52900,7 @@
         <v>45342</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -52973,7 +52973,7 @@
         <v>45364</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -53051,7 +53051,7 @@
         <v>45275</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -53124,7 +53124,7 @@
         <v>45275</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -53202,7 +53202,7 @@
         <v>45275</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -53275,7 +53275,7 @@
         <v>45153</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -53353,7 +53353,7 @@
         <v>45397</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -53426,7 +53426,7 @@
         <v>45404</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -53499,7 +53499,7 @@
         <v>44810</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -53572,7 +53572,7 @@
         <v>45491</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -53645,7 +53645,7 @@
         <v>44812</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -53718,7 +53718,7 @@
         <v>44794</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -53791,7 +53791,7 @@
         <v>44643</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -53864,7 +53864,7 @@
         <v>45299</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -53937,7 +53937,7 @@
         <v>45049</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -54010,7 +54010,7 @@
         <v>45048</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -54083,7 +54083,7 @@
         <v>45774</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -54156,7 +54156,7 @@
         <v>44859</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -54234,7 +54234,7 @@
         <v>45275</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -54312,7 +54312,7 @@
         <v>45671</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -54385,7 +54385,7 @@
         <v>45779</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -54458,7 +54458,7 @@
         <v>45779</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -54531,7 +54531,7 @@
         <v>45785</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -54604,7 +54604,7 @@
         <v>45359</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -54677,7 +54677,7 @@
         <v>45342</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -54750,7 +54750,7 @@
         <v>45573</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -54823,7 +54823,7 @@
         <v>45541</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -54896,7 +54896,7 @@
         <v>44855</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -54969,7 +54969,7 @@
         <v>45133</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -55042,7 +55042,7 @@
         <v>45541</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -55115,7 +55115,7 @@
         <v>45699</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -55188,7 +55188,7 @@
         <v>46040</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -55261,7 +55261,7 @@
         <v>46108</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -55334,7 +55334,7 @@
         <v>46183</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>

--- a/Översikt LINKÖPING.xlsx
+++ b/Översikt LINKÖPING.xlsx
@@ -601,7 +601,7 @@
         <v>45756</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -741,7 +741,7 @@
         <v>45644</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>44679</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>46090</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>45293</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>44855</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
         <v>45278</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1505,7 +1505,7 @@
         <v>46275</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1634,7 +1634,7 @@
         <v>44368</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1750,7 +1750,7 @@
         <v>46090</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1863,7 +1863,7 @@
         <v>45720</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1975,7 +1975,7 @@
         <v>45720</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         <v>46055</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2207,7 +2207,7 @@
         <v>45860</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2318,7 +2318,7 @@
         <v>45804</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2433,7 +2433,7 @@
         <v>46206</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2552,7 +2552,7 @@
         <v>45280</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2668,7 +2668,7 @@
         <v>46090</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2778,7 +2778,7 @@
         <v>45756</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2892,7 +2892,7 @@
         <v>46275</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3010,7 +3010,7 @@
         <v>45068</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
         <v>46146</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3233,7 +3233,7 @@
         <v>44949</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
         <v>44588</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3455,7 +3455,7 @@
         <v>44679</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3569,7 +3569,7 @@
         <v>43997</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3678,7 +3678,7 @@
         <v>44679</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3795,7 +3795,7 @@
         <v>44745</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3903,7 +3903,7 @@
         <v>46050</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4011,7 +4011,7 @@
         <v>45714</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4124,7 +4124,7 @@
         <v>45943</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4232,7 +4232,7 @@
         <v>46079</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4340,7 +4340,7 @@
         <v>46107</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4457,7 +4457,7 @@
         <v>45932</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4570,7 +4570,7 @@
         <v>44479</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4683,7 +4683,7 @@
         <v>45555</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4796,7 +4796,7 @@
         <v>45089</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4904,7 +4904,7 @@
         <v>44834</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5012,7 +5012,7 @@
         <v>44679</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5124,7 +5124,7 @@
         <v>44679</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5236,7 +5236,7 @@
         <v>44479</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5348,7 +5348,7 @@
         <v>44855</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5459,7 +5459,7 @@
         <v>44930</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5575,7 +5575,7 @@
         <v>45664</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5682,7 +5682,7 @@
         <v>45153</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5794,7 +5794,7 @@
         <v>45941</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5905,7 +5905,7 @@
         <v>46087</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6016,7 +6016,7 @@
         <v>44830</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6123,7 +6123,7 @@
         <v>45989</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6230,7 +6230,7 @@
         <v>44916</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6342,7 +6342,7 @@
         <v>45774</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6453,7 +6453,7 @@
         <v>46146</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6564,7 +6564,7 @@
         <v>45236</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6675,7 +6675,7 @@
         <v>45294</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6782,7 +6782,7 @@
         <v>46206</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6889,7 +6889,7 @@
         <v>46289</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7009,7 +7009,7 @@
         <v>45163</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7116,7 +7116,7 @@
         <v>45217</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7228,7 +7228,7 @@
         <v>45621</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7335,7 +7335,7 @@
         <v>44848</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7441,7 +7441,7 @@
         <v>44498</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7551,7 +7551,7 @@
         <v>45191</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7662,7 +7662,7 @@
         <v>45216</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7768,7 +7768,7 @@
         <v>44909</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7878,7 +7878,7 @@
         <v>46043</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7993,7 +7993,7 @@
         <v>45572</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8099,7 +8099,7 @@
         <v>45071</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8210,7 +8210,7 @@
         <v>45712</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8321,7 +8321,7 @@
         <v>44597</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8427,7 +8427,7 @@
         <v>44936</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8533,7 +8533,7 @@
         <v>45639</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8639,7 +8639,7 @@
         <v>44487</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8750,7 +8750,7 @@
         <v>45804</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8856,7 +8856,7 @@
         <v>45745</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8966,7 +8966,7 @@
         <v>45932</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9077,7 +9077,7 @@
         <v>45461</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9183,7 +9183,7 @@
         <v>45140</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9293,7 +9293,7 @@
         <v>45595</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9399,7 +9399,7 @@
         <v>45554</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9514,7 +9514,7 @@
         <v>46107</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9625,7 +9625,7 @@
         <v>46153</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9731,7 +9731,7 @@
         <v>45547</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9841,7 +9841,7 @@
         <v>44487</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9952,7 +9952,7 @@
         <v>45774</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10058,7 +10058,7 @@
         <v>46259</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10169,7 +10169,7 @@
         <v>45244</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10280,7 +10280,7 @@
         <v>44930</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10391,7 +10391,7 @@
         <v>46178</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10497,7 +10497,7 @@
         <v>45176</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10603,7 +10603,7 @@
         <v>45148</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10709,7 +10709,7 @@
         <v>45621</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10815,7 +10815,7 @@
         <v>45774</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10925,7 +10925,7 @@
         <v>44159</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11036,7 +11036,7 @@
         <v>44537</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11146,7 +11146,7 @@
         <v>45665</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11256,7 +11256,7 @@
         <v>44938</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11361,7 +11361,7 @@
         <v>45176</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11466,7 +11466,7 @@
         <v>45369</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11571,7 +11571,7 @@
         <v>44768</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11676,7 +11676,7 @@
         <v>45141</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11781,7 +11781,7 @@
         <v>45915</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11891,7 +11891,7 @@
         <v>45463</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11996,7 +11996,7 @@
         <v>45541</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12101,7 +12101,7 @@
         <v>45222</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12215,7 +12215,7 @@
         <v>45941</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12320,7 +12320,7 @@
         <v>46079</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12425,7 +12425,7 @@
         <v>45812</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12530,7 +12530,7 @@
         <v>45243</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12640,7 +12640,7 @@
         <v>45816</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12745,7 +12745,7 @@
         <v>45968</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12850,7 +12850,7 @@
         <v>45604</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12960,7 +12960,7 @@
         <v>45988</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13070,7 +13070,7 @@
         <v>44929</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13175,7 +13175,7 @@
         <v>45554</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13285,7 +13285,7 @@
         <v>45994</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13390,7 +13390,7 @@
         <v>45153</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13500,7 +13500,7 @@
         <v>45579</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13605,7 +13605,7 @@
         <v>45244</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13715,7 +13715,7 @@
         <v>45965</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13825,7 +13825,7 @@
         <v>45246</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13935,7 +13935,7 @@
         <v>44889</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14040,7 +14040,7 @@
         <v>45604</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14150,7 +14150,7 @@
         <v>46175</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14255,7 +14255,7 @@
         <v>45071</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14365,7 +14365,7 @@
         <v>46259</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14475,7 +14475,7 @@
         <v>45308</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14585,7 +14585,7 @@
         <v>46264</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14690,7 +14690,7 @@
         <v>45442</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14799,7 +14799,7 @@
         <v>44945</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14904,7 +14904,7 @@
         <v>45412</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -15009,7 +15009,7 @@
         <v>45244</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -15119,7 +15119,7 @@
         <v>46206</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15224,7 +15224,7 @@
         <v>44945</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15329,7 +15329,7 @@
         <v>44881</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15434,7 +15434,7 @@
         <v>46289</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15544,7 +15544,7 @@
         <v>45460</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -15649,7 +15649,7 @@
         <v>44950</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -15754,7 +15754,7 @@
         <v>45294</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -15864,7 +15864,7 @@
         <v>45266</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -15969,7 +15969,7 @@
         <v>45111</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -16074,7 +16074,7 @@
         <v>44949</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -16179,7 +16179,7 @@
         <v>45491</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -16284,7 +16284,7 @@
         <v>44496</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -16394,7 +16394,7 @@
         <v>44478</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -16472,7 +16472,7 @@
         <v>44523</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -16545,7 +16545,7 @@
         <v>44608</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -16618,7 +16618,7 @@
         <v>44510</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -16691,7 +16691,7 @@
         <v>44488</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -16764,7 +16764,7 @@
         <v>44764</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -16837,7 +16837,7 @@
         <v>44855</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -16915,7 +16915,7 @@
         <v>44846</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -16988,7 +16988,7 @@
         <v>44573</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -17061,7 +17061,7 @@
         <v>44496</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -17134,7 +17134,7 @@
         <v>44853</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -17207,7 +17207,7 @@
         <v>44782</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -17280,7 +17280,7 @@
         <v>44679</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -17358,7 +17358,7 @@
         <v>44777</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -17431,7 +17431,7 @@
         <v>44753</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -17509,7 +17509,7 @@
         <v>44510</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -17582,7 +17582,7 @@
         <v>44487</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -17660,7 +17660,7 @@
         <v>44487</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -17738,7 +17738,7 @@
         <v>44823</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -17811,7 +17811,7 @@
         <v>44515</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -17889,7 +17889,7 @@
         <v>44767</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -17962,7 +17962,7 @@
         <v>44719</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -18040,7 +18040,7 @@
         <v>44487</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -18118,7 +18118,7 @@
         <v>44776</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -18191,7 +18191,7 @@
         <v>44692</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -18264,7 +18264,7 @@
         <v>44882</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -18342,7 +18342,7 @@
         <v>44803</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -18415,7 +18415,7 @@
         <v>44588</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -18488,7 +18488,7 @@
         <v>44743</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -18561,7 +18561,7 @@
         <v>44574</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -18634,7 +18634,7 @@
         <v>44571</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -18707,7 +18707,7 @@
         <v>44841</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -18780,7 +18780,7 @@
         <v>44537</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -18853,7 +18853,7 @@
         <v>44809</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -18926,7 +18926,7 @@
         <v>44884</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -18999,7 +18999,7 @@
         <v>44884</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -19072,7 +19072,7 @@
         <v>44628</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -19145,7 +19145,7 @@
         <v>44525</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -19218,7 +19218,7 @@
         <v>44525</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -19291,7 +19291,7 @@
         <v>44627</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -19364,7 +19364,7 @@
         <v>44785</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -19437,7 +19437,7 @@
         <v>44643</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -19510,7 +19510,7 @@
         <v>44720</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -19583,7 +19583,7 @@
         <v>44595</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -19661,7 +19661,7 @@
         <v>44481</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -19734,7 +19734,7 @@
         <v>44743</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -19807,7 +19807,7 @@
         <v>44497</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -19880,7 +19880,7 @@
         <v>44848</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -19953,7 +19953,7 @@
         <v>44776</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -20026,7 +20026,7 @@
         <v>44826</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -20099,7 +20099,7 @@
         <v>44791</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -20172,7 +20172,7 @@
         <v>44498</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -20245,7 +20245,7 @@
         <v>44638</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -20318,7 +20318,7 @@
         <v>44796</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -20396,7 +20396,7 @@
         <v>44812</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -20469,7 +20469,7 @@
         <v>44794</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -20542,7 +20542,7 @@
         <v>45274</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -20615,7 +20615,7 @@
         <v>44945</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -20688,7 +20688,7 @@
         <v>45728</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -20761,7 +20761,7 @@
         <v>45477</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -20839,7 +20839,7 @@
         <v>45236</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -20917,7 +20917,7 @@
         <v>44767</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -20990,7 +20990,7 @@
         <v>45435</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -21063,7 +21063,7 @@
         <v>45294</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -21136,7 +21136,7 @@
         <v>45457</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -21209,7 +21209,7 @@
         <v>45089</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -21287,7 +21287,7 @@
         <v>45140</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -21360,7 +21360,7 @@
         <v>44767</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -21433,7 +21433,7 @@
         <v>44897</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -21511,7 +21511,7 @@
         <v>44939</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -21584,7 +21584,7 @@
         <v>45217</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -21657,7 +21657,7 @@
         <v>45217</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -21730,7 +21730,7 @@
         <v>45142</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -21803,7 +21803,7 @@
         <v>45302</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -21876,7 +21876,7 @@
         <v>45225</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -21954,7 +21954,7 @@
         <v>45182</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -22027,7 +22027,7 @@
         <v>45238</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -22100,7 +22100,7 @@
         <v>45225</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -22173,7 +22173,7 @@
         <v>45225</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -22246,7 +22246,7 @@
         <v>45623</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -22319,7 +22319,7 @@
         <v>45664</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -22392,7 +22392,7 @@
         <v>45546</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -22465,7 +22465,7 @@
         <v>44498</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -22538,7 +22538,7 @@
         <v>44498</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -22611,7 +22611,7 @@
         <v>45275</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -22684,7 +22684,7 @@
         <v>45246</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -22757,7 +22757,7 @@
         <v>45133</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -22830,7 +22830,7 @@
         <v>45545</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -22903,7 +22903,7 @@
         <v>45483</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -22976,7 +22976,7 @@
         <v>44903</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -23049,7 +23049,7 @@
         <v>44945</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -23122,7 +23122,7 @@
         <v>46010</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -23195,7 +23195,7 @@
         <v>45030</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -23268,7 +23268,7 @@
         <v>44909</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -23341,7 +23341,7 @@
         <v>44909</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -23414,7 +23414,7 @@
         <v>44930</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -23492,7 +23492,7 @@
         <v>45161</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -23565,7 +23565,7 @@
         <v>46030</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -23638,7 +23638,7 @@
         <v>46030</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -23711,7 +23711,7 @@
         <v>46030</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -23784,7 +23784,7 @@
         <v>46030</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -23862,7 +23862,7 @@
         <v>46030</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -23940,7 +23940,7 @@
         <v>46030</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -24013,7 +24013,7 @@
         <v>46030</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -24086,7 +24086,7 @@
         <v>45309</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -24159,7 +24159,7 @@
         <v>46035</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -24232,7 +24232,7 @@
         <v>45901</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -24305,7 +24305,7 @@
         <v>45111</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -24378,7 +24378,7 @@
         <v>45793</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -24451,7 +24451,7 @@
         <v>46035</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -24524,7 +24524,7 @@
         <v>45160</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -24597,7 +24597,7 @@
         <v>45755</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -24670,7 +24670,7 @@
         <v>46038</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -24743,7 +24743,7 @@
         <v>45593</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -24816,7 +24816,7 @@
         <v>45624</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -24889,7 +24889,7 @@
         <v>45915</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -24962,7 +24962,7 @@
         <v>45912</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -25040,7 +25040,7 @@
         <v>45912</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -25118,7 +25118,7 @@
         <v>45912</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -25196,7 +25196,7 @@
         <v>45737</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -25269,7 +25269,7 @@
         <v>45111</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -25342,7 +25342,7 @@
         <v>45573</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -25415,7 +25415,7 @@
         <v>45294</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -25488,7 +25488,7 @@
         <v>45919</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -25561,7 +25561,7 @@
         <v>45804</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -25634,7 +25634,7 @@
         <v>45491</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -25707,7 +25707,7 @@
         <v>45922</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -25785,7 +25785,7 @@
         <v>44894</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -25858,7 +25858,7 @@
         <v>46055</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -25931,7 +25931,7 @@
         <v>46055</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -26004,7 +26004,7 @@
         <v>45928</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -26077,7 +26077,7 @@
         <v>45930</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -26150,7 +26150,7 @@
         <v>45678</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -26223,7 +26223,7 @@
         <v>45932</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -26301,7 +26301,7 @@
         <v>45750</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -26374,7 +26374,7 @@
         <v>44683</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -26447,7 +26447,7 @@
         <v>45274</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -26520,7 +26520,7 @@
         <v>45146</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -26598,7 +26598,7 @@
         <v>45941</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -26671,7 +26671,7 @@
         <v>45945</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -26744,7 +26744,7 @@
         <v>44888</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -26817,7 +26817,7 @@
         <v>45275</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -26890,7 +26890,7 @@
         <v>44487</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -26968,7 +26968,7 @@
         <v>46077</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -27041,7 +27041,7 @@
         <v>46079</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -27114,7 +27114,7 @@
         <v>45623</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -27187,7 +27187,7 @@
         <v>45623</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -27260,7 +27260,7 @@
         <v>44949</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -27333,7 +27333,7 @@
         <v>45456</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -27406,7 +27406,7 @@
         <v>45952</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -27479,7 +27479,7 @@
         <v>45957</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -27552,7 +27552,7 @@
         <v>45957</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -27625,7 +27625,7 @@
         <v>45957</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -27698,7 +27698,7 @@
         <v>46087</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -27771,7 +27771,7 @@
         <v>45013</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -27844,7 +27844,7 @@
         <v>44558</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -27917,7 +27917,7 @@
         <v>44743</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -27990,7 +27990,7 @@
         <v>45230</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -28063,7 +28063,7 @@
         <v>45816</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -28136,7 +28136,7 @@
         <v>45125</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -28209,7 +28209,7 @@
         <v>45610</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -28282,7 +28282,7 @@
         <v>46098</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -28355,7 +28355,7 @@
         <v>45968</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -28428,7 +28428,7 @@
         <v>45968</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -28501,7 +28501,7 @@
         <v>45968</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -28574,7 +28574,7 @@
         <v>46094</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -28647,7 +28647,7 @@
         <v>44865</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -28720,7 +28720,7 @@
         <v>46099</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -28798,7 +28798,7 @@
         <v>45359</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -28871,7 +28871,7 @@
         <v>45973</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -28944,7 +28944,7 @@
         <v>45973</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -29017,7 +29017,7 @@
         <v>45208</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -29090,7 +29090,7 @@
         <v>45147</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -29163,7 +29163,7 @@
         <v>45977</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -29241,7 +29241,7 @@
         <v>44600</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -29314,7 +29314,7 @@
         <v>45202</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -29387,7 +29387,7 @@
         <v>45729</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -29460,7 +29460,7 @@
         <v>45021</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -29533,7 +29533,7 @@
         <v>45821</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -29606,7 +29606,7 @@
         <v>45281</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -29684,7 +29684,7 @@
         <v>44783</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -29757,7 +29757,7 @@
         <v>45989</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -29830,7 +29830,7 @@
         <v>46120</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -29903,7 +29903,7 @@
         <v>44928</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -29976,7 +29976,7 @@
         <v>44933</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -30049,7 +30049,7 @@
         <v>44768</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -30122,7 +30122,7 @@
         <v>44909</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -30195,7 +30195,7 @@
         <v>44862</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -30268,7 +30268,7 @@
         <v>44889</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -30346,7 +30346,7 @@
         <v>45203</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -30419,7 +30419,7 @@
         <v>45996</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -30497,7 +30497,7 @@
         <v>44665</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -30575,7 +30575,7 @@
         <v>44860</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -30648,7 +30648,7 @@
         <v>46000</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -30726,7 +30726,7 @@
         <v>45774</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -30799,7 +30799,7 @@
         <v>44795</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -30872,7 +30872,7 @@
         <v>44933</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -30945,7 +30945,7 @@
         <v>44942</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -31018,7 +31018,7 @@
         <v>45293</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -31091,7 +31091,7 @@
         <v>45195</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -31164,7 +31164,7 @@
         <v>45111</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -31237,7 +31237,7 @@
         <v>45555</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -31315,7 +31315,7 @@
         <v>46134</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -31388,7 +31388,7 @@
         <v>45774</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -31461,7 +31461,7 @@
         <v>45082</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -31534,7 +31534,7 @@
         <v>45082</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -31607,7 +31607,7 @@
         <v>45967</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -31680,7 +31680,7 @@
         <v>46086</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -31753,7 +31753,7 @@
         <v>45590</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -31826,7 +31826,7 @@
         <v>46086</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -31899,7 +31899,7 @@
         <v>45244</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -31977,7 +31977,7 @@
         <v>44936</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -32050,7 +32050,7 @@
         <v>44931</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -32123,7 +32123,7 @@
         <v>45938</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -32201,7 +32201,7 @@
         <v>46008</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -32274,7 +32274,7 @@
         <v>45678</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -32347,7 +32347,7 @@
         <v>44623</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -32420,7 +32420,7 @@
         <v>45111</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -32498,7 +32498,7 @@
         <v>44923</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -32576,7 +32576,7 @@
         <v>45614</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -32649,7 +32649,7 @@
         <v>45489</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -32722,7 +32722,7 @@
         <v>45655</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -32795,7 +32795,7 @@
         <v>45712</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -32868,7 +32868,7 @@
         <v>46099</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -32941,7 +32941,7 @@
         <v>45106</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -33014,7 +33014,7 @@
         <v>45106</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -33087,7 +33087,7 @@
         <v>45296</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -33160,7 +33160,7 @@
         <v>45069</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -33233,7 +33233,7 @@
         <v>44501</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -33306,7 +33306,7 @@
         <v>45392</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -33379,7 +33379,7 @@
         <v>45555</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -33457,7 +33457,7 @@
         <v>45644</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -33530,7 +33530,7 @@
         <v>45852</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -33603,7 +33603,7 @@
         <v>44944</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -33676,7 +33676,7 @@
         <v>45261</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -33749,7 +33749,7 @@
         <v>45237</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -33822,7 +33822,7 @@
         <v>45140</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -33895,7 +33895,7 @@
         <v>45905</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -33968,7 +33968,7 @@
         <v>44803</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -34041,7 +34041,7 @@
         <v>46086</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -34114,7 +34114,7 @@
         <v>46057</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -34187,7 +34187,7 @@
         <v>45086</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -34260,7 +34260,7 @@
         <v>45860</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -34333,7 +34333,7 @@
         <v>45860</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -34406,7 +34406,7 @@
         <v>44987</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -34479,7 +34479,7 @@
         <v>45121</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -34552,7 +34552,7 @@
         <v>44565</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -34625,7 +34625,7 @@
         <v>44690</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -34698,7 +34698,7 @@
         <v>44768</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -34771,7 +34771,7 @@
         <v>44888</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -34844,7 +34844,7 @@
         <v>44986</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -34917,7 +34917,7 @@
         <v>44498</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -34990,7 +34990,7 @@
         <v>44967</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -35068,7 +35068,7 @@
         <v>45177</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -35141,7 +35141,7 @@
         <v>45116</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -35214,7 +35214,7 @@
         <v>46147</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -35292,7 +35292,7 @@
         <v>45146</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -35370,7 +35370,7 @@
         <v>46147</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -35448,7 +35448,7 @@
         <v>45153</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -35526,7 +35526,7 @@
         <v>46145</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -35599,7 +35599,7 @@
         <v>45230</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -35672,7 +35672,7 @@
         <v>45306</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -35745,7 +35745,7 @@
         <v>44862</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -35818,7 +35818,7 @@
         <v>45470</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -35896,7 +35896,7 @@
         <v>44911</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -35969,7 +35969,7 @@
         <v>45105</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -36047,7 +36047,7 @@
         <v>45187</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -36125,7 +36125,7 @@
         <v>46153</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -36198,7 +36198,7 @@
         <v>44930</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -36276,7 +36276,7 @@
         <v>44994</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -36349,7 +36349,7 @@
         <v>46154</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -36427,7 +36427,7 @@
         <v>45044</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -36500,7 +36500,7 @@
         <v>46154</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -36578,7 +36578,7 @@
         <v>46154</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -36656,7 +36656,7 @@
         <v>45300</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -36734,7 +36734,7 @@
         <v>44475</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -36807,7 +36807,7 @@
         <v>46154</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -36885,7 +36885,7 @@
         <v>46154</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -36963,7 +36963,7 @@
         <v>46154</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -37041,7 +37041,7 @@
         <v>45392</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -37119,7 +37119,7 @@
         <v>45655</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -37192,7 +37192,7 @@
         <v>45086</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -37265,7 +37265,7 @@
         <v>44483</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -37338,7 +37338,7 @@
         <v>45755</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -37411,7 +37411,7 @@
         <v>45737</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -37484,7 +37484,7 @@
         <v>45755</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -37557,7 +37557,7 @@
         <v>45755</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -37630,7 +37630,7 @@
         <v>45729</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -37708,7 +37708,7 @@
         <v>45379</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -37781,7 +37781,7 @@
         <v>45774</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -37854,7 +37854,7 @@
         <v>45117</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -37927,7 +37927,7 @@
         <v>45833</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -38000,7 +38000,7 @@
         <v>45374</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -38073,7 +38073,7 @@
         <v>44498</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -38146,7 +38146,7 @@
         <v>45337</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -38219,7 +38219,7 @@
         <v>45294</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -38297,7 +38297,7 @@
         <v>45625</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -38370,7 +38370,7 @@
         <v>44993</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -38443,7 +38443,7 @@
         <v>44508</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -38516,7 +38516,7 @@
         <v>45741</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -38589,7 +38589,7 @@
         <v>45320</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -38662,7 +38662,7 @@
         <v>45266</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -38740,7 +38740,7 @@
         <v>45695</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -38813,7 +38813,7 @@
         <v>45231</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -38886,7 +38886,7 @@
         <v>44949</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -38959,7 +38959,7 @@
         <v>44882</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -39032,7 +39032,7 @@
         <v>44882</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -39105,7 +39105,7 @@
         <v>45804</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -39178,7 +39178,7 @@
         <v>44930</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -39256,7 +39256,7 @@
         <v>45268</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -39329,7 +39329,7 @@
         <v>45005</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -39402,7 +39402,7 @@
         <v>44498</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -39475,7 +39475,7 @@
         <v>45092</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -39548,7 +39548,7 @@
         <v>44509</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -39626,7 +39626,7 @@
         <v>44475</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -39699,7 +39699,7 @@
         <v>46181</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -39772,7 +39772,7 @@
         <v>46181</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -39845,7 +39845,7 @@
         <v>45275</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -39918,7 +39918,7 @@
         <v>45275</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -39996,7 +39996,7 @@
         <v>45275</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -40074,7 +40074,7 @@
         <v>45411</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -40147,7 +40147,7 @@
         <v>46085</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -40220,7 +40220,7 @@
         <v>44658</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -40293,7 +40293,7 @@
         <v>45217</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -40366,7 +40366,7 @@
         <v>44873</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -40444,7 +40444,7 @@
         <v>45096</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -40522,7 +40522,7 @@
         <v>45741</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -40595,7 +40595,7 @@
         <v>44775</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -40668,7 +40668,7 @@
         <v>45655</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -40741,7 +40741,7 @@
         <v>45037</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -40819,7 +40819,7 @@
         <v>45271</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -40892,7 +40892,7 @@
         <v>46199</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -40965,7 +40965,7 @@
         <v>45177</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -41038,7 +41038,7 @@
         <v>46203</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -41111,7 +41111,7 @@
         <v>46154</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -41189,7 +41189,7 @@
         <v>45161</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -41262,7 +41262,7 @@
         <v>44958</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -41335,7 +41335,7 @@
         <v>44936</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -41408,7 +41408,7 @@
         <v>46206</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -41481,7 +41481,7 @@
         <v>46205</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -41554,7 +41554,7 @@
         <v>46206</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -41627,7 +41627,7 @@
         <v>46206</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -41700,7 +41700,7 @@
         <v>44638</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -41773,7 +41773,7 @@
         <v>46206</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -41846,7 +41846,7 @@
         <v>46206</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -41919,7 +41919,7 @@
         <v>46206</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -41992,7 +41992,7 @@
         <v>46206</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -42065,7 +42065,7 @@
         <v>46206</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -42138,7 +42138,7 @@
         <v>46206</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -42211,7 +42211,7 @@
         <v>45453</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -42284,7 +42284,7 @@
         <v>45293</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -42357,7 +42357,7 @@
         <v>44599</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -42430,7 +42430,7 @@
         <v>44776</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -42503,7 +42503,7 @@
         <v>45245</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -42581,7 +42581,7 @@
         <v>46259</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -42659,7 +42659,7 @@
         <v>46259</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -42737,7 +42737,7 @@
         <v>44970</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -42815,7 +42815,7 @@
         <v>45120</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -42888,7 +42888,7 @@
         <v>44608</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -42966,7 +42966,7 @@
         <v>45475</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -43039,7 +43039,7 @@
         <v>44824</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -43112,7 +43112,7 @@
         <v>45604</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -43190,7 +43190,7 @@
         <v>44865</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -43268,7 +43268,7 @@
         <v>45268</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -43341,7 +43341,7 @@
         <v>46265</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -43414,7 +43414,7 @@
         <v>45106</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -43487,7 +43487,7 @@
         <v>46265</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -43560,7 +43560,7 @@
         <v>46147</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -43638,7 +43638,7 @@
         <v>46267</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -43716,7 +43716,7 @@
         <v>46264</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -43789,7 +43789,7 @@
         <v>45090</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -43862,7 +43862,7 @@
         <v>44937</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -43935,7 +43935,7 @@
         <v>45111</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -44013,7 +44013,7 @@
         <v>46266</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -44086,7 +44086,7 @@
         <v>46266</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -44159,7 +44159,7 @@
         <v>44994</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -44232,7 +44232,7 @@
         <v>44945</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -44305,7 +44305,7 @@
         <v>46267</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -44383,7 +44383,7 @@
         <v>45596</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -44456,7 +44456,7 @@
         <v>46267</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -44534,7 +44534,7 @@
         <v>46267</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -44612,7 +44612,7 @@
         <v>46267</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -44690,7 +44690,7 @@
         <v>45077</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -44763,7 +44763,7 @@
         <v>46269</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -44841,7 +44841,7 @@
         <v>46269</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -44919,7 +44919,7 @@
         <v>46269</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -44997,7 +44997,7 @@
         <v>46269</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -45075,7 +45075,7 @@
         <v>46269</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -45153,7 +45153,7 @@
         <v>46269</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -45231,7 +45231,7 @@
         <v>45579</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -45304,7 +45304,7 @@
         <v>46269</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -45382,7 +45382,7 @@
         <v>46272</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -45460,7 +45460,7 @@
         <v>46272</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -45538,7 +45538,7 @@
         <v>46272</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -45616,7 +45616,7 @@
         <v>44966</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -45689,7 +45689,7 @@
         <v>46275</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -45762,7 +45762,7 @@
         <v>46274</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -45840,7 +45840,7 @@
         <v>45147</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -45913,7 +45913,7 @@
         <v>46275</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -45986,7 +45986,7 @@
         <v>46275</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -46059,7 +46059,7 @@
         <v>46272</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -46137,7 +46137,7 @@
         <v>46272</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -46215,7 +46215,7 @@
         <v>46279</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -46288,7 +46288,7 @@
         <v>45579</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -46361,7 +46361,7 @@
         <v>45155</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -46434,7 +46434,7 @@
         <v>45231</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -46507,7 +46507,7 @@
         <v>45230</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -46580,7 +46580,7 @@
         <v>45231</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -46653,7 +46653,7 @@
         <v>44509</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -46731,7 +46731,7 @@
         <v>45341</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -46804,7 +46804,7 @@
         <v>46239</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -46877,7 +46877,7 @@
         <v>45483</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -46950,7 +46950,7 @@
         <v>46239</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -47023,7 +47023,7 @@
         <v>46240</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -47101,7 +47101,7 @@
         <v>45229</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -47174,7 +47174,7 @@
         <v>44740</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -47247,7 +47247,7 @@
         <v>45082</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -47320,7 +47320,7 @@
         <v>45655</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -47393,7 +47393,7 @@
         <v>46272</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -47471,7 +47471,7 @@
         <v>44988</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -47549,7 +47549,7 @@
         <v>45568</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -47622,7 +47622,7 @@
         <v>45568</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -47695,7 +47695,7 @@
         <v>45485</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -47768,7 +47768,7 @@
         <v>45579</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -47841,7 +47841,7 @@
         <v>45748</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -47914,7 +47914,7 @@
         <v>45492</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -47987,7 +47987,7 @@
         <v>45230</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -48060,7 +48060,7 @@
         <v>46245</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -48133,7 +48133,7 @@
         <v>46289</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -48211,7 +48211,7 @@
         <v>46289</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -48289,7 +48289,7 @@
         <v>44475</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -48362,7 +48362,7 @@
         <v>46288</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -48435,7 +48435,7 @@
         <v>44986</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -48508,7 +48508,7 @@
         <v>44953</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -48581,7 +48581,7 @@
         <v>46288</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -48654,7 +48654,7 @@
         <v>46289</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -48732,7 +48732,7 @@
         <v>45092</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -48805,7 +48805,7 @@
         <v>46288</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -48878,7 +48878,7 @@
         <v>46245</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -48951,7 +48951,7 @@
         <v>45142</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -49024,7 +49024,7 @@
         <v>45300</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -49102,7 +49102,7 @@
         <v>44509</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -49175,7 +49175,7 @@
         <v>46288</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -49248,7 +49248,7 @@
         <v>45152</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -49321,7 +49321,7 @@
         <v>45209</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -49394,7 +49394,7 @@
         <v>46248</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -49472,7 +49472,7 @@
         <v>46248</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -49550,7 +49550,7 @@
         <v>46248</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -49628,7 +49628,7 @@
         <v>46275</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -49701,7 +49701,7 @@
         <v>46248</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -49779,7 +49779,7 @@
         <v>46290</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -49852,7 +49852,7 @@
         <v>46290</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -49925,7 +49925,7 @@
         <v>44858</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -49998,7 +49998,7 @@
         <v>45275</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -50076,7 +50076,7 @@
         <v>45639</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -50149,7 +50149,7 @@
         <v>46248</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -50227,7 +50227,7 @@
         <v>46248</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -50305,7 +50305,7 @@
         <v>45427</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -50378,7 +50378,7 @@
         <v>44628</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -50451,7 +50451,7 @@
         <v>46294</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -50529,7 +50529,7 @@
         <v>46294</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -50607,7 +50607,7 @@
         <v>46294</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -50685,7 +50685,7 @@
         <v>46294</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -50758,7 +50758,7 @@
         <v>44986</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -50831,7 +50831,7 @@
         <v>46294</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -50909,7 +50909,7 @@
         <v>44944</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -50982,7 +50982,7 @@
         <v>45655</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -51055,7 +51055,7 @@
         <v>45655</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -51128,7 +51128,7 @@
         <v>46294</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -51206,7 +51206,7 @@
         <v>46254</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -51279,7 +51279,7 @@
         <v>45597</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -51352,7 +51352,7 @@
         <v>45219</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -51430,7 +51430,7 @@
         <v>44994</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -51503,7 +51503,7 @@
         <v>45555</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -51576,7 +51576,7 @@
         <v>45703</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -51649,7 +51649,7 @@
         <v>45205</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -51722,7 +51722,7 @@
         <v>46293</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -51795,7 +51795,7 @@
         <v>44641</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -51873,7 +51873,7 @@
         <v>45655</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -51946,7 +51946,7 @@
         <v>44767</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -52019,7 +52019,7 @@
         <v>44909</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -52092,7 +52092,7 @@
         <v>44909</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -52165,7 +52165,7 @@
         <v>45230</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -52238,7 +52238,7 @@
         <v>45265</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -52311,7 +52311,7 @@
         <v>45294</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -52384,7 +52384,7 @@
         <v>45429</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -52457,7 +52457,7 @@
         <v>45299</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -52530,7 +52530,7 @@
         <v>45491</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -52603,7 +52603,7 @@
         <v>45274</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -52676,7 +52676,7 @@
         <v>45266</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -52749,7 +52749,7 @@
         <v>45268</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -52822,7 +52822,7 @@
         <v>45300</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -52900,7 +52900,7 @@
         <v>45342</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -52973,7 +52973,7 @@
         <v>45364</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -53051,7 +53051,7 @@
         <v>45275</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -53124,7 +53124,7 @@
         <v>45275</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -53202,7 +53202,7 @@
         <v>45275</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -53275,7 +53275,7 @@
         <v>45153</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -53353,7 +53353,7 @@
         <v>45397</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -53426,7 +53426,7 @@
         <v>45404</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -53499,7 +53499,7 @@
         <v>44810</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -53572,7 +53572,7 @@
         <v>45491</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -53645,7 +53645,7 @@
         <v>44812</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -53718,7 +53718,7 @@
         <v>44794</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -53791,7 +53791,7 @@
         <v>44643</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -53864,7 +53864,7 @@
         <v>45299</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -53937,7 +53937,7 @@
         <v>45049</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -54010,7 +54010,7 @@
         <v>45048</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -54083,7 +54083,7 @@
         <v>45774</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -54156,7 +54156,7 @@
         <v>44859</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -54234,7 +54234,7 @@
         <v>45275</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -54312,7 +54312,7 @@
         <v>45671</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -54385,7 +54385,7 @@
         <v>45779</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -54458,7 +54458,7 @@
         <v>45779</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -54531,7 +54531,7 @@
         <v>45785</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -54604,7 +54604,7 @@
         <v>45359</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -54677,7 +54677,7 @@
         <v>45342</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -54750,7 +54750,7 @@
         <v>45573</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -54823,7 +54823,7 @@
         <v>45541</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -54896,7 +54896,7 @@
         <v>44855</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -54969,7 +54969,7 @@
         <v>45133</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -55042,7 +55042,7 @@
         <v>45541</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -55115,7 +55115,7 @@
         <v>45699</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -55188,7 +55188,7 @@
         <v>46040</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -55261,7 +55261,7 @@
         <v>46108</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -55334,7 +55334,7 @@
         <v>46183</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>

--- a/Översikt LINKÖPING.xlsx
+++ b/Översikt LINKÖPING.xlsx
@@ -601,7 +601,7 @@
         <v>45756</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -741,7 +741,7 @@
         <v>45644</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>44679</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>45293</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>46090</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>44855</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
         <v>45278</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1505,7 +1505,7 @@
         <v>46275</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1634,7 +1634,7 @@
         <v>44368</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1750,7 +1750,7 @@
         <v>46090</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1863,7 +1863,7 @@
         <v>45720</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1975,7 +1975,7 @@
         <v>45720</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         <v>45860</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2198,7 +2198,7 @@
         <v>45804</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2313,7 +2313,7 @@
         <v>46206</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2432,7 +2432,7 @@
         <v>45280</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2548,7 +2548,7 @@
         <v>45756</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2662,7 +2662,7 @@
         <v>46090</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2772,7 +2772,7 @@
         <v>46275</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2890,7 +2890,7 @@
         <v>44949</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2999,7 +2999,7 @@
         <v>45068</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3113,7 +3113,7 @@
         <v>44679</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3227,7 +3227,7 @@
         <v>44588</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3340,7 +3340,7 @@
         <v>46146</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3449,7 +3449,7 @@
         <v>43997</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3558,7 +3558,7 @@
         <v>44679</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3675,7 +3675,7 @@
         <v>44745</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3783,7 +3783,7 @@
         <v>45943</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3891,7 +3891,7 @@
         <v>46107</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4008,7 +4008,7 @@
         <v>45555</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4121,7 +4121,7 @@
         <v>45932</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4234,7 +4234,7 @@
         <v>46050</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4342,7 +4342,7 @@
         <v>46079</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4450,7 +4450,7 @@
         <v>44479</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4563,7 +4563,7 @@
         <v>45714</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4676,7 +4676,7 @@
         <v>45089</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4784,7 +4784,7 @@
         <v>44834</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4892,7 +4892,7 @@
         <v>44679</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5004,7 +5004,7 @@
         <v>44679</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5116,7 +5116,7 @@
         <v>44479</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5228,7 +5228,7 @@
         <v>44855</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5339,7 +5339,7 @@
         <v>45153</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5451,7 +5451,7 @@
         <v>45294</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5558,7 +5558,7 @@
         <v>45236</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5669,7 +5669,7 @@
         <v>44930</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5785,7 +5785,7 @@
         <v>45163</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5892,7 +5892,7 @@
         <v>45664</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
         <v>44830</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6106,7 +6106,7 @@
         <v>45217</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6218,7 +6218,7 @@
         <v>45941</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6329,7 +6329,7 @@
         <v>44916</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6441,7 +6441,7 @@
         <v>45774</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6552,7 +6552,7 @@
         <v>45621</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6659,7 +6659,7 @@
         <v>46146</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6770,7 +6770,7 @@
         <v>46087</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6881,7 +6881,7 @@
         <v>46206</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6988,7 +6988,7 @@
         <v>46289</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7108,7 +7108,7 @@
         <v>44848</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7214,7 +7214,7 @@
         <v>44498</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7324,7 +7324,7 @@
         <v>45595</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7430,7 +7430,7 @@
         <v>44930</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7541,7 +7541,7 @@
         <v>45774</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7647,7 +7647,7 @@
         <v>44487</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7758,7 +7758,7 @@
         <v>44487</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7869,7 +7869,7 @@
         <v>45216</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7975,7 +7975,7 @@
         <v>45140</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8085,7 +8085,7 @@
         <v>45572</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8191,7 +8191,7 @@
         <v>45191</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8302,7 +8302,7 @@
         <v>45774</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8412,7 +8412,7 @@
         <v>45148</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8518,7 +8518,7 @@
         <v>45244</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8629,7 +8629,7 @@
         <v>44936</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8735,7 +8735,7 @@
         <v>45071</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8846,7 +8846,7 @@
         <v>44909</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8956,7 +8956,7 @@
         <v>45804</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9062,7 +9062,7 @@
         <v>45176</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9168,7 +9168,7 @@
         <v>44597</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9274,7 +9274,7 @@
         <v>45712</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9385,7 +9385,7 @@
         <v>45554</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9500,7 +9500,7 @@
         <v>45639</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9606,7 +9606,7 @@
         <v>45745</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9716,7 +9716,7 @@
         <v>45461</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9822,7 +9822,7 @@
         <v>45932</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9933,7 +9933,7 @@
         <v>46043</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10048,7 +10048,7 @@
         <v>45621</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10154,7 +10154,7 @@
         <v>46107</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10265,7 +10265,7 @@
         <v>46153</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10371,7 +10371,7 @@
         <v>45547</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10481,7 +10481,7 @@
         <v>46178</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10587,7 +10587,7 @@
         <v>46259</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10698,7 +10698,7 @@
         <v>44159</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10809,7 +10809,7 @@
         <v>44537</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10919,7 +10919,7 @@
         <v>45412</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11024,7 +11024,7 @@
         <v>44889</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11129,7 +11129,7 @@
         <v>44938</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11234,7 +11234,7 @@
         <v>45491</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11339,7 +11339,7 @@
         <v>45222</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11453,7 +11453,7 @@
         <v>45665</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11563,7 +11563,7 @@
         <v>45308</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11673,7 +11673,7 @@
         <v>45554</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11783,7 +11783,7 @@
         <v>45460</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11888,7 +11888,7 @@
         <v>44949</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11993,7 +11993,7 @@
         <v>45442</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12102,7 +12102,7 @@
         <v>45463</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12207,7 +12207,7 @@
         <v>44929</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12312,7 +12312,7 @@
         <v>45604</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12422,7 +12422,7 @@
         <v>44881</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12527,7 +12527,7 @@
         <v>45604</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12637,7 +12637,7 @@
         <v>45915</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12747,7 +12747,7 @@
         <v>45579</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12852,7 +12852,7 @@
         <v>45369</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12957,7 +12957,7 @@
         <v>45176</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13062,7 +13062,7 @@
         <v>45541</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13167,7 +13167,7 @@
         <v>44945</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13272,7 +13272,7 @@
         <v>45812</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13377,7 +13377,7 @@
         <v>45941</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13482,7 +13482,7 @@
         <v>44950</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13587,7 +13587,7 @@
         <v>45816</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13692,7 +13692,7 @@
         <v>45244</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13802,7 +13802,7 @@
         <v>44496</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13912,7 +13912,7 @@
         <v>45243</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14022,7 +14022,7 @@
         <v>45294</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14132,7 +14132,7 @@
         <v>45141</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14237,7 +14237,7 @@
         <v>44768</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14342,7 +14342,7 @@
         <v>45968</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14447,7 +14447,7 @@
         <v>45153</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14557,7 +14557,7 @@
         <v>45266</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14662,7 +14662,7 @@
         <v>45244</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14772,7 +14772,7 @@
         <v>45111</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14877,7 +14877,7 @@
         <v>45988</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14987,7 +14987,7 @@
         <v>44945</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -15092,7 +15092,7 @@
         <v>45994</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15197,7 +15197,7 @@
         <v>45246</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15307,7 +15307,7 @@
         <v>45965</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15417,7 +15417,7 @@
         <v>45071</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15527,7 +15527,7 @@
         <v>46079</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -15632,7 +15632,7 @@
         <v>46175</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -15737,7 +15737,7 @@
         <v>46264</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -15842,7 +15842,7 @@
         <v>46206</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -15947,7 +15947,7 @@
         <v>46289</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -16057,7 +16057,7 @@
         <v>46259</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -16167,7 +16167,7 @@
         <v>46302</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -16272,7 +16272,7 @@
         <v>44523</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -16345,7 +16345,7 @@
         <v>44608</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -16418,7 +16418,7 @@
         <v>44510</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -16491,7 +16491,7 @@
         <v>44488</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -16564,7 +16564,7 @@
         <v>44764</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -16637,7 +16637,7 @@
         <v>44855</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -16715,7 +16715,7 @@
         <v>44573</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -16788,7 +16788,7 @@
         <v>44846</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -16861,7 +16861,7 @@
         <v>44496</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -16934,7 +16934,7 @@
         <v>44853</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -17007,7 +17007,7 @@
         <v>44782</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -17080,7 +17080,7 @@
         <v>44679</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -17158,7 +17158,7 @@
         <v>44777</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -17231,7 +17231,7 @@
         <v>44753</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -17309,7 +17309,7 @@
         <v>44510</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -17382,7 +17382,7 @@
         <v>44487</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -17460,7 +17460,7 @@
         <v>44487</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -17538,7 +17538,7 @@
         <v>44627</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -17611,7 +17611,7 @@
         <v>44848</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -17684,7 +17684,7 @@
         <v>44743</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -17757,7 +17757,7 @@
         <v>44785</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -17830,7 +17830,7 @@
         <v>44823</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -17903,7 +17903,7 @@
         <v>44643</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -17976,7 +17976,7 @@
         <v>44515</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -18054,7 +18054,7 @@
         <v>44574</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -18127,7 +18127,7 @@
         <v>44571</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -18200,7 +18200,7 @@
         <v>44767</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -18273,7 +18273,7 @@
         <v>44720</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -18346,7 +18346,7 @@
         <v>44595</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -18424,7 +18424,7 @@
         <v>44481</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -18497,7 +18497,7 @@
         <v>44719</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -18575,7 +18575,7 @@
         <v>44776</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -18648,7 +18648,7 @@
         <v>44743</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -18721,7 +18721,7 @@
         <v>44487</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -18799,7 +18799,7 @@
         <v>44841</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -18872,7 +18872,7 @@
         <v>44537</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -18945,7 +18945,7 @@
         <v>44809</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -19018,7 +19018,7 @@
         <v>44776</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -19091,7 +19091,7 @@
         <v>44884</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -19164,7 +19164,7 @@
         <v>44884</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -19237,7 +19237,7 @@
         <v>44692</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -19310,7 +19310,7 @@
         <v>44628</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -19383,7 +19383,7 @@
         <v>44882</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -19461,7 +19461,7 @@
         <v>44826</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -19534,7 +19534,7 @@
         <v>44803</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -19607,7 +19607,7 @@
         <v>44791</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -19680,7 +19680,7 @@
         <v>44588</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -19753,7 +19753,7 @@
         <v>44497</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -19826,7 +19826,7 @@
         <v>44498</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -19899,7 +19899,7 @@
         <v>44638</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -19972,7 +19972,7 @@
         <v>44525</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -20045,7 +20045,7 @@
         <v>44525</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -20118,7 +20118,7 @@
         <v>45579</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -20191,7 +20191,7 @@
         <v>44812</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -20264,7 +20264,7 @@
         <v>45133</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -20337,7 +20337,7 @@
         <v>45266</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -20410,7 +20410,7 @@
         <v>45302</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -20483,7 +20483,7 @@
         <v>45082</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -20556,7 +20556,7 @@
         <v>44796</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -20634,7 +20634,7 @@
         <v>45590</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -20707,7 +20707,7 @@
         <v>44498</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -20780,7 +20780,7 @@
         <v>45082</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -20853,7 +20853,7 @@
         <v>45209</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -20926,7 +20926,7 @@
         <v>44812</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -20999,7 +20999,7 @@
         <v>44882</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -21072,7 +21072,7 @@
         <v>45364</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -21150,7 +21150,7 @@
         <v>44862</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -21223,7 +21223,7 @@
         <v>45555</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -21301,7 +21301,7 @@
         <v>45374</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -21374,7 +21374,7 @@
         <v>45655</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -21447,7 +21447,7 @@
         <v>45655</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -21520,7 +21520,7 @@
         <v>45655</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -21593,7 +21593,7 @@
         <v>44928</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -21666,7 +21666,7 @@
         <v>45092</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -21739,7 +21739,7 @@
         <v>45275</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -21812,7 +21812,7 @@
         <v>45728</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -21885,7 +21885,7 @@
         <v>44909</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -21958,7 +21958,7 @@
         <v>45678</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -22031,7 +22031,7 @@
         <v>44860</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -22104,7 +22104,7 @@
         <v>45140</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -22177,7 +22177,7 @@
         <v>45491</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -22250,7 +22250,7 @@
         <v>45231</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -22323,7 +22323,7 @@
         <v>45427</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -22396,7 +22396,7 @@
         <v>44966</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -22469,7 +22469,7 @@
         <v>45568</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -22542,7 +22542,7 @@
         <v>45755</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -22615,7 +22615,7 @@
         <v>45755</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -22688,7 +22688,7 @@
         <v>45755</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -22761,7 +22761,7 @@
         <v>44794</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -22834,7 +22834,7 @@
         <v>45294</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -22912,7 +22912,7 @@
         <v>45411</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -22985,7 +22985,7 @@
         <v>45021</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -23058,7 +23058,7 @@
         <v>45491</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -23131,7 +23131,7 @@
         <v>44768</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -23204,7 +23204,7 @@
         <v>45217</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -23277,7 +23277,7 @@
         <v>45217</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -23350,7 +23350,7 @@
         <v>44501</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -23423,7 +23423,7 @@
         <v>44949</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -23496,7 +23496,7 @@
         <v>45294</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -23569,7 +23569,7 @@
         <v>45341</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -23642,7 +23642,7 @@
         <v>45429</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -23715,7 +23715,7 @@
         <v>45177</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -23788,7 +23788,7 @@
         <v>45457</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -23861,7 +23861,7 @@
         <v>45359</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -23934,7 +23934,7 @@
         <v>45268</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -24007,7 +24007,7 @@
         <v>44903</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -24080,7 +24080,7 @@
         <v>45299</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -24153,7 +24153,7 @@
         <v>44865</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -24231,7 +24231,7 @@
         <v>45275</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -24309,7 +24309,7 @@
         <v>45275</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -24387,7 +24387,7 @@
         <v>45275</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -24460,7 +24460,7 @@
         <v>44794</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -24533,7 +24533,7 @@
         <v>45230</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -24606,7 +24606,7 @@
         <v>45231</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -24679,7 +24679,7 @@
         <v>44933</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -24752,7 +24752,7 @@
         <v>44970</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -24830,7 +24830,7 @@
         <v>45579</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -24903,7 +24903,7 @@
         <v>44945</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -24976,7 +24976,7 @@
         <v>45320</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -25049,7 +25049,7 @@
         <v>44986</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -25122,7 +25122,7 @@
         <v>45623</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -25195,7 +25195,7 @@
         <v>45623</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -25268,7 +25268,7 @@
         <v>45203</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -25341,7 +25341,7 @@
         <v>44498</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -25414,7 +25414,7 @@
         <v>44509</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -25492,7 +25492,7 @@
         <v>45604</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -25570,7 +25570,7 @@
         <v>45271</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -25643,7 +25643,7 @@
         <v>44923</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -25721,7 +25721,7 @@
         <v>45748</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -25794,7 +25794,7 @@
         <v>44909</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -25867,7 +25867,7 @@
         <v>45217</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -25940,7 +25940,7 @@
         <v>45195</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -26013,7 +26013,7 @@
         <v>44953</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -26086,7 +26086,7 @@
         <v>45274</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -26159,7 +26159,7 @@
         <v>45275</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -26232,7 +26232,7 @@
         <v>45161</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -26305,7 +26305,7 @@
         <v>45293</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -26378,7 +26378,7 @@
         <v>45741</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -26451,7 +26451,7 @@
         <v>45489</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -26524,7 +26524,7 @@
         <v>45265</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -26597,7 +26597,7 @@
         <v>45337</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -26670,7 +26670,7 @@
         <v>45342</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -26743,7 +26743,7 @@
         <v>45261</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -26816,7 +26816,7 @@
         <v>45299</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -26889,7 +26889,7 @@
         <v>45296</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -26962,7 +26962,7 @@
         <v>45300</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -27040,7 +27040,7 @@
         <v>44873</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -27118,7 +27118,7 @@
         <v>45219</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -27196,7 +27196,7 @@
         <v>45230</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -27269,7 +27269,7 @@
         <v>45082</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -27342,7 +27342,7 @@
         <v>45404</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -27415,7 +27415,7 @@
         <v>45111</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -27493,7 +27493,7 @@
         <v>44558</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -27566,7 +27566,7 @@
         <v>45275</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -27639,7 +27639,7 @@
         <v>45268</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -27712,7 +27712,7 @@
         <v>45485</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -27785,7 +27785,7 @@
         <v>45294</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -27858,7 +27858,7 @@
         <v>45294</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -27931,7 +27931,7 @@
         <v>44986</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -28004,7 +28004,7 @@
         <v>44894</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -28077,7 +28077,7 @@
         <v>45655</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -28150,7 +28150,7 @@
         <v>45266</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -28228,7 +28228,7 @@
         <v>45901</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -28301,7 +28301,7 @@
         <v>45300</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -28379,7 +28379,7 @@
         <v>44936</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -28452,7 +28452,7 @@
         <v>45182</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -28525,7 +28525,7 @@
         <v>45453</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -28598,7 +28598,7 @@
         <v>44599</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -28671,7 +28671,7 @@
         <v>45695</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -28744,7 +28744,7 @@
         <v>45483</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -28817,7 +28817,7 @@
         <v>45086</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -28890,7 +28890,7 @@
         <v>45106</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -28963,7 +28963,7 @@
         <v>45106</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -29036,7 +29036,7 @@
         <v>45106</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -29109,7 +29109,7 @@
         <v>44487</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -29187,7 +29187,7 @@
         <v>45456</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -29260,7 +29260,7 @@
         <v>45655</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -29333,7 +29333,7 @@
         <v>45545</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -29406,7 +29406,7 @@
         <v>45610</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -29479,7 +29479,7 @@
         <v>44509</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -29552,7 +29552,7 @@
         <v>45208</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -29625,7 +29625,7 @@
         <v>45037</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -29703,7 +29703,7 @@
         <v>45120</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -29776,7 +29776,7 @@
         <v>45671</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -29849,7 +29849,7 @@
         <v>44945</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -29922,7 +29922,7 @@
         <v>44937</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -29995,7 +29995,7 @@
         <v>45912</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -30073,7 +30073,7 @@
         <v>44888</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -30146,7 +30146,7 @@
         <v>45779</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -30219,7 +30219,7 @@
         <v>45912</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -30297,7 +30297,7 @@
         <v>45912</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -30375,7 +30375,7 @@
         <v>45030</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -30448,7 +30448,7 @@
         <v>45915</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -30521,7 +30521,7 @@
         <v>45779</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -30594,7 +30594,7 @@
         <v>45644</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -30667,7 +30667,7 @@
         <v>45117</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -30740,7 +30740,7 @@
         <v>45750</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -30813,7 +30813,7 @@
         <v>45140</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -30886,7 +30886,7 @@
         <v>45491</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -30959,7 +30959,7 @@
         <v>45125</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -31032,7 +31032,7 @@
         <v>45678</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -31105,7 +31105,7 @@
         <v>45116</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -31178,7 +31178,7 @@
         <v>44628</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -31251,7 +31251,7 @@
         <v>45246</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -31324,7 +31324,7 @@
         <v>44897</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -31402,7 +31402,7 @@
         <v>45470</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -31480,7 +31480,7 @@
         <v>45741</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -31553,7 +31553,7 @@
         <v>45359</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -31626,7 +31626,7 @@
         <v>45919</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -31699,7 +31699,7 @@
         <v>45155</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -31772,7 +31772,7 @@
         <v>45785</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -31845,7 +31845,7 @@
         <v>44889</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -31923,7 +31923,7 @@
         <v>45555</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -32001,7 +32001,7 @@
         <v>44993</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -32074,7 +32074,7 @@
         <v>45177</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -32147,7 +32147,7 @@
         <v>45342</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -32220,7 +32220,7 @@
         <v>45922</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -32298,7 +32298,7 @@
         <v>45546</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -32371,7 +32371,7 @@
         <v>45664</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -32444,7 +32444,7 @@
         <v>45573</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -32517,7 +32517,7 @@
         <v>44783</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -32590,7 +32590,7 @@
         <v>45483</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -32663,7 +32663,7 @@
         <v>45930</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -32736,7 +32736,7 @@
         <v>45593</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -32809,7 +32809,7 @@
         <v>45928</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -32882,7 +32882,7 @@
         <v>45005</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -32955,7 +32955,7 @@
         <v>45274</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -33028,7 +33028,7 @@
         <v>45275</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -33106,7 +33106,7 @@
         <v>45275</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -33184,7 +33184,7 @@
         <v>45737</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -33257,7 +33257,7 @@
         <v>44608</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -33335,7 +33335,7 @@
         <v>45152</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -33408,7 +33408,7 @@
         <v>45793</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -33481,7 +33481,7 @@
         <v>45625</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -33554,7 +33554,7 @@
         <v>45392</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -33627,7 +33627,7 @@
         <v>45932</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -33705,7 +33705,7 @@
         <v>45397</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -33778,7 +33778,7 @@
         <v>44643</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -33851,7 +33851,7 @@
         <v>44944</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -33924,7 +33924,7 @@
         <v>45230</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -33997,7 +33997,7 @@
         <v>45202</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -34070,7 +34070,7 @@
         <v>45229</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -34143,7 +34143,7 @@
         <v>45573</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -34216,7 +34216,7 @@
         <v>45244</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -34294,7 +34294,7 @@
         <v>45555</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -34367,7 +34367,7 @@
         <v>44945</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -34440,7 +34440,7 @@
         <v>44803</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -34513,7 +34513,7 @@
         <v>45623</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -34586,7 +34586,7 @@
         <v>44859</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -34664,7 +34664,7 @@
         <v>44939</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -34737,7 +34737,7 @@
         <v>44944</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -34810,7 +34810,7 @@
         <v>44986</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -34883,7 +34883,7 @@
         <v>45804</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -34956,7 +34956,7 @@
         <v>45142</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -35029,7 +35029,7 @@
         <v>44600</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -35102,7 +35102,7 @@
         <v>44795</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -35175,7 +35175,7 @@
         <v>45225</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -35248,7 +35248,7 @@
         <v>45596</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -35321,7 +35321,7 @@
         <v>45230</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -35394,7 +35394,7 @@
         <v>44776</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -35467,7 +35467,7 @@
         <v>44942</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -35540,7 +35540,7 @@
         <v>44683</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -35613,7 +35613,7 @@
         <v>45941</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -35686,7 +35686,7 @@
         <v>45655</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -35759,7 +35759,7 @@
         <v>45945</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -35832,7 +35832,7 @@
         <v>44638</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -35905,7 +35905,7 @@
         <v>44623</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -35978,7 +35978,7 @@
         <v>44690</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -36051,7 +36051,7 @@
         <v>45703</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -36124,7 +36124,7 @@
         <v>45816</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -36197,7 +36197,7 @@
         <v>45092</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -36270,7 +36270,7 @@
         <v>45146</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -36348,7 +36348,7 @@
         <v>45111</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -36421,7 +36421,7 @@
         <v>45821</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -36494,7 +36494,7 @@
         <v>45624</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -36567,7 +36567,7 @@
         <v>44933</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -36640,7 +36640,7 @@
         <v>45089</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -36718,7 +36718,7 @@
         <v>44909</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -36791,7 +36791,7 @@
         <v>45774</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -36864,7 +36864,7 @@
         <v>44994</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -36937,7 +36937,7 @@
         <v>45952</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -37010,7 +37010,7 @@
         <v>45231</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -37083,7 +37083,7 @@
         <v>45230</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -37156,7 +37156,7 @@
         <v>45957</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -37229,7 +37229,7 @@
         <v>45957</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -37302,7 +37302,7 @@
         <v>45957</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -37375,7 +37375,7 @@
         <v>44936</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -37448,7 +37448,7 @@
         <v>44967</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -37526,7 +37526,7 @@
         <v>45160</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -37599,7 +37599,7 @@
         <v>45300</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -37677,7 +37677,7 @@
         <v>45275</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -37750,7 +37750,7 @@
         <v>45153</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -37828,7 +37828,7 @@
         <v>45096</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -37906,7 +37906,7 @@
         <v>45225</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -37984,7 +37984,7 @@
         <v>44743</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -38057,7 +38057,7 @@
         <v>45142</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -38130,7 +38130,7 @@
         <v>45968</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -38203,7 +38203,7 @@
         <v>45968</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -38276,7 +38276,7 @@
         <v>45968</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -38349,7 +38349,7 @@
         <v>45205</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -38422,7 +38422,7 @@
         <v>45655</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -38495,7 +38495,7 @@
         <v>45614</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -38568,7 +38568,7 @@
         <v>45639</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -38641,7 +38641,7 @@
         <v>45086</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -38714,7 +38714,7 @@
         <v>45973</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -38787,7 +38787,7 @@
         <v>45147</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -38860,7 +38860,7 @@
         <v>44909</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -38933,7 +38933,7 @@
         <v>44767</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -39006,7 +39006,7 @@
         <v>45306</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -39079,7 +39079,7 @@
         <v>45973</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -39152,7 +39152,7 @@
         <v>45977</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -39230,7 +39230,7 @@
         <v>45852</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -39303,7 +39303,7 @@
         <v>45860</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -39376,7 +39376,7 @@
         <v>44768</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -39449,7 +39449,7 @@
         <v>45860</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -39522,7 +39522,7 @@
         <v>44767</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -39595,7 +39595,7 @@
         <v>45187</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -39673,7 +39673,7 @@
         <v>44858</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -39746,7 +39746,7 @@
         <v>45477</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -39824,7 +39824,7 @@
         <v>44775</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -39897,7 +39897,7 @@
         <v>44930</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -39975,7 +39975,7 @@
         <v>44865</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -40048,7 +40048,7 @@
         <v>44888</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -40121,7 +40121,7 @@
         <v>44509</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -40199,7 +40199,7 @@
         <v>44824</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -40272,7 +40272,7 @@
         <v>45275</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -40350,7 +40350,7 @@
         <v>45153</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -40428,7 +40428,7 @@
         <v>45044</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -40501,7 +40501,7 @@
         <v>44930</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -40579,7 +40579,7 @@
         <v>45309</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -40652,7 +40652,7 @@
         <v>45013</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -40725,7 +40725,7 @@
         <v>45729</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -40798,7 +40798,7 @@
         <v>45293</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -40871,7 +40871,7 @@
         <v>45804</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -40944,7 +40944,7 @@
         <v>45238</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -41017,7 +41017,7 @@
         <v>45048</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -41090,7 +41090,7 @@
         <v>46098</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -41163,7 +41163,7 @@
         <v>46099</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -41241,7 +41241,7 @@
         <v>45225</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -41314,7 +41314,7 @@
         <v>45268</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -41387,7 +41387,7 @@
         <v>45568</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -41460,7 +41460,7 @@
         <v>45161</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -41533,7 +41533,7 @@
         <v>45755</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -41606,7 +41606,7 @@
         <v>44862</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -41679,7 +41679,7 @@
         <v>45069</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -41752,7 +41752,7 @@
         <v>44994</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -41825,7 +41825,7 @@
         <v>45111</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -41903,7 +41903,7 @@
         <v>44987</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -41976,7 +41976,7 @@
         <v>45989</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -42049,7 +42049,7 @@
         <v>45077</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -42122,7 +42122,7 @@
         <v>44565</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -42195,7 +42195,7 @@
         <v>45090</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -42268,7 +42268,7 @@
         <v>46120</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -42341,7 +42341,7 @@
         <v>44498</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -42414,7 +42414,7 @@
         <v>44498</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -42487,7 +42487,7 @@
         <v>44909</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -42560,7 +42560,7 @@
         <v>45492</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -42633,7 +42633,7 @@
         <v>44958</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -42706,7 +42706,7 @@
         <v>44810</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -42779,7 +42779,7 @@
         <v>45996</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -42857,7 +42857,7 @@
         <v>46000</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -42935,7 +42935,7 @@
         <v>44949</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -43008,7 +43008,7 @@
         <v>44911</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -43081,7 +43081,7 @@
         <v>44641</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -43159,7 +43159,7 @@
         <v>46134</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -43232,7 +43232,7 @@
         <v>45774</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -43305,7 +43305,7 @@
         <v>45967</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -43378,7 +43378,7 @@
         <v>45579</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -43451,7 +43451,7 @@
         <v>44483</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -43524,7 +43524,7 @@
         <v>45147</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -43597,7 +43597,7 @@
         <v>46086</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -43670,7 +43670,7 @@
         <v>44994</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -43743,7 +43743,7 @@
         <v>45712</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -43816,7 +43816,7 @@
         <v>44882</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -43889,7 +43889,7 @@
         <v>45905</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -43962,7 +43962,7 @@
         <v>45938</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -44040,7 +44040,7 @@
         <v>46008</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -44113,7 +44113,7 @@
         <v>46010</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -44186,7 +44186,7 @@
         <v>46057</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -44259,7 +44259,7 @@
         <v>46099</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -44332,7 +44332,7 @@
         <v>46086</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -44405,7 +44405,7 @@
         <v>46086</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -44478,7 +44478,7 @@
         <v>45111</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -44551,7 +44551,7 @@
         <v>45774</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -44624,7 +44624,7 @@
         <v>44740</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -44697,7 +44697,7 @@
         <v>44658</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -44770,7 +44770,7 @@
         <v>45237</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -44843,7 +44843,7 @@
         <v>44930</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -44921,7 +44921,7 @@
         <v>45281</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -44999,7 +44999,7 @@
         <v>44498</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -45072,7 +45072,7 @@
         <v>46030</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -45145,7 +45145,7 @@
         <v>46030</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -45218,7 +45218,7 @@
         <v>46030</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -45291,7 +45291,7 @@
         <v>45274</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -45364,7 +45364,7 @@
         <v>46030</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -45437,7 +45437,7 @@
         <v>46030</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -45510,7 +45510,7 @@
         <v>45435</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -45583,7 +45583,7 @@
         <v>45111</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -45656,7 +45656,7 @@
         <v>45392</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -45734,7 +45734,7 @@
         <v>46035</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -45807,7 +45807,7 @@
         <v>46035</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -45880,7 +45880,7 @@
         <v>44508</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -45953,7 +45953,7 @@
         <v>46038</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -46026,7 +46026,7 @@
         <v>45049</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -46099,7 +46099,7 @@
         <v>45146</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -46177,7 +46177,7 @@
         <v>44665</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -46255,7 +46255,7 @@
         <v>45597</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -46328,7 +46328,7 @@
         <v>45236</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -46406,7 +46406,7 @@
         <v>44767</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -46479,7 +46479,7 @@
         <v>44931</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -46552,7 +46552,7 @@
         <v>45475</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -46625,7 +46625,7 @@
         <v>45121</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -46698,7 +46698,7 @@
         <v>44988</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -46776,7 +46776,7 @@
         <v>46055</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -46849,7 +46849,7 @@
         <v>46055</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -46922,7 +46922,7 @@
         <v>46145</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -46995,7 +46995,7 @@
         <v>46147</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -47073,7 +47073,7 @@
         <v>46147</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -47151,7 +47151,7 @@
         <v>46154</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -47229,7 +47229,7 @@
         <v>46077</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -47302,7 +47302,7 @@
         <v>46154</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -47380,7 +47380,7 @@
         <v>46154</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -47458,7 +47458,7 @@
         <v>46154</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -47536,7 +47536,7 @@
         <v>45105</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -47614,7 +47614,7 @@
         <v>46154</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -47692,7 +47692,7 @@
         <v>46079</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -47765,7 +47765,7 @@
         <v>46154</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -47843,7 +47843,7 @@
         <v>46153</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -47916,7 +47916,7 @@
         <v>46087</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -47989,7 +47989,7 @@
         <v>45729</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -48067,7 +48067,7 @@
         <v>45379</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -48140,7 +48140,7 @@
         <v>45774</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -48213,7 +48213,7 @@
         <v>45737</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -48286,7 +48286,7 @@
         <v>46094</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -48359,7 +48359,7 @@
         <v>45833</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -48432,7 +48432,7 @@
         <v>46181</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -48505,7 +48505,7 @@
         <v>46181</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -48578,7 +48578,7 @@
         <v>46085</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -48651,7 +48651,7 @@
         <v>46199</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -48724,7 +48724,7 @@
         <v>46154</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -48802,7 +48802,7 @@
         <v>46203</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -48875,7 +48875,7 @@
         <v>46205</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -48948,7 +48948,7 @@
         <v>46206</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -49021,7 +49021,7 @@
         <v>46206</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -49094,7 +49094,7 @@
         <v>46206</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -49167,7 +49167,7 @@
         <v>46206</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -49240,7 +49240,7 @@
         <v>46206</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -49313,7 +49313,7 @@
         <v>46206</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -49386,7 +49386,7 @@
         <v>46206</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -49459,7 +49459,7 @@
         <v>46206</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -49532,7 +49532,7 @@
         <v>46206</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -49605,7 +49605,7 @@
         <v>45245</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -49683,7 +49683,7 @@
         <v>46147</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -49761,7 +49761,7 @@
         <v>46266</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -49834,7 +49834,7 @@
         <v>46266</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -49907,7 +49907,7 @@
         <v>46265</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -49980,7 +49980,7 @@
         <v>46265</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -50053,7 +50053,7 @@
         <v>46267</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -50131,7 +50131,7 @@
         <v>46267</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -50209,7 +50209,7 @@
         <v>46267</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -50287,7 +50287,7 @@
         <v>46264</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -50360,7 +50360,7 @@
         <v>46267</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -50438,7 +50438,7 @@
         <v>46267</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -50516,7 +50516,7 @@
         <v>46269</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -50594,7 +50594,7 @@
         <v>46269</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -50672,7 +50672,7 @@
         <v>46269</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -50750,7 +50750,7 @@
         <v>46269</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -50828,7 +50828,7 @@
         <v>46272</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -50906,7 +50906,7 @@
         <v>46269</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -50984,7 +50984,7 @@
         <v>46269</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -51062,7 +51062,7 @@
         <v>46272</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -51140,7 +51140,7 @@
         <v>46269</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -51218,7 +51218,7 @@
         <v>46274</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -51296,7 +51296,7 @@
         <v>46272</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -51374,7 +51374,7 @@
         <v>46272</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -51452,7 +51452,7 @@
         <v>46275</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -51525,7 +51525,7 @@
         <v>46275</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -51598,7 +51598,7 @@
         <v>46272</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -51676,7 +51676,7 @@
         <v>46275</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -51749,7 +51749,7 @@
         <v>46279</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -51822,7 +51822,7 @@
         <v>46239</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -51895,7 +51895,7 @@
         <v>46239</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -51968,7 +51968,7 @@
         <v>46272</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -52046,7 +52046,7 @@
         <v>46240</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -52124,7 +52124,7 @@
         <v>46245</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -52197,7 +52197,7 @@
         <v>46245</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -52270,7 +52270,7 @@
         <v>46288</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -52343,7 +52343,7 @@
         <v>46288</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -52416,7 +52416,7 @@
         <v>46288</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -52489,7 +52489,7 @@
         <v>46288</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -52562,7 +52562,7 @@
         <v>46290</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -52635,7 +52635,7 @@
         <v>46290</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -52708,7 +52708,7 @@
         <v>46289</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -52786,7 +52786,7 @@
         <v>46289</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -52864,7 +52864,7 @@
         <v>46248</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -52942,7 +52942,7 @@
         <v>46294</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -53020,7 +53020,7 @@
         <v>46294</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -53098,7 +53098,7 @@
         <v>46248</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -53176,7 +53176,7 @@
         <v>46248</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -53254,7 +53254,7 @@
         <v>46248</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -53332,7 +53332,7 @@
         <v>46248</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -53410,7 +53410,7 @@
         <v>46294</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -53488,7 +53488,7 @@
         <v>46294</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -53561,7 +53561,7 @@
         <v>46294</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -53639,7 +53639,7 @@
         <v>46294</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -53717,7 +53717,7 @@
         <v>46248</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -53795,7 +53795,7 @@
         <v>46254</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -53868,7 +53868,7 @@
         <v>46301</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -53941,7 +53941,7 @@
         <v>46302</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -54014,7 +54014,7 @@
         <v>46259</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -54092,7 +54092,7 @@
         <v>46259</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -54170,7 +54170,7 @@
         <v>46303</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -54243,7 +54243,7 @@
         <v>46275</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -54316,7 +54316,7 @@
         <v>46030</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -54394,7 +54394,7 @@
         <v>46293</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -54467,7 +54467,7 @@
         <v>46303</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -54540,7 +54540,7 @@
         <v>46030</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -54618,7 +54618,7 @@
         <v>45541</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -54691,7 +54691,7 @@
         <v>44855</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -54764,7 +54764,7 @@
         <v>45133</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -54837,7 +54837,7 @@
         <v>45541</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -54910,7 +54910,7 @@
         <v>45699</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -54983,7 +54983,7 @@
         <v>46040</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -55056,7 +55056,7 @@
         <v>46108</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -55129,7 +55129,7 @@
         <v>46183</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>

--- a/Översikt LINKÖPING.xlsx
+++ b/Översikt LINKÖPING.xlsx
@@ -601,7 +601,7 @@
         <v>45756</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -741,7 +741,7 @@
         <v>45644</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>44679</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>45293</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>46090</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>44855</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
         <v>45278</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1505,7 +1505,7 @@
         <v>46275</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1634,7 +1634,7 @@
         <v>44368</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1750,7 +1750,7 @@
         <v>46090</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1863,7 +1863,7 @@
         <v>45720</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1975,7 +1975,7 @@
         <v>45720</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         <v>45860</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2198,7 +2198,7 @@
         <v>45804</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2313,7 +2313,7 @@
         <v>46206</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2432,7 +2432,7 @@
         <v>45280</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2548,7 +2548,7 @@
         <v>45756</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2662,7 +2662,7 @@
         <v>46090</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2772,7 +2772,7 @@
         <v>46275</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2890,7 +2890,7 @@
         <v>44949</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2999,7 +2999,7 @@
         <v>45068</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3113,7 +3113,7 @@
         <v>44679</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3227,7 +3227,7 @@
         <v>44588</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3340,7 +3340,7 @@
         <v>46146</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3449,7 +3449,7 @@
         <v>43997</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3558,7 +3558,7 @@
         <v>44679</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3675,7 +3675,7 @@
         <v>44745</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3783,7 +3783,7 @@
         <v>45943</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3891,7 +3891,7 @@
         <v>46107</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4008,7 +4008,7 @@
         <v>45555</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4121,7 +4121,7 @@
         <v>45932</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4234,7 +4234,7 @@
         <v>46050</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4342,7 +4342,7 @@
         <v>46079</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4450,7 +4450,7 @@
         <v>44479</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4563,7 +4563,7 @@
         <v>45714</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4676,7 +4676,7 @@
         <v>45089</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4784,7 +4784,7 @@
         <v>44834</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4892,7 +4892,7 @@
         <v>44679</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5004,7 +5004,7 @@
         <v>44679</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5116,7 +5116,7 @@
         <v>44479</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5228,7 +5228,7 @@
         <v>44855</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5339,7 +5339,7 @@
         <v>45153</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5451,7 +5451,7 @@
         <v>45294</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5558,7 +5558,7 @@
         <v>45236</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5669,7 +5669,7 @@
         <v>44930</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5785,7 +5785,7 @@
         <v>45163</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5892,7 +5892,7 @@
         <v>45664</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
         <v>44830</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6106,7 +6106,7 @@
         <v>45217</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6218,7 +6218,7 @@
         <v>45941</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6329,7 +6329,7 @@
         <v>44916</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6441,7 +6441,7 @@
         <v>45774</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6552,7 +6552,7 @@
         <v>45621</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6659,7 +6659,7 @@
         <v>46146</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6770,7 +6770,7 @@
         <v>46087</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6881,7 +6881,7 @@
         <v>46206</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6988,7 +6988,7 @@
         <v>46289</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7108,7 +7108,7 @@
         <v>44848</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7214,7 +7214,7 @@
         <v>44498</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7324,7 +7324,7 @@
         <v>45595</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7430,7 +7430,7 @@
         <v>44930</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7541,7 +7541,7 @@
         <v>45774</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7647,7 +7647,7 @@
         <v>44487</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7758,7 +7758,7 @@
         <v>44487</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7869,7 +7869,7 @@
         <v>45216</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7975,7 +7975,7 @@
         <v>45140</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8085,7 +8085,7 @@
         <v>45572</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8191,7 +8191,7 @@
         <v>45191</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8302,7 +8302,7 @@
         <v>45774</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8412,7 +8412,7 @@
         <v>45148</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8518,7 +8518,7 @@
         <v>45244</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8629,7 +8629,7 @@
         <v>44936</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8735,7 +8735,7 @@
         <v>45071</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8846,7 +8846,7 @@
         <v>44909</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8956,7 +8956,7 @@
         <v>45804</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9062,7 +9062,7 @@
         <v>45176</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9168,7 +9168,7 @@
         <v>44597</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9274,7 +9274,7 @@
         <v>45712</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9385,7 +9385,7 @@
         <v>45554</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9500,7 +9500,7 @@
         <v>45639</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9606,7 +9606,7 @@
         <v>45745</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9716,7 +9716,7 @@
         <v>45461</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9822,7 +9822,7 @@
         <v>45932</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9933,7 +9933,7 @@
         <v>46043</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10048,7 +10048,7 @@
         <v>45621</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10154,7 +10154,7 @@
         <v>46107</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10265,7 +10265,7 @@
         <v>46153</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10371,7 +10371,7 @@
         <v>45547</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10481,7 +10481,7 @@
         <v>46178</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10587,7 +10587,7 @@
         <v>46259</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10698,7 +10698,7 @@
         <v>44159</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10809,7 +10809,7 @@
         <v>44537</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10919,7 +10919,7 @@
         <v>45412</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11024,7 +11024,7 @@
         <v>44889</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11129,7 +11129,7 @@
         <v>44938</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11234,7 +11234,7 @@
         <v>45491</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11339,7 +11339,7 @@
         <v>45222</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11453,7 +11453,7 @@
         <v>45665</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11563,7 +11563,7 @@
         <v>45308</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11673,7 +11673,7 @@
         <v>45554</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11783,7 +11783,7 @@
         <v>45460</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11888,7 +11888,7 @@
         <v>44949</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11993,7 +11993,7 @@
         <v>45442</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12102,7 +12102,7 @@
         <v>45463</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12207,7 +12207,7 @@
         <v>44929</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12312,7 +12312,7 @@
         <v>45604</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12422,7 +12422,7 @@
         <v>44881</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12527,7 +12527,7 @@
         <v>45604</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12637,7 +12637,7 @@
         <v>45915</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12747,7 +12747,7 @@
         <v>45579</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12852,7 +12852,7 @@
         <v>45369</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12957,7 +12957,7 @@
         <v>45176</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13062,7 +13062,7 @@
         <v>45541</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13167,7 +13167,7 @@
         <v>44945</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13272,7 +13272,7 @@
         <v>45812</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13377,7 +13377,7 @@
         <v>45941</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13482,7 +13482,7 @@
         <v>44950</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13587,7 +13587,7 @@
         <v>45816</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13692,7 +13692,7 @@
         <v>45244</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13802,7 +13802,7 @@
         <v>44496</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13912,7 +13912,7 @@
         <v>45243</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14022,7 +14022,7 @@
         <v>45294</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14132,7 +14132,7 @@
         <v>45141</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14237,7 +14237,7 @@
         <v>44768</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14342,7 +14342,7 @@
         <v>45968</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14447,7 +14447,7 @@
         <v>45153</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14557,7 +14557,7 @@
         <v>45266</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14662,7 +14662,7 @@
         <v>45244</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14772,7 +14772,7 @@
         <v>45111</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14877,7 +14877,7 @@
         <v>45988</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14987,7 +14987,7 @@
         <v>44945</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -15092,7 +15092,7 @@
         <v>45994</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15197,7 +15197,7 @@
         <v>45246</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15307,7 +15307,7 @@
         <v>45965</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15417,7 +15417,7 @@
         <v>45071</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15527,7 +15527,7 @@
         <v>46079</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -15632,7 +15632,7 @@
         <v>46175</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -15737,7 +15737,7 @@
         <v>46264</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -15842,7 +15842,7 @@
         <v>46206</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -15947,7 +15947,7 @@
         <v>46289</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -16057,7 +16057,7 @@
         <v>46259</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -16167,7 +16167,7 @@
         <v>46302</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -16272,7 +16272,7 @@
         <v>44523</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -16345,7 +16345,7 @@
         <v>44608</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -16418,7 +16418,7 @@
         <v>44510</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -16491,7 +16491,7 @@
         <v>44488</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -16564,7 +16564,7 @@
         <v>44764</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -16637,7 +16637,7 @@
         <v>44855</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -16715,7 +16715,7 @@
         <v>44573</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -16788,7 +16788,7 @@
         <v>44846</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -16861,7 +16861,7 @@
         <v>44496</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -16934,7 +16934,7 @@
         <v>44853</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -17007,7 +17007,7 @@
         <v>44782</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -17080,7 +17080,7 @@
         <v>44679</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -17158,7 +17158,7 @@
         <v>44777</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -17231,7 +17231,7 @@
         <v>44753</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -17309,7 +17309,7 @@
         <v>44510</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -17382,7 +17382,7 @@
         <v>44487</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -17460,7 +17460,7 @@
         <v>44487</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -17538,7 +17538,7 @@
         <v>44627</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -17611,7 +17611,7 @@
         <v>44848</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -17684,7 +17684,7 @@
         <v>44743</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -17757,7 +17757,7 @@
         <v>44785</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -17830,7 +17830,7 @@
         <v>44823</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -17903,7 +17903,7 @@
         <v>44643</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -17976,7 +17976,7 @@
         <v>44515</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -18054,7 +18054,7 @@
         <v>44574</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -18127,7 +18127,7 @@
         <v>44571</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -18200,7 +18200,7 @@
         <v>44767</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -18273,7 +18273,7 @@
         <v>44720</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -18346,7 +18346,7 @@
         <v>44595</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -18424,7 +18424,7 @@
         <v>44481</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -18497,7 +18497,7 @@
         <v>44719</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -18575,7 +18575,7 @@
         <v>44776</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -18648,7 +18648,7 @@
         <v>44743</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -18721,7 +18721,7 @@
         <v>44487</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -18799,7 +18799,7 @@
         <v>44841</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -18872,7 +18872,7 @@
         <v>44537</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -18945,7 +18945,7 @@
         <v>44809</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -19018,7 +19018,7 @@
         <v>44776</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -19091,7 +19091,7 @@
         <v>44884</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -19164,7 +19164,7 @@
         <v>44884</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -19237,7 +19237,7 @@
         <v>44692</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -19310,7 +19310,7 @@
         <v>44628</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -19383,7 +19383,7 @@
         <v>44882</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -19461,7 +19461,7 @@
         <v>44826</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -19534,7 +19534,7 @@
         <v>44803</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -19607,7 +19607,7 @@
         <v>44791</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -19680,7 +19680,7 @@
         <v>44588</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -19753,7 +19753,7 @@
         <v>44497</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -19826,7 +19826,7 @@
         <v>44498</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -19899,7 +19899,7 @@
         <v>44638</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -19972,7 +19972,7 @@
         <v>44525</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -20045,7 +20045,7 @@
         <v>44525</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -20118,7 +20118,7 @@
         <v>45579</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -20191,7 +20191,7 @@
         <v>44812</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -20264,7 +20264,7 @@
         <v>45133</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -20337,7 +20337,7 @@
         <v>45266</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -20410,7 +20410,7 @@
         <v>45302</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -20483,7 +20483,7 @@
         <v>45082</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -20556,7 +20556,7 @@
         <v>44796</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -20634,7 +20634,7 @@
         <v>45590</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -20707,7 +20707,7 @@
         <v>44498</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -20780,7 +20780,7 @@
         <v>45082</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -20853,7 +20853,7 @@
         <v>45209</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -20926,7 +20926,7 @@
         <v>44812</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -20999,7 +20999,7 @@
         <v>44882</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -21072,7 +21072,7 @@
         <v>45364</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -21150,7 +21150,7 @@
         <v>44862</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -21223,7 +21223,7 @@
         <v>45555</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -21301,7 +21301,7 @@
         <v>45374</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -21374,7 +21374,7 @@
         <v>45655</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -21447,7 +21447,7 @@
         <v>45655</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -21520,7 +21520,7 @@
         <v>45655</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -21593,7 +21593,7 @@
         <v>44928</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -21666,7 +21666,7 @@
         <v>45092</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -21739,7 +21739,7 @@
         <v>45275</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -21812,7 +21812,7 @@
         <v>45728</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -21885,7 +21885,7 @@
         <v>44909</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -21958,7 +21958,7 @@
         <v>45678</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -22031,7 +22031,7 @@
         <v>44860</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -22104,7 +22104,7 @@
         <v>45140</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -22177,7 +22177,7 @@
         <v>45491</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -22250,7 +22250,7 @@
         <v>45231</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -22323,7 +22323,7 @@
         <v>45427</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -22396,7 +22396,7 @@
         <v>44966</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -22469,7 +22469,7 @@
         <v>45568</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -22542,7 +22542,7 @@
         <v>45755</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -22615,7 +22615,7 @@
         <v>45755</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -22688,7 +22688,7 @@
         <v>45755</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -22761,7 +22761,7 @@
         <v>44794</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -22834,7 +22834,7 @@
         <v>45294</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -22912,7 +22912,7 @@
         <v>45411</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -22985,7 +22985,7 @@
         <v>45021</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -23058,7 +23058,7 @@
         <v>45491</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -23131,7 +23131,7 @@
         <v>44768</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -23204,7 +23204,7 @@
         <v>45217</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -23277,7 +23277,7 @@
         <v>45217</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -23350,7 +23350,7 @@
         <v>44501</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -23423,7 +23423,7 @@
         <v>44949</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -23496,7 +23496,7 @@
         <v>45294</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -23569,7 +23569,7 @@
         <v>45341</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -23642,7 +23642,7 @@
         <v>45429</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -23715,7 +23715,7 @@
         <v>45177</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -23788,7 +23788,7 @@
         <v>45457</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -23861,7 +23861,7 @@
         <v>45359</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -23934,7 +23934,7 @@
         <v>45268</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -24007,7 +24007,7 @@
         <v>44903</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -24080,7 +24080,7 @@
         <v>45299</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -24153,7 +24153,7 @@
         <v>44865</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -24231,7 +24231,7 @@
         <v>45275</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -24309,7 +24309,7 @@
         <v>45275</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -24387,7 +24387,7 @@
         <v>45275</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -24460,7 +24460,7 @@
         <v>44794</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -24533,7 +24533,7 @@
         <v>45230</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -24606,7 +24606,7 @@
         <v>45231</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -24679,7 +24679,7 @@
         <v>44933</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -24752,7 +24752,7 @@
         <v>44970</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -24830,7 +24830,7 @@
         <v>45579</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -24903,7 +24903,7 @@
         <v>44945</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -24976,7 +24976,7 @@
         <v>45320</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -25049,7 +25049,7 @@
         <v>44986</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -25122,7 +25122,7 @@
         <v>45623</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -25195,7 +25195,7 @@
         <v>45623</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -25268,7 +25268,7 @@
         <v>45203</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -25341,7 +25341,7 @@
         <v>44498</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -25414,7 +25414,7 @@
         <v>44509</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -25492,7 +25492,7 @@
         <v>45604</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -25570,7 +25570,7 @@
         <v>45271</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -25643,7 +25643,7 @@
         <v>44923</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -25721,7 +25721,7 @@
         <v>45748</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -25794,7 +25794,7 @@
         <v>44909</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -25867,7 +25867,7 @@
         <v>45217</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -25940,7 +25940,7 @@
         <v>45195</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -26013,7 +26013,7 @@
         <v>44953</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -26086,7 +26086,7 @@
         <v>45274</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -26159,7 +26159,7 @@
         <v>45275</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -26232,7 +26232,7 @@
         <v>45161</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -26305,7 +26305,7 @@
         <v>45293</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -26378,7 +26378,7 @@
         <v>45741</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -26451,7 +26451,7 @@
         <v>45489</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -26524,7 +26524,7 @@
         <v>45265</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -26597,7 +26597,7 @@
         <v>45337</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -26670,7 +26670,7 @@
         <v>45342</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -26743,7 +26743,7 @@
         <v>45261</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -26816,7 +26816,7 @@
         <v>45299</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -26889,7 +26889,7 @@
         <v>45296</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -26962,7 +26962,7 @@
         <v>45300</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -27040,7 +27040,7 @@
         <v>44873</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -27118,7 +27118,7 @@
         <v>45219</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -27196,7 +27196,7 @@
         <v>45230</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -27269,7 +27269,7 @@
         <v>45082</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -27342,7 +27342,7 @@
         <v>45404</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -27415,7 +27415,7 @@
         <v>45111</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -27493,7 +27493,7 @@
         <v>44558</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -27566,7 +27566,7 @@
         <v>45275</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -27639,7 +27639,7 @@
         <v>45268</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -27712,7 +27712,7 @@
         <v>45485</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -27785,7 +27785,7 @@
         <v>45294</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -27858,7 +27858,7 @@
         <v>45294</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -27931,7 +27931,7 @@
         <v>44986</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -28004,7 +28004,7 @@
         <v>44894</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -28077,7 +28077,7 @@
         <v>45655</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -28150,7 +28150,7 @@
         <v>45266</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -28228,7 +28228,7 @@
         <v>45901</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -28301,7 +28301,7 @@
         <v>45300</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -28379,7 +28379,7 @@
         <v>44936</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -28452,7 +28452,7 @@
         <v>45182</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -28525,7 +28525,7 @@
         <v>45453</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -28598,7 +28598,7 @@
         <v>44599</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -28671,7 +28671,7 @@
         <v>45695</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -28744,7 +28744,7 @@
         <v>45483</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -28817,7 +28817,7 @@
         <v>45086</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -28890,7 +28890,7 @@
         <v>45106</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -28963,7 +28963,7 @@
         <v>45106</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -29036,7 +29036,7 @@
         <v>45106</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -29109,7 +29109,7 @@
         <v>44487</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -29187,7 +29187,7 @@
         <v>45456</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -29260,7 +29260,7 @@
         <v>45655</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -29333,7 +29333,7 @@
         <v>45545</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -29406,7 +29406,7 @@
         <v>45610</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -29479,7 +29479,7 @@
         <v>44509</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -29552,7 +29552,7 @@
         <v>45208</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -29625,7 +29625,7 @@
         <v>45037</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -29703,7 +29703,7 @@
         <v>45120</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -29776,7 +29776,7 @@
         <v>45671</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -29849,7 +29849,7 @@
         <v>44945</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -29922,7 +29922,7 @@
         <v>44937</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -29995,7 +29995,7 @@
         <v>45912</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -30073,7 +30073,7 @@
         <v>44888</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -30146,7 +30146,7 @@
         <v>45779</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -30219,7 +30219,7 @@
         <v>45912</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -30297,7 +30297,7 @@
         <v>45912</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -30375,7 +30375,7 @@
         <v>45030</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -30448,7 +30448,7 @@
         <v>45915</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -30521,7 +30521,7 @@
         <v>45779</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -30594,7 +30594,7 @@
         <v>45644</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -30667,7 +30667,7 @@
         <v>45117</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -30740,7 +30740,7 @@
         <v>45750</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -30813,7 +30813,7 @@
         <v>45140</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -30886,7 +30886,7 @@
         <v>45491</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -30959,7 +30959,7 @@
         <v>45125</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -31032,7 +31032,7 @@
         <v>45678</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -31105,7 +31105,7 @@
         <v>45116</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -31178,7 +31178,7 @@
         <v>44628</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -31251,7 +31251,7 @@
         <v>45246</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -31324,7 +31324,7 @@
         <v>44897</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -31402,7 +31402,7 @@
         <v>45470</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -31480,7 +31480,7 @@
         <v>45741</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -31553,7 +31553,7 @@
         <v>45359</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -31626,7 +31626,7 @@
         <v>45919</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -31699,7 +31699,7 @@
         <v>45155</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -31772,7 +31772,7 @@
         <v>45785</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -31845,7 +31845,7 @@
         <v>44889</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -31923,7 +31923,7 @@
         <v>45555</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -32001,7 +32001,7 @@
         <v>44993</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -32074,7 +32074,7 @@
         <v>45177</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -32147,7 +32147,7 @@
         <v>45342</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -32220,7 +32220,7 @@
         <v>45922</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -32298,7 +32298,7 @@
         <v>45546</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -32371,7 +32371,7 @@
         <v>45664</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -32444,7 +32444,7 @@
         <v>45573</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -32517,7 +32517,7 @@
         <v>44783</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -32590,7 +32590,7 @@
         <v>45483</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -32663,7 +32663,7 @@
         <v>45930</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -32736,7 +32736,7 @@
         <v>45593</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -32809,7 +32809,7 @@
         <v>45928</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -32882,7 +32882,7 @@
         <v>45005</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -32955,7 +32955,7 @@
         <v>45274</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -33028,7 +33028,7 @@
         <v>45275</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -33106,7 +33106,7 @@
         <v>45275</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -33184,7 +33184,7 @@
         <v>45737</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -33257,7 +33257,7 @@
         <v>44608</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -33335,7 +33335,7 @@
         <v>45152</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -33408,7 +33408,7 @@
         <v>45793</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -33481,7 +33481,7 @@
         <v>45625</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -33554,7 +33554,7 @@
         <v>45392</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -33627,7 +33627,7 @@
         <v>45932</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -33705,7 +33705,7 @@
         <v>45397</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -33778,7 +33778,7 @@
         <v>44643</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -33851,7 +33851,7 @@
         <v>44944</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -33924,7 +33924,7 @@
         <v>45230</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -33997,7 +33997,7 @@
         <v>45202</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -34070,7 +34070,7 @@
         <v>45229</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -34143,7 +34143,7 @@
         <v>45573</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -34216,7 +34216,7 @@
         <v>45244</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -34294,7 +34294,7 @@
         <v>45555</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -34367,7 +34367,7 @@
         <v>44945</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -34440,7 +34440,7 @@
         <v>44803</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -34513,7 +34513,7 @@
         <v>45623</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -34586,7 +34586,7 @@
         <v>44859</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -34664,7 +34664,7 @@
         <v>44939</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -34737,7 +34737,7 @@
         <v>44944</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -34810,7 +34810,7 @@
         <v>44986</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -34883,7 +34883,7 @@
         <v>45804</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -34956,7 +34956,7 @@
         <v>45142</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -35029,7 +35029,7 @@
         <v>44600</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -35102,7 +35102,7 @@
         <v>44795</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -35175,7 +35175,7 @@
         <v>45225</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -35248,7 +35248,7 @@
         <v>45596</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -35321,7 +35321,7 @@
         <v>45230</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -35394,7 +35394,7 @@
         <v>44776</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -35467,7 +35467,7 @@
         <v>44942</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -35540,7 +35540,7 @@
         <v>44683</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -35613,7 +35613,7 @@
         <v>45941</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -35686,7 +35686,7 @@
         <v>45655</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -35759,7 +35759,7 @@
         <v>45945</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -35832,7 +35832,7 @@
         <v>44638</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -35905,7 +35905,7 @@
         <v>44623</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -35978,7 +35978,7 @@
         <v>44690</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -36051,7 +36051,7 @@
         <v>45703</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -36124,7 +36124,7 @@
         <v>45816</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -36197,7 +36197,7 @@
         <v>45092</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -36270,7 +36270,7 @@
         <v>45146</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -36348,7 +36348,7 @@
         <v>45111</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -36421,7 +36421,7 @@
         <v>45821</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -36494,7 +36494,7 @@
         <v>45624</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -36567,7 +36567,7 @@
         <v>44933</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -36640,7 +36640,7 @@
         <v>45089</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -36718,7 +36718,7 @@
         <v>44909</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -36791,7 +36791,7 @@
         <v>45774</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -36864,7 +36864,7 @@
         <v>44994</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -36937,7 +36937,7 @@
         <v>45952</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -37010,7 +37010,7 @@
         <v>45231</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -37083,7 +37083,7 @@
         <v>45230</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -37156,7 +37156,7 @@
         <v>45957</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -37229,7 +37229,7 @@
         <v>45957</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -37302,7 +37302,7 @@
         <v>45957</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -37375,7 +37375,7 @@
         <v>44936</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -37448,7 +37448,7 @@
         <v>44967</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -37526,7 +37526,7 @@
         <v>45160</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -37599,7 +37599,7 @@
         <v>45300</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -37677,7 +37677,7 @@
         <v>45275</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -37750,7 +37750,7 @@
         <v>45153</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -37828,7 +37828,7 @@
         <v>45096</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -37906,7 +37906,7 @@
         <v>45225</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -37984,7 +37984,7 @@
         <v>44743</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -38057,7 +38057,7 @@
         <v>45142</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -38130,7 +38130,7 @@
         <v>45968</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -38203,7 +38203,7 @@
         <v>45968</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -38276,7 +38276,7 @@
         <v>45968</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -38349,7 +38349,7 @@
         <v>45205</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -38422,7 +38422,7 @@
         <v>45655</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -38495,7 +38495,7 @@
         <v>45614</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -38568,7 +38568,7 @@
         <v>45639</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -38641,7 +38641,7 @@
         <v>45086</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -38714,7 +38714,7 @@
         <v>45973</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -38787,7 +38787,7 @@
         <v>45147</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -38860,7 +38860,7 @@
         <v>44909</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -38933,7 +38933,7 @@
         <v>44767</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -39006,7 +39006,7 @@
         <v>45306</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -39079,7 +39079,7 @@
         <v>45973</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -39152,7 +39152,7 @@
         <v>45977</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -39230,7 +39230,7 @@
         <v>45852</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -39303,7 +39303,7 @@
         <v>45860</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -39376,7 +39376,7 @@
         <v>44768</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -39449,7 +39449,7 @@
         <v>45860</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -39522,7 +39522,7 @@
         <v>44767</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -39595,7 +39595,7 @@
         <v>45187</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -39673,7 +39673,7 @@
         <v>44858</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -39746,7 +39746,7 @@
         <v>45477</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -39824,7 +39824,7 @@
         <v>44775</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -39897,7 +39897,7 @@
         <v>44930</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -39975,7 +39975,7 @@
         <v>44865</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -40048,7 +40048,7 @@
         <v>44888</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -40121,7 +40121,7 @@
         <v>44509</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -40199,7 +40199,7 @@
         <v>44824</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -40272,7 +40272,7 @@
         <v>45275</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -40350,7 +40350,7 @@
         <v>45153</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -40428,7 +40428,7 @@
         <v>45044</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -40501,7 +40501,7 @@
         <v>44930</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -40579,7 +40579,7 @@
         <v>45309</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -40652,7 +40652,7 @@
         <v>45013</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -40725,7 +40725,7 @@
         <v>45729</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -40798,7 +40798,7 @@
         <v>45293</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -40871,7 +40871,7 @@
         <v>45804</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -40944,7 +40944,7 @@
         <v>45238</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -41017,7 +41017,7 @@
         <v>45048</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -41090,7 +41090,7 @@
         <v>46098</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -41163,7 +41163,7 @@
         <v>46099</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -41241,7 +41241,7 @@
         <v>45225</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -41314,7 +41314,7 @@
         <v>45268</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -41387,7 +41387,7 @@
         <v>45568</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -41460,7 +41460,7 @@
         <v>45161</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -41533,7 +41533,7 @@
         <v>45755</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -41606,7 +41606,7 @@
         <v>44862</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -41679,7 +41679,7 @@
         <v>45069</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -41752,7 +41752,7 @@
         <v>44994</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -41825,7 +41825,7 @@
         <v>45111</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -41903,7 +41903,7 @@
         <v>44987</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -41976,7 +41976,7 @@
         <v>45989</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -42049,7 +42049,7 @@
         <v>45077</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -42122,7 +42122,7 @@
         <v>44565</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -42195,7 +42195,7 @@
         <v>45090</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -42268,7 +42268,7 @@
         <v>46120</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -42341,7 +42341,7 @@
         <v>44498</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -42414,7 +42414,7 @@
         <v>44498</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -42487,7 +42487,7 @@
         <v>44909</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -42560,7 +42560,7 @@
         <v>45492</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -42633,7 +42633,7 @@
         <v>44958</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -42706,7 +42706,7 @@
         <v>44810</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -42779,7 +42779,7 @@
         <v>45996</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -42857,7 +42857,7 @@
         <v>46000</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -42935,7 +42935,7 @@
         <v>44949</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -43008,7 +43008,7 @@
         <v>44911</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -43081,7 +43081,7 @@
         <v>44641</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -43159,7 +43159,7 @@
         <v>46134</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -43232,7 +43232,7 @@
         <v>45774</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -43305,7 +43305,7 @@
         <v>45967</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -43378,7 +43378,7 @@
         <v>45579</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -43451,7 +43451,7 @@
         <v>44483</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -43524,7 +43524,7 @@
         <v>45147</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -43597,7 +43597,7 @@
         <v>46086</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -43670,7 +43670,7 @@
         <v>44994</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -43743,7 +43743,7 @@
         <v>45712</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -43816,7 +43816,7 @@
         <v>44882</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -43889,7 +43889,7 @@
         <v>45905</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -43962,7 +43962,7 @@
         <v>45938</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -44040,7 +44040,7 @@
         <v>46008</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -44113,7 +44113,7 @@
         <v>46010</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -44186,7 +44186,7 @@
         <v>46057</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -44259,7 +44259,7 @@
         <v>46099</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -44332,7 +44332,7 @@
         <v>46086</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -44405,7 +44405,7 @@
         <v>46086</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -44478,7 +44478,7 @@
         <v>45111</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -44551,7 +44551,7 @@
         <v>45774</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -44624,7 +44624,7 @@
         <v>44740</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -44697,7 +44697,7 @@
         <v>44658</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -44770,7 +44770,7 @@
         <v>45237</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -44843,7 +44843,7 @@
         <v>44930</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -44921,7 +44921,7 @@
         <v>45281</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -44999,7 +44999,7 @@
         <v>44498</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -45072,7 +45072,7 @@
         <v>46030</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -45145,7 +45145,7 @@
         <v>46030</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -45218,7 +45218,7 @@
         <v>46030</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -45291,7 +45291,7 @@
         <v>45274</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -45364,7 +45364,7 @@
         <v>46030</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -45437,7 +45437,7 @@
         <v>46030</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -45510,7 +45510,7 @@
         <v>45435</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -45583,7 +45583,7 @@
         <v>45111</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -45656,7 +45656,7 @@
         <v>45392</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -45734,7 +45734,7 @@
         <v>46035</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -45807,7 +45807,7 @@
         <v>46035</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -45880,7 +45880,7 @@
         <v>44508</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -45953,7 +45953,7 @@
         <v>46038</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -46026,7 +46026,7 @@
         <v>45049</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -46099,7 +46099,7 @@
         <v>45146</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -46177,7 +46177,7 @@
         <v>44665</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -46255,7 +46255,7 @@
         <v>45597</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -46328,7 +46328,7 @@
         <v>45236</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -46406,7 +46406,7 @@
         <v>44767</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -46479,7 +46479,7 @@
         <v>44931</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -46552,7 +46552,7 @@
         <v>45475</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -46625,7 +46625,7 @@
         <v>45121</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -46698,7 +46698,7 @@
         <v>44988</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -46776,7 +46776,7 @@
         <v>46055</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -46849,7 +46849,7 @@
         <v>46055</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -46922,7 +46922,7 @@
         <v>46145</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -46995,7 +46995,7 @@
         <v>46147</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -47073,7 +47073,7 @@
         <v>46147</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -47151,7 +47151,7 @@
         <v>46154</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -47229,7 +47229,7 @@
         <v>46077</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -47302,7 +47302,7 @@
         <v>46154</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -47380,7 +47380,7 @@
         <v>46154</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -47458,7 +47458,7 @@
         <v>46154</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -47536,7 +47536,7 @@
         <v>45105</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -47614,7 +47614,7 @@
         <v>46154</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -47692,7 +47692,7 @@
         <v>46079</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -47765,7 +47765,7 @@
         <v>46154</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -47843,7 +47843,7 @@
         <v>46153</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -47916,7 +47916,7 @@
         <v>46087</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -47989,7 +47989,7 @@
         <v>45729</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -48067,7 +48067,7 @@
         <v>45379</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -48140,7 +48140,7 @@
         <v>45774</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -48213,7 +48213,7 @@
         <v>45737</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -48286,7 +48286,7 @@
         <v>46094</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -48359,7 +48359,7 @@
         <v>45833</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -48432,7 +48432,7 @@
         <v>46181</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -48505,7 +48505,7 @@
         <v>46181</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -48578,7 +48578,7 @@
         <v>46085</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -48651,7 +48651,7 @@
         <v>46199</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -48724,7 +48724,7 @@
         <v>46154</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -48802,7 +48802,7 @@
         <v>46203</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -48875,7 +48875,7 @@
         <v>46205</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -48948,7 +48948,7 @@
         <v>46206</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -49021,7 +49021,7 @@
         <v>46206</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -49094,7 +49094,7 @@
         <v>46206</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -49167,7 +49167,7 @@
         <v>46206</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -49240,7 +49240,7 @@
         <v>46206</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -49313,7 +49313,7 @@
         <v>46206</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -49386,7 +49386,7 @@
         <v>46206</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -49459,7 +49459,7 @@
         <v>46206</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -49532,7 +49532,7 @@
         <v>46206</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -49605,7 +49605,7 @@
         <v>45245</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -49683,7 +49683,7 @@
         <v>46147</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -49761,7 +49761,7 @@
         <v>46266</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -49834,7 +49834,7 @@
         <v>46266</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -49907,7 +49907,7 @@
         <v>46265</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -49980,7 +49980,7 @@
         <v>46265</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -50053,7 +50053,7 @@
         <v>46267</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -50131,7 +50131,7 @@
         <v>46267</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -50209,7 +50209,7 @@
         <v>46267</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -50287,7 +50287,7 @@
         <v>46264</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -50360,7 +50360,7 @@
         <v>46267</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -50438,7 +50438,7 @@
         <v>46267</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -50516,7 +50516,7 @@
         <v>46269</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -50594,7 +50594,7 @@
         <v>46269</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -50672,7 +50672,7 @@
         <v>46269</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -50750,7 +50750,7 @@
         <v>46269</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -50828,7 +50828,7 @@
         <v>46272</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -50906,7 +50906,7 @@
         <v>46269</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -50984,7 +50984,7 @@
         <v>46269</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -51062,7 +51062,7 @@
         <v>46272</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -51140,7 +51140,7 @@
         <v>46269</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -51218,7 +51218,7 @@
         <v>46274</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -51296,7 +51296,7 @@
         <v>46272</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -51374,7 +51374,7 @@
         <v>46272</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -51452,7 +51452,7 @@
         <v>46275</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -51525,7 +51525,7 @@
         <v>46275</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -51598,7 +51598,7 @@
         <v>46272</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -51676,7 +51676,7 @@
         <v>46275</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -51749,7 +51749,7 @@
         <v>46279</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -51822,7 +51822,7 @@
         <v>46239</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -51895,7 +51895,7 @@
         <v>46239</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -51968,7 +51968,7 @@
         <v>46272</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -52046,7 +52046,7 @@
         <v>46240</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -52124,7 +52124,7 @@
         <v>46245</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -52197,7 +52197,7 @@
         <v>46245</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -52270,7 +52270,7 @@
         <v>46288</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -52343,7 +52343,7 @@
         <v>46288</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -52416,7 +52416,7 @@
         <v>46288</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -52489,7 +52489,7 @@
         <v>46288</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -52562,7 +52562,7 @@
         <v>46290</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -52635,7 +52635,7 @@
         <v>46290</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -52708,7 +52708,7 @@
         <v>46289</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -52786,7 +52786,7 @@
         <v>46289</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -52864,7 +52864,7 @@
         <v>46248</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -52942,7 +52942,7 @@
         <v>46294</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -53020,7 +53020,7 @@
         <v>46294</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -53098,7 +53098,7 @@
         <v>46248</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -53176,7 +53176,7 @@
         <v>46248</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -53254,7 +53254,7 @@
         <v>46248</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -53332,7 +53332,7 @@
         <v>46248</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -53410,7 +53410,7 @@
         <v>46294</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -53488,7 +53488,7 @@
         <v>46294</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -53561,7 +53561,7 @@
         <v>46294</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -53639,7 +53639,7 @@
         <v>46294</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -53717,7 +53717,7 @@
         <v>46248</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -53795,7 +53795,7 @@
         <v>46254</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -53868,7 +53868,7 @@
         <v>46301</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -53941,7 +53941,7 @@
         <v>46302</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -54014,7 +54014,7 @@
         <v>46259</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -54092,7 +54092,7 @@
         <v>46259</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -54170,7 +54170,7 @@
         <v>46303</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -54243,7 +54243,7 @@
         <v>46275</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -54316,7 +54316,7 @@
         <v>46030</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -54394,7 +54394,7 @@
         <v>46293</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -54467,7 +54467,7 @@
         <v>46303</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -54540,7 +54540,7 @@
         <v>46030</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -54618,7 +54618,7 @@
         <v>45541</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -54691,7 +54691,7 @@
         <v>44855</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -54764,7 +54764,7 @@
         <v>45133</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -54837,7 +54837,7 @@
         <v>45541</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -54910,7 +54910,7 @@
         <v>45699</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -54983,7 +54983,7 @@
         <v>46040</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -55056,7 +55056,7 @@
         <v>46108</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -55129,7 +55129,7 @@
         <v>46183</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>

--- a/Översikt LINKÖPING.xlsx
+++ b/Översikt LINKÖPING.xlsx
@@ -601,7 +601,7 @@
         <v>45756</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -741,7 +741,7 @@
         <v>45644</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>44679</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>45293</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>46090</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>44855</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
         <v>45278</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1505,7 +1505,7 @@
         <v>46275</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1634,7 +1634,7 @@
         <v>44368</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1750,7 +1750,7 @@
         <v>46090</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1863,7 +1863,7 @@
         <v>45720</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1975,7 +1975,7 @@
         <v>45720</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         <v>46206</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2206,7 +2206,7 @@
         <v>45860</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2317,7 +2317,7 @@
         <v>45804</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2432,7 +2432,7 @@
         <v>45280</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2548,7 +2548,7 @@
         <v>45756</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2662,7 +2662,7 @@
         <v>46090</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2772,7 +2772,7 @@
         <v>46275</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2890,7 +2890,7 @@
         <v>46146</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2999,7 +2999,7 @@
         <v>45068</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3113,7 +3113,7 @@
         <v>44949</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3222,7 +3222,7 @@
         <v>44588</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3335,7 +3335,7 @@
         <v>44679</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3449,7 +3449,7 @@
         <v>43997</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3558,7 +3558,7 @@
         <v>44679</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3675,7 +3675,7 @@
         <v>44745</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3783,7 +3783,7 @@
         <v>45932</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3896,7 +3896,7 @@
         <v>45943</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4004,7 +4004,7 @@
         <v>46050</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4112,7 +4112,7 @@
         <v>46079</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4220,7 +4220,7 @@
         <v>45555</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4333,7 +4333,7 @@
         <v>46107</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4450,7 +4450,7 @@
         <v>45714</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4563,7 +4563,7 @@
         <v>45089</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4671,7 +4671,7 @@
         <v>44834</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4779,7 +4779,7 @@
         <v>44679</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4891,7 +4891,7 @@
         <v>44679</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5003,7 +5003,7 @@
         <v>44855</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5114,7 +5114,7 @@
         <v>44930</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5230,7 +5230,7 @@
         <v>45153</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5342,7 +5342,7 @@
         <v>44830</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5449,7 +5449,7 @@
         <v>44916</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5561,7 +5561,7 @@
         <v>46146</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5672,7 +5672,7 @@
         <v>45941</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5783,7 +5783,7 @@
         <v>45236</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5894,7 +5894,7 @@
         <v>45294</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6001,7 +6001,7 @@
         <v>46087</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6112,7 +6112,7 @@
         <v>45774</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6223,7 +6223,7 @@
         <v>46206</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6330,7 +6330,7 @@
         <v>45163</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6437,7 +6437,7 @@
         <v>45217</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6549,7 +6549,7 @@
         <v>46289</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6669,7 +6669,7 @@
         <v>45621</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6776,7 +6776,7 @@
         <v>45664</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6883,7 +6883,7 @@
         <v>44848</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6989,7 +6989,7 @@
         <v>44498</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7099,7 +7099,7 @@
         <v>45191</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7210,7 +7210,7 @@
         <v>45216</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7316,7 +7316,7 @@
         <v>44909</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7426,7 +7426,7 @@
         <v>45572</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7532,7 +7532,7 @@
         <v>45071</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7643,7 +7643,7 @@
         <v>45712</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7754,7 +7754,7 @@
         <v>44597</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7860,7 +7860,7 @@
         <v>45745</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7970,7 +7970,7 @@
         <v>45932</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8081,7 +8081,7 @@
         <v>44487</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8192,7 +8192,7 @@
         <v>44936</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8298,7 +8298,7 @@
         <v>44487</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8409,7 +8409,7 @@
         <v>46107</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8520,7 +8520,7 @@
         <v>46153</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8626,7 +8626,7 @@
         <v>45461</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8732,7 +8732,7 @@
         <v>45140</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8842,7 +8842,7 @@
         <v>45595</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8948,7 +8948,7 @@
         <v>45554</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9063,7 +9063,7 @@
         <v>45547</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9173,7 +9173,7 @@
         <v>46043</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9288,7 +9288,7 @@
         <v>45774</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9394,7 +9394,7 @@
         <v>45639</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9500,7 +9500,7 @@
         <v>45244</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9611,7 +9611,7 @@
         <v>44930</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9722,7 +9722,7 @@
         <v>45176</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9828,7 +9828,7 @@
         <v>45148</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9934,7 +9934,7 @@
         <v>46178</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10040,7 +10040,7 @@
         <v>45621</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10146,7 +10146,7 @@
         <v>45774</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10256,7 +10256,7 @@
         <v>46259</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10367,7 +10367,7 @@
         <v>45804</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10473,7 +10473,7 @@
         <v>44159</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10584,7 +10584,7 @@
         <v>44537</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10694,7 +10694,7 @@
         <v>44938</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10799,7 +10799,7 @@
         <v>45665</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10909,7 +10909,7 @@
         <v>44768</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11014,7 +11014,7 @@
         <v>45141</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11119,7 +11119,7 @@
         <v>45463</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11224,7 +11224,7 @@
         <v>45541</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11329,7 +11329,7 @@
         <v>45222</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11443,7 +11443,7 @@
         <v>45243</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11553,7 +11553,7 @@
         <v>45604</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11663,7 +11663,7 @@
         <v>44929</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11768,7 +11768,7 @@
         <v>45554</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11878,7 +11878,7 @@
         <v>45965</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11988,7 +11988,7 @@
         <v>45246</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12098,7 +12098,7 @@
         <v>45915</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12208,7 +12208,7 @@
         <v>45579</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12313,7 +12313,7 @@
         <v>45244</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12423,7 +12423,7 @@
         <v>45941</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12528,7 +12528,7 @@
         <v>44889</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12633,7 +12633,7 @@
         <v>45968</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12738,7 +12738,7 @@
         <v>45988</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12848,7 +12848,7 @@
         <v>45604</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12958,7 +12958,7 @@
         <v>46175</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13063,7 +13063,7 @@
         <v>45071</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13173,7 +13173,7 @@
         <v>46079</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13278,7 +13278,7 @@
         <v>45308</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13388,7 +13388,7 @@
         <v>45442</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13497,7 +13497,7 @@
         <v>44945</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13602,7 +13602,7 @@
         <v>45994</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13707,7 +13707,7 @@
         <v>45412</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13812,7 +13812,7 @@
         <v>45244</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13922,7 +13922,7 @@
         <v>44945</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14027,7 +14027,7 @@
         <v>44881</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14132,7 +14132,7 @@
         <v>45460</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14237,7 +14237,7 @@
         <v>46206</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14342,7 +14342,7 @@
         <v>44950</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14447,7 +14447,7 @@
         <v>45294</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14557,7 +14557,7 @@
         <v>45266</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14662,7 +14662,7 @@
         <v>45111</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14767,7 +14767,7 @@
         <v>44949</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14872,7 +14872,7 @@
         <v>46289</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14982,7 +14982,7 @@
         <v>45491</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -15087,7 +15087,7 @@
         <v>44496</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15197,7 +15197,7 @@
         <v>45176</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15302,7 +15302,7 @@
         <v>46259</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15412,7 +15412,7 @@
         <v>45369</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15517,7 +15517,7 @@
         <v>46302</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -15622,7 +15622,7 @@
         <v>46264</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -15727,7 +15727,7 @@
         <v>46308</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -15841,7 +15841,7 @@
         <v>45812</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -15946,7 +15946,7 @@
         <v>45816</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -16051,7 +16051,7 @@
         <v>45153</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -16161,7 +16161,7 @@
         <v>44523</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -16234,7 +16234,7 @@
         <v>44608</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -16307,7 +16307,7 @@
         <v>44510</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -16380,7 +16380,7 @@
         <v>44488</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -16453,7 +16453,7 @@
         <v>44764</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -16526,7 +16526,7 @@
         <v>44855</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -16604,7 +16604,7 @@
         <v>44573</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -16677,7 +16677,7 @@
         <v>44846</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -16750,7 +16750,7 @@
         <v>44496</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -16823,7 +16823,7 @@
         <v>44782</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -16896,7 +16896,7 @@
         <v>44853</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -16969,7 +16969,7 @@
         <v>44679</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -17047,7 +17047,7 @@
         <v>44777</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -17120,7 +17120,7 @@
         <v>44753</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -17198,7 +17198,7 @@
         <v>44510</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -17271,7 +17271,7 @@
         <v>44487</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -17349,7 +17349,7 @@
         <v>44487</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -17427,7 +17427,7 @@
         <v>44823</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -17500,7 +17500,7 @@
         <v>44515</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -17578,7 +17578,7 @@
         <v>44767</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -17651,7 +17651,7 @@
         <v>44719</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -17729,7 +17729,7 @@
         <v>44487</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -17807,7 +17807,7 @@
         <v>44776</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -17880,7 +17880,7 @@
         <v>44692</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -17953,7 +17953,7 @@
         <v>44803</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -18026,7 +18026,7 @@
         <v>44882</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -18104,7 +18104,7 @@
         <v>44588</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -18177,7 +18177,7 @@
         <v>44743</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -18250,7 +18250,7 @@
         <v>44574</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -18323,7 +18323,7 @@
         <v>44571</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -18396,7 +18396,7 @@
         <v>44841</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -18469,7 +18469,7 @@
         <v>44537</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -18542,7 +18542,7 @@
         <v>44809</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -18615,7 +18615,7 @@
         <v>44884</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -18688,7 +18688,7 @@
         <v>44884</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -18761,7 +18761,7 @@
         <v>44628</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -18834,7 +18834,7 @@
         <v>44525</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -18907,7 +18907,7 @@
         <v>44525</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -18980,7 +18980,7 @@
         <v>44627</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -19053,7 +19053,7 @@
         <v>44785</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -19126,7 +19126,7 @@
         <v>44643</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -19199,7 +19199,7 @@
         <v>44720</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -19272,7 +19272,7 @@
         <v>44595</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -19350,7 +19350,7 @@
         <v>44743</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -19423,7 +19423,7 @@
         <v>44497</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -19496,7 +19496,7 @@
         <v>44848</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -19569,7 +19569,7 @@
         <v>44776</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -19642,7 +19642,7 @@
         <v>44826</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -19715,7 +19715,7 @@
         <v>44791</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -19788,7 +19788,7 @@
         <v>44498</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -19861,7 +19861,7 @@
         <v>44638</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -19934,7 +19934,7 @@
         <v>44812</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -20007,7 +20007,7 @@
         <v>44796</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -20085,7 +20085,7 @@
         <v>44794</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -20158,7 +20158,7 @@
         <v>45274</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -20231,7 +20231,7 @@
         <v>45236</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -20309,7 +20309,7 @@
         <v>45477</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -20387,7 +20387,7 @@
         <v>44945</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -20460,7 +20460,7 @@
         <v>45728</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -20533,7 +20533,7 @@
         <v>45435</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -20606,7 +20606,7 @@
         <v>45457</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -20679,7 +20679,7 @@
         <v>45294</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -20752,7 +20752,7 @@
         <v>45089</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -20830,7 +20830,7 @@
         <v>45140</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -20903,7 +20903,7 @@
         <v>44767</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -20976,7 +20976,7 @@
         <v>44767</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -21049,7 +21049,7 @@
         <v>44897</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -21127,7 +21127,7 @@
         <v>44939</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -21200,7 +21200,7 @@
         <v>45217</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -21273,7 +21273,7 @@
         <v>45217</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -21346,7 +21346,7 @@
         <v>45182</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -21419,7 +21419,7 @@
         <v>45238</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -21492,7 +21492,7 @@
         <v>45225</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -21565,7 +21565,7 @@
         <v>45225</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -21638,7 +21638,7 @@
         <v>45142</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -21711,7 +21711,7 @@
         <v>45302</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -21784,7 +21784,7 @@
         <v>45225</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -21862,7 +21862,7 @@
         <v>45623</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -21935,7 +21935,7 @@
         <v>44498</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -22008,7 +22008,7 @@
         <v>44498</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -22081,7 +22081,7 @@
         <v>45275</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -22154,7 +22154,7 @@
         <v>45133</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -22227,7 +22227,7 @@
         <v>45545</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -22300,7 +22300,7 @@
         <v>44909</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -22373,7 +22373,7 @@
         <v>44909</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -22446,7 +22446,7 @@
         <v>44903</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -22519,7 +22519,7 @@
         <v>44930</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -22597,7 +22597,7 @@
         <v>45030</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -22670,7 +22670,7 @@
         <v>45161</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -22743,7 +22743,7 @@
         <v>45309</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -22816,7 +22816,7 @@
         <v>45160</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -22889,7 +22889,7 @@
         <v>45111</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -22962,7 +22962,7 @@
         <v>45755</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -23035,7 +23035,7 @@
         <v>45624</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -23108,7 +23108,7 @@
         <v>45294</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -23181,7 +23181,7 @@
         <v>45111</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -23254,7 +23254,7 @@
         <v>45491</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -23327,7 +23327,7 @@
         <v>44894</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -23400,7 +23400,7 @@
         <v>45750</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -23473,7 +23473,7 @@
         <v>44683</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -23546,7 +23546,7 @@
         <v>45275</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -23619,7 +23619,7 @@
         <v>45274</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -23692,7 +23692,7 @@
         <v>45146</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -23770,7 +23770,7 @@
         <v>44888</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -23843,7 +23843,7 @@
         <v>44487</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -23921,7 +23921,7 @@
         <v>45456</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -23994,7 +23994,7 @@
         <v>45623</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -24067,7 +24067,7 @@
         <v>45623</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -24140,7 +24140,7 @@
         <v>44949</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -24213,7 +24213,7 @@
         <v>45013</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -24286,7 +24286,7 @@
         <v>44558</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -24359,7 +24359,7 @@
         <v>44743</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -24432,7 +24432,7 @@
         <v>45125</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -24505,7 +24505,7 @@
         <v>45610</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -24578,7 +24578,7 @@
         <v>44865</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -24651,7 +24651,7 @@
         <v>45230</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -24724,7 +24724,7 @@
         <v>45678</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -24797,7 +24797,7 @@
         <v>45147</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -24870,7 +24870,7 @@
         <v>45359</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -24943,7 +24943,7 @@
         <v>45208</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -25016,7 +25016,7 @@
         <v>44600</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -25089,7 +25089,7 @@
         <v>45202</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -25162,7 +25162,7 @@
         <v>45729</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -25235,7 +25235,7 @@
         <v>45021</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -25308,7 +25308,7 @@
         <v>45712</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -25381,7 +25381,7 @@
         <v>46099</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -25454,7 +25454,7 @@
         <v>45281</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -25532,7 +25532,7 @@
         <v>44783</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -25605,7 +25605,7 @@
         <v>44928</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -25678,7 +25678,7 @@
         <v>44933</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -25751,7 +25751,7 @@
         <v>44945</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -25824,7 +25824,7 @@
         <v>44768</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -25897,7 +25897,7 @@
         <v>44909</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -25970,7 +25970,7 @@
         <v>44862</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -26043,7 +26043,7 @@
         <v>44498</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -26116,7 +26116,7 @@
         <v>44509</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -26194,7 +26194,7 @@
         <v>44889</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -26272,7 +26272,7 @@
         <v>45203</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -26345,7 +26345,7 @@
         <v>44665</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -26423,7 +26423,7 @@
         <v>44860</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -26496,7 +26496,7 @@
         <v>45905</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -26569,7 +26569,7 @@
         <v>46086</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -26642,7 +26642,7 @@
         <v>46057</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -26715,7 +26715,7 @@
         <v>44795</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -26788,7 +26788,7 @@
         <v>45121</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -26861,7 +26861,7 @@
         <v>44933</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -26934,7 +26934,7 @@
         <v>44942</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -27007,7 +27007,7 @@
         <v>45293</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -27080,7 +27080,7 @@
         <v>45901</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -27153,7 +27153,7 @@
         <v>45195</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -27226,7 +27226,7 @@
         <v>45111</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -27299,7 +27299,7 @@
         <v>45555</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -27377,7 +27377,7 @@
         <v>45082</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -27450,7 +27450,7 @@
         <v>45082</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -27523,7 +27523,7 @@
         <v>45590</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -27596,7 +27596,7 @@
         <v>45244</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -27674,7 +27674,7 @@
         <v>44498</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -27747,7 +27747,7 @@
         <v>45915</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -27820,7 +27820,7 @@
         <v>44936</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -27893,7 +27893,7 @@
         <v>45912</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -27971,7 +27971,7 @@
         <v>44931</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -28044,7 +28044,7 @@
         <v>45912</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -28122,7 +28122,7 @@
         <v>45912</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -28200,7 +28200,7 @@
         <v>45678</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -28273,7 +28273,7 @@
         <v>44623</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -28346,7 +28346,7 @@
         <v>46147</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -28424,7 +28424,7 @@
         <v>45111</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -28502,7 +28502,7 @@
         <v>45919</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -28575,7 +28575,7 @@
         <v>46147</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -28653,7 +28653,7 @@
         <v>44923</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -28731,7 +28731,7 @@
         <v>45489</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -28804,7 +28804,7 @@
         <v>45922</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -28882,7 +28882,7 @@
         <v>45106</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -28955,7 +28955,7 @@
         <v>45106</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -29028,7 +29028,7 @@
         <v>45296</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -29101,7 +29101,7 @@
         <v>46145</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -29174,7 +29174,7 @@
         <v>45069</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -29247,7 +29247,7 @@
         <v>44501</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -29320,7 +29320,7 @@
         <v>45392</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -29393,7 +29393,7 @@
         <v>45555</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -29471,7 +29471,7 @@
         <v>45644</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -29544,7 +29544,7 @@
         <v>44944</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -29617,7 +29617,7 @@
         <v>45928</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -29690,7 +29690,7 @@
         <v>45930</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -29763,7 +29763,7 @@
         <v>45932</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -29841,7 +29841,7 @@
         <v>45105</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -29919,7 +29919,7 @@
         <v>46153</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -29992,7 +29992,7 @@
         <v>45261</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -30065,7 +30065,7 @@
         <v>45237</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -30138,7 +30138,7 @@
         <v>45140</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -30211,7 +30211,7 @@
         <v>44803</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -30284,7 +30284,7 @@
         <v>45941</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -30357,7 +30357,7 @@
         <v>45945</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -30430,7 +30430,7 @@
         <v>45086</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -30503,7 +30503,7 @@
         <v>46154</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -30581,7 +30581,7 @@
         <v>44987</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -30654,7 +30654,7 @@
         <v>46154</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -30732,7 +30732,7 @@
         <v>44565</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -30805,7 +30805,7 @@
         <v>46154</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -30883,7 +30883,7 @@
         <v>44690</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -30956,7 +30956,7 @@
         <v>45952</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -31029,7 +31029,7 @@
         <v>46154</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -31107,7 +31107,7 @@
         <v>44768</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -31180,7 +31180,7 @@
         <v>46154</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -31258,7 +31258,7 @@
         <v>45957</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -31331,7 +31331,7 @@
         <v>46154</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -31409,7 +31409,7 @@
         <v>44888</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -31482,7 +31482,7 @@
         <v>45957</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -31555,7 +31555,7 @@
         <v>45957</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -31628,7 +31628,7 @@
         <v>44986</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -31701,7 +31701,7 @@
         <v>45737</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -31774,7 +31774,7 @@
         <v>45729</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -31852,7 +31852,7 @@
         <v>44967</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -31930,7 +31930,7 @@
         <v>45379</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -32003,7 +32003,7 @@
         <v>45968</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -32076,7 +32076,7 @@
         <v>45968</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -32149,7 +32149,7 @@
         <v>45774</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -32222,7 +32222,7 @@
         <v>45968</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -32295,7 +32295,7 @@
         <v>45177</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -32368,7 +32368,7 @@
         <v>45116</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -32441,7 +32441,7 @@
         <v>45146</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -32519,7 +32519,7 @@
         <v>45973</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -32592,7 +32592,7 @@
         <v>45973</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -32665,7 +32665,7 @@
         <v>45153</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -32743,7 +32743,7 @@
         <v>45230</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -32816,7 +32816,7 @@
         <v>45833</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -32889,7 +32889,7 @@
         <v>45977</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -32967,7 +32967,7 @@
         <v>45306</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -33040,7 +33040,7 @@
         <v>44862</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -33113,7 +33113,7 @@
         <v>45470</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -33191,7 +33191,7 @@
         <v>44911</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -33264,7 +33264,7 @@
         <v>45187</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -33342,7 +33342,7 @@
         <v>44930</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -33420,7 +33420,7 @@
         <v>44994</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -33493,7 +33493,7 @@
         <v>45044</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -33566,7 +33566,7 @@
         <v>45300</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -33644,7 +33644,7 @@
         <v>45392</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -33722,7 +33722,7 @@
         <v>45655</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -33795,7 +33795,7 @@
         <v>45086</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -33868,7 +33868,7 @@
         <v>45989</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -33941,7 +33941,7 @@
         <v>45755</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -34014,7 +34014,7 @@
         <v>45755</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -34087,7 +34087,7 @@
         <v>45755</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -34160,7 +34160,7 @@
         <v>45117</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -34233,7 +34233,7 @@
         <v>45374</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -34306,7 +34306,7 @@
         <v>45996</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -34384,7 +34384,7 @@
         <v>44498</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -34457,7 +34457,7 @@
         <v>46000</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -34535,7 +34535,7 @@
         <v>45337</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -34608,7 +34608,7 @@
         <v>45294</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -34686,7 +34686,7 @@
         <v>45625</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -34759,7 +34759,7 @@
         <v>44993</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -34832,7 +34832,7 @@
         <v>44508</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -34905,7 +34905,7 @@
         <v>45741</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -34978,7 +34978,7 @@
         <v>45320</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -35051,7 +35051,7 @@
         <v>45266</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -35129,7 +35129,7 @@
         <v>45695</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -35202,7 +35202,7 @@
         <v>45231</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -35275,7 +35275,7 @@
         <v>44949</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -35348,7 +35348,7 @@
         <v>44882</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -35421,7 +35421,7 @@
         <v>44882</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -35494,7 +35494,7 @@
         <v>46010</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -35567,7 +35567,7 @@
         <v>44930</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -35645,7 +35645,7 @@
         <v>45268</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -35718,7 +35718,7 @@
         <v>45005</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -35791,7 +35791,7 @@
         <v>45092</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -35864,7 +35864,7 @@
         <v>46030</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -35937,7 +35937,7 @@
         <v>46030</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -36010,7 +36010,7 @@
         <v>46030</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -36083,7 +36083,7 @@
         <v>45275</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -36156,7 +36156,7 @@
         <v>46030</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -36229,7 +36229,7 @@
         <v>46030</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -36302,7 +36302,7 @@
         <v>46035</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -36375,7 +36375,7 @@
         <v>45275</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -36453,7 +36453,7 @@
         <v>45275</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -36531,7 +36531,7 @@
         <v>46035</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -36604,7 +36604,7 @@
         <v>46038</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -36677,7 +36677,7 @@
         <v>45411</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -36750,7 +36750,7 @@
         <v>44658</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -36823,7 +36823,7 @@
         <v>45217</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -36896,7 +36896,7 @@
         <v>46181</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -36969,7 +36969,7 @@
         <v>44873</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -37047,7 +37047,7 @@
         <v>45096</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -37125,7 +37125,7 @@
         <v>46055</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -37198,7 +37198,7 @@
         <v>46055</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -37271,7 +37271,7 @@
         <v>46181</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -37344,7 +37344,7 @@
         <v>45741</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -37417,7 +37417,7 @@
         <v>44775</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -37490,7 +37490,7 @@
         <v>45655</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -37563,7 +37563,7 @@
         <v>45037</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -37641,7 +37641,7 @@
         <v>45271</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -37714,7 +37714,7 @@
         <v>45177</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -37787,7 +37787,7 @@
         <v>45161</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -37860,7 +37860,7 @@
         <v>44958</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -37933,7 +37933,7 @@
         <v>44936</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -38006,7 +38006,7 @@
         <v>46077</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -38079,7 +38079,7 @@
         <v>46079</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -38152,7 +38152,7 @@
         <v>44638</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -38225,7 +38225,7 @@
         <v>46087</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -38298,7 +38298,7 @@
         <v>45453</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -38371,7 +38371,7 @@
         <v>45293</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -38444,7 +38444,7 @@
         <v>44599</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -38517,7 +38517,7 @@
         <v>46085</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -38590,7 +38590,7 @@
         <v>44776</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -38663,7 +38663,7 @@
         <v>46098</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -38736,7 +38736,7 @@
         <v>46094</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -38809,7 +38809,7 @@
         <v>44970</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -38887,7 +38887,7 @@
         <v>46099</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -38965,7 +38965,7 @@
         <v>45120</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -39038,7 +39038,7 @@
         <v>44608</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -39116,7 +39116,7 @@
         <v>45475</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -39189,7 +39189,7 @@
         <v>44824</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -39262,7 +39262,7 @@
         <v>45604</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -39340,7 +39340,7 @@
         <v>44865</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -39418,7 +39418,7 @@
         <v>45268</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -39491,7 +39491,7 @@
         <v>45106</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -39564,7 +39564,7 @@
         <v>45090</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -39637,7 +39637,7 @@
         <v>44937</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -39710,7 +39710,7 @@
         <v>45111</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -39788,7 +39788,7 @@
         <v>44994</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -39861,7 +39861,7 @@
         <v>46120</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -39934,7 +39934,7 @@
         <v>44945</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -40007,7 +40007,7 @@
         <v>45596</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -40080,7 +40080,7 @@
         <v>46199</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -40153,7 +40153,7 @@
         <v>45077</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -40226,7 +40226,7 @@
         <v>46203</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -40299,7 +40299,7 @@
         <v>45579</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -40372,7 +40372,7 @@
         <v>46154</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -40450,7 +40450,7 @@
         <v>44966</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -40523,7 +40523,7 @@
         <v>45774</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -40596,7 +40596,7 @@
         <v>46134</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -40669,7 +40669,7 @@
         <v>45774</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -40742,7 +40742,7 @@
         <v>45147</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -40815,7 +40815,7 @@
         <v>45967</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -40888,7 +40888,7 @@
         <v>46086</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -40961,7 +40961,7 @@
         <v>45579</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -41034,7 +41034,7 @@
         <v>46086</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -41107,7 +41107,7 @@
         <v>45155</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -41180,7 +41180,7 @@
         <v>46206</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -41253,7 +41253,7 @@
         <v>46205</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -41326,7 +41326,7 @@
         <v>45231</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -41399,7 +41399,7 @@
         <v>45230</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -41472,7 +41472,7 @@
         <v>46206</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -41545,7 +41545,7 @@
         <v>46206</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -41618,7 +41618,7 @@
         <v>45231</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -41691,7 +41691,7 @@
         <v>46206</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -41764,7 +41764,7 @@
         <v>44509</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -41842,7 +41842,7 @@
         <v>46206</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -41915,7 +41915,7 @@
         <v>45938</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -41993,7 +41993,7 @@
         <v>46008</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -42066,7 +42066,7 @@
         <v>45341</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -42139,7 +42139,7 @@
         <v>46206</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -42212,7 +42212,7 @@
         <v>46206</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -42285,7 +42285,7 @@
         <v>46206</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -42358,7 +42358,7 @@
         <v>46206</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -42431,7 +42431,7 @@
         <v>45483</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -42504,7 +42504,7 @@
         <v>45229</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -42577,7 +42577,7 @@
         <v>44740</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -42650,7 +42650,7 @@
         <v>45245</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -42728,7 +42728,7 @@
         <v>45082</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -42801,7 +42801,7 @@
         <v>45655</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -42874,7 +42874,7 @@
         <v>44988</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -42952,7 +42952,7 @@
         <v>45568</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -43025,7 +43025,7 @@
         <v>45568</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -43098,7 +43098,7 @@
         <v>45485</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -43171,7 +43171,7 @@
         <v>45579</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -43244,7 +43244,7 @@
         <v>45748</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -43317,7 +43317,7 @@
         <v>45492</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -43390,7 +43390,7 @@
         <v>45230</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -43463,7 +43463,7 @@
         <v>46147</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -43541,7 +43541,7 @@
         <v>44986</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -43614,7 +43614,7 @@
         <v>44953</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -43687,7 +43687,7 @@
         <v>46272</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -43765,7 +43765,7 @@
         <v>46272</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -43843,7 +43843,7 @@
         <v>45092</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -43916,7 +43916,7 @@
         <v>45142</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -43989,7 +43989,7 @@
         <v>45300</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -44067,7 +44067,7 @@
         <v>44509</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -44140,7 +44140,7 @@
         <v>46272</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -44218,7 +44218,7 @@
         <v>45152</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -44291,7 +44291,7 @@
         <v>45209</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -44364,7 +44364,7 @@
         <v>46275</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -44437,7 +44437,7 @@
         <v>46274</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -44515,7 +44515,7 @@
         <v>46275</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -44588,7 +44588,7 @@
         <v>46275</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -44661,7 +44661,7 @@
         <v>44858</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -44734,7 +44734,7 @@
         <v>45275</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -44812,7 +44812,7 @@
         <v>45639</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -44885,7 +44885,7 @@
         <v>46272</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -44963,7 +44963,7 @@
         <v>45427</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -45036,7 +45036,7 @@
         <v>44628</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -45109,7 +45109,7 @@
         <v>46272</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -45187,7 +45187,7 @@
         <v>46279</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -45260,7 +45260,7 @@
         <v>44986</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -45333,7 +45333,7 @@
         <v>44944</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -45406,7 +45406,7 @@
         <v>45655</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -45479,7 +45479,7 @@
         <v>45655</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -45552,7 +45552,7 @@
         <v>46239</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -45625,7 +45625,7 @@
         <v>46239</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -45698,7 +45698,7 @@
         <v>45597</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -45771,7 +45771,7 @@
         <v>46240</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -45849,7 +45849,7 @@
         <v>45219</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -45927,7 +45927,7 @@
         <v>44994</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -46000,7 +46000,7 @@
         <v>45555</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -46073,7 +46073,7 @@
         <v>45703</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -46146,7 +46146,7 @@
         <v>45205</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -46219,7 +46219,7 @@
         <v>44641</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -46297,7 +46297,7 @@
         <v>45655</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -46370,7 +46370,7 @@
         <v>44767</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -46443,7 +46443,7 @@
         <v>44909</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -46516,7 +46516,7 @@
         <v>44909</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -46589,7 +46589,7 @@
         <v>45230</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -46662,7 +46662,7 @@
         <v>45265</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -46735,7 +46735,7 @@
         <v>46272</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -46813,7 +46813,7 @@
         <v>45294</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -46886,7 +46886,7 @@
         <v>45429</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -46959,7 +46959,7 @@
         <v>45299</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -47032,7 +47032,7 @@
         <v>46245</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -47105,7 +47105,7 @@
         <v>45491</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -47178,7 +47178,7 @@
         <v>46289</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -47256,7 +47256,7 @@
         <v>46289</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -47334,7 +47334,7 @@
         <v>46288</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -47407,7 +47407,7 @@
         <v>45274</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -47480,7 +47480,7 @@
         <v>46288</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -47553,7 +47553,7 @@
         <v>45266</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -47626,7 +47626,7 @@
         <v>45268</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -47699,7 +47699,7 @@
         <v>46288</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -47772,7 +47772,7 @@
         <v>45300</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -47850,7 +47850,7 @@
         <v>46245</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -47923,7 +47923,7 @@
         <v>46288</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -47996,7 +47996,7 @@
         <v>45342</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -48069,7 +48069,7 @@
         <v>45364</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -48147,7 +48147,7 @@
         <v>45275</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -48220,7 +48220,7 @@
         <v>45275</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -48298,7 +48298,7 @@
         <v>45275</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -48371,7 +48371,7 @@
         <v>45153</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -48449,7 +48449,7 @@
         <v>45397</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -48522,7 +48522,7 @@
         <v>46248</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -48600,7 +48600,7 @@
         <v>46248</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -48678,7 +48678,7 @@
         <v>46248</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -48756,7 +48756,7 @@
         <v>46248</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -48834,7 +48834,7 @@
         <v>46290</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -48907,7 +48907,7 @@
         <v>46290</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -48980,7 +48980,7 @@
         <v>45404</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -49053,7 +49053,7 @@
         <v>44810</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -49126,7 +49126,7 @@
         <v>45491</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -49199,7 +49199,7 @@
         <v>46248</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -49277,7 +49277,7 @@
         <v>46248</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -49355,7 +49355,7 @@
         <v>44812</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -49428,7 +49428,7 @@
         <v>44794</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -49501,7 +49501,7 @@
         <v>44643</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -49574,7 +49574,7 @@
         <v>45299</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -49647,7 +49647,7 @@
         <v>46294</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -49725,7 +49725,7 @@
         <v>46294</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -49803,7 +49803,7 @@
         <v>46294</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -49881,7 +49881,7 @@
         <v>46294</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -49954,7 +49954,7 @@
         <v>45049</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -50027,7 +50027,7 @@
         <v>45048</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -50100,7 +50100,7 @@
         <v>46294</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -50178,7 +50178,7 @@
         <v>46294</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -50256,7 +50256,7 @@
         <v>45774</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -50329,7 +50329,7 @@
         <v>44859</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -50407,7 +50407,7 @@
         <v>46254</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -50480,7 +50480,7 @@
         <v>45275</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -50558,7 +50558,7 @@
         <v>45671</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -50631,7 +50631,7 @@
         <v>45779</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -50704,7 +50704,7 @@
         <v>45779</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -50777,7 +50777,7 @@
         <v>45785</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -50850,7 +50850,7 @@
         <v>46301</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -50923,7 +50923,7 @@
         <v>45359</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -50996,7 +50996,7 @@
         <v>45342</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -51069,7 +51069,7 @@
         <v>45573</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -51142,7 +51142,7 @@
         <v>46303</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -51215,7 +51215,7 @@
         <v>46030</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -51293,7 +51293,7 @@
         <v>46259</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -51371,7 +51371,7 @@
         <v>46259</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -51449,7 +51449,7 @@
         <v>46030</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -51527,7 +51527,7 @@
         <v>45664</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -51600,7 +51600,7 @@
         <v>46302</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -51673,7 +51673,7 @@
         <v>45546</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -51746,7 +51746,7 @@
         <v>45246</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -51819,7 +51819,7 @@
         <v>45483</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -51892,7 +51892,7 @@
         <v>46303</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -51965,7 +51965,7 @@
         <v>45793</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -52038,7 +52038,7 @@
         <v>46307</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -52116,7 +52116,7 @@
         <v>45593</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -52189,7 +52189,7 @@
         <v>46264</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -52262,7 +52262,7 @@
         <v>45737</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -52335,7 +52335,7 @@
         <v>46307</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -52413,7 +52413,7 @@
         <v>45573</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -52486,7 +52486,7 @@
         <v>46293</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -52559,7 +52559,7 @@
         <v>46266</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -52632,7 +52632,7 @@
         <v>46266</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -52705,7 +52705,7 @@
         <v>46267</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -52783,7 +52783,7 @@
         <v>46267</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -52861,7 +52861,7 @@
         <v>45804</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -52934,7 +52934,7 @@
         <v>46309</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -53012,7 +53012,7 @@
         <v>46265</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -53085,7 +53085,7 @@
         <v>46309</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -53163,7 +53163,7 @@
         <v>46265</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -53236,7 +53236,7 @@
         <v>46310</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -53309,7 +53309,7 @@
         <v>46269</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -53387,7 +53387,7 @@
         <v>46269</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -53465,7 +53465,7 @@
         <v>46269</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -53543,7 +53543,7 @@
         <v>45816</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -53616,7 +53616,7 @@
         <v>46275</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -53689,7 +53689,7 @@
         <v>46267</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -53767,7 +53767,7 @@
         <v>46269</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -53845,7 +53845,7 @@
         <v>45821</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -53918,7 +53918,7 @@
         <v>46267</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -53996,7 +53996,7 @@
         <v>46269</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -54074,7 +54074,7 @@
         <v>46269</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -54152,7 +54152,7 @@
         <v>46267</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -54230,7 +54230,7 @@
         <v>46269</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -54308,7 +54308,7 @@
         <v>45614</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -54381,7 +54381,7 @@
         <v>45655</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -54454,7 +54454,7 @@
         <v>45852</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -54527,7 +54527,7 @@
         <v>45860</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -54600,7 +54600,7 @@
         <v>45860</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -54673,7 +54673,7 @@
         <v>45804</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -54746,7 +54746,7 @@
         <v>45541</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -54819,7 +54819,7 @@
         <v>44855</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -54892,7 +54892,7 @@
         <v>45133</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -54965,7 +54965,7 @@
         <v>45541</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -55038,7 +55038,7 @@
         <v>45699</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -55111,7 +55111,7 @@
         <v>46040</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -55184,7 +55184,7 @@
         <v>46108</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -55257,7 +55257,7 @@
         <v>46183</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -55330,7 +55330,7 @@
         <v>46307</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>

--- a/Översikt LINKÖPING.xlsx
+++ b/Översikt LINKÖPING.xlsx
@@ -601,7 +601,7 @@
         <v>45756</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -741,7 +741,7 @@
         <v>45644</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>44679</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>45293</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>46090</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>44855</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
         <v>45278</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1505,7 +1505,7 @@
         <v>46275</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1634,7 +1634,7 @@
         <v>44368</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1750,7 +1750,7 @@
         <v>46090</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1863,7 +1863,7 @@
         <v>45720</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1975,7 +1975,7 @@
         <v>45720</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         <v>46206</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2206,7 +2206,7 @@
         <v>45860</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2317,7 +2317,7 @@
         <v>45804</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2432,7 +2432,7 @@
         <v>45280</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2548,7 +2548,7 @@
         <v>45756</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2662,7 +2662,7 @@
         <v>46090</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2772,7 +2772,7 @@
         <v>46275</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2890,7 +2890,7 @@
         <v>46146</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2999,7 +2999,7 @@
         <v>45068</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3113,7 +3113,7 @@
         <v>44949</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3222,7 +3222,7 @@
         <v>44588</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3335,7 +3335,7 @@
         <v>44679</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3449,7 +3449,7 @@
         <v>43997</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3558,7 +3558,7 @@
         <v>44679</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3675,7 +3675,7 @@
         <v>44745</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3783,7 +3783,7 @@
         <v>45932</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3896,7 +3896,7 @@
         <v>45943</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4004,7 +4004,7 @@
         <v>46050</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4112,7 +4112,7 @@
         <v>46079</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4220,7 +4220,7 @@
         <v>45555</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4333,7 +4333,7 @@
         <v>46107</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4450,7 +4450,7 @@
         <v>45714</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4563,7 +4563,7 @@
         <v>45089</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4671,7 +4671,7 @@
         <v>44834</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4779,7 +4779,7 @@
         <v>44679</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4891,7 +4891,7 @@
         <v>44679</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5003,7 +5003,7 @@
         <v>44855</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5114,7 +5114,7 @@
         <v>44930</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5230,7 +5230,7 @@
         <v>45153</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5342,7 +5342,7 @@
         <v>44830</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5449,7 +5449,7 @@
         <v>44916</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5561,7 +5561,7 @@
         <v>46146</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5672,7 +5672,7 @@
         <v>45941</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5783,7 +5783,7 @@
         <v>45236</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5894,7 +5894,7 @@
         <v>45294</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6001,7 +6001,7 @@
         <v>46087</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6112,7 +6112,7 @@
         <v>45774</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6223,7 +6223,7 @@
         <v>46206</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6330,7 +6330,7 @@
         <v>45163</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6437,7 +6437,7 @@
         <v>45217</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6549,7 +6549,7 @@
         <v>46289</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6669,7 +6669,7 @@
         <v>45621</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6776,7 +6776,7 @@
         <v>45664</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6883,7 +6883,7 @@
         <v>44848</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6989,7 +6989,7 @@
         <v>44498</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7099,7 +7099,7 @@
         <v>45191</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7210,7 +7210,7 @@
         <v>45216</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7316,7 +7316,7 @@
         <v>44909</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7426,7 +7426,7 @@
         <v>45572</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7532,7 +7532,7 @@
         <v>45071</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7643,7 +7643,7 @@
         <v>45712</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7754,7 +7754,7 @@
         <v>44597</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7860,7 +7860,7 @@
         <v>45745</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7970,7 +7970,7 @@
         <v>45932</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8081,7 +8081,7 @@
         <v>44487</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8192,7 +8192,7 @@
         <v>44936</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8298,7 +8298,7 @@
         <v>44487</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8409,7 +8409,7 @@
         <v>46107</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8520,7 +8520,7 @@
         <v>46153</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8626,7 +8626,7 @@
         <v>45461</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8732,7 +8732,7 @@
         <v>45140</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8842,7 +8842,7 @@
         <v>45595</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8948,7 +8948,7 @@
         <v>45554</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9063,7 +9063,7 @@
         <v>45547</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9173,7 +9173,7 @@
         <v>46043</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9288,7 +9288,7 @@
         <v>45774</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9394,7 +9394,7 @@
         <v>45639</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9500,7 +9500,7 @@
         <v>45244</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9611,7 +9611,7 @@
         <v>44930</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9722,7 +9722,7 @@
         <v>45176</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9828,7 +9828,7 @@
         <v>45148</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9934,7 +9934,7 @@
         <v>46178</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10040,7 +10040,7 @@
         <v>45621</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10146,7 +10146,7 @@
         <v>45774</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10256,7 +10256,7 @@
         <v>46259</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10367,7 +10367,7 @@
         <v>45804</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10473,7 +10473,7 @@
         <v>44159</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10584,7 +10584,7 @@
         <v>44537</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10694,7 +10694,7 @@
         <v>44938</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10799,7 +10799,7 @@
         <v>45665</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10909,7 +10909,7 @@
         <v>44768</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11014,7 +11014,7 @@
         <v>45141</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11119,7 +11119,7 @@
         <v>45463</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11224,7 +11224,7 @@
         <v>45541</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11329,7 +11329,7 @@
         <v>45222</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11443,7 +11443,7 @@
         <v>45243</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11553,7 +11553,7 @@
         <v>45604</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11663,7 +11663,7 @@
         <v>44929</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11768,7 +11768,7 @@
         <v>45554</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11878,7 +11878,7 @@
         <v>45965</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11988,7 +11988,7 @@
         <v>45246</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12098,7 +12098,7 @@
         <v>45915</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12208,7 +12208,7 @@
         <v>45579</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12313,7 +12313,7 @@
         <v>45244</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12423,7 +12423,7 @@
         <v>45941</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12528,7 +12528,7 @@
         <v>44889</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12633,7 +12633,7 @@
         <v>45968</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12738,7 +12738,7 @@
         <v>45988</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12848,7 +12848,7 @@
         <v>45604</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12958,7 +12958,7 @@
         <v>46175</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13063,7 +13063,7 @@
         <v>45071</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13173,7 +13173,7 @@
         <v>46079</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13278,7 +13278,7 @@
         <v>45308</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13388,7 +13388,7 @@
         <v>45442</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13497,7 +13497,7 @@
         <v>44945</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13602,7 +13602,7 @@
         <v>45994</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13707,7 +13707,7 @@
         <v>45412</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13812,7 +13812,7 @@
         <v>45244</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13922,7 +13922,7 @@
         <v>44945</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14027,7 +14027,7 @@
         <v>44881</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14132,7 +14132,7 @@
         <v>45460</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14237,7 +14237,7 @@
         <v>46206</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14342,7 +14342,7 @@
         <v>44950</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14447,7 +14447,7 @@
         <v>45294</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14557,7 +14557,7 @@
         <v>45266</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14662,7 +14662,7 @@
         <v>45111</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14767,7 +14767,7 @@
         <v>44949</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14872,7 +14872,7 @@
         <v>46289</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14982,7 +14982,7 @@
         <v>45491</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -15087,7 +15087,7 @@
         <v>44496</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15197,7 +15197,7 @@
         <v>45176</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15302,7 +15302,7 @@
         <v>46259</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15412,7 +15412,7 @@
         <v>45369</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15517,7 +15517,7 @@
         <v>46302</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -15622,7 +15622,7 @@
         <v>46264</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -15727,7 +15727,7 @@
         <v>46308</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -15841,7 +15841,7 @@
         <v>45812</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -15946,7 +15946,7 @@
         <v>45816</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -16051,7 +16051,7 @@
         <v>45153</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -16161,7 +16161,7 @@
         <v>44523</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -16234,7 +16234,7 @@
         <v>44608</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -16307,7 +16307,7 @@
         <v>44510</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -16380,7 +16380,7 @@
         <v>44488</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -16453,7 +16453,7 @@
         <v>44764</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -16526,7 +16526,7 @@
         <v>44855</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -16604,7 +16604,7 @@
         <v>44573</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -16677,7 +16677,7 @@
         <v>44846</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -16750,7 +16750,7 @@
         <v>44496</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -16823,7 +16823,7 @@
         <v>44782</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -16896,7 +16896,7 @@
         <v>44853</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -16969,7 +16969,7 @@
         <v>44679</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -17047,7 +17047,7 @@
         <v>44777</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -17120,7 +17120,7 @@
         <v>44753</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -17198,7 +17198,7 @@
         <v>44510</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -17271,7 +17271,7 @@
         <v>44487</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -17349,7 +17349,7 @@
         <v>44487</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -17427,7 +17427,7 @@
         <v>44823</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -17500,7 +17500,7 @@
         <v>44515</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -17578,7 +17578,7 @@
         <v>44767</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -17651,7 +17651,7 @@
         <v>44719</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -17729,7 +17729,7 @@
         <v>44487</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -17807,7 +17807,7 @@
         <v>44776</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -17880,7 +17880,7 @@
         <v>44692</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -17953,7 +17953,7 @@
         <v>44803</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -18026,7 +18026,7 @@
         <v>44882</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -18104,7 +18104,7 @@
         <v>44588</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -18177,7 +18177,7 @@
         <v>44743</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -18250,7 +18250,7 @@
         <v>44574</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -18323,7 +18323,7 @@
         <v>44571</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -18396,7 +18396,7 @@
         <v>44841</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -18469,7 +18469,7 @@
         <v>44537</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -18542,7 +18542,7 @@
         <v>44809</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -18615,7 +18615,7 @@
         <v>44884</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -18688,7 +18688,7 @@
         <v>44884</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -18761,7 +18761,7 @@
         <v>44628</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -18834,7 +18834,7 @@
         <v>44525</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -18907,7 +18907,7 @@
         <v>44525</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -18980,7 +18980,7 @@
         <v>44627</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -19053,7 +19053,7 @@
         <v>44785</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -19126,7 +19126,7 @@
         <v>44643</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -19199,7 +19199,7 @@
         <v>44720</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -19272,7 +19272,7 @@
         <v>44595</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -19350,7 +19350,7 @@
         <v>44743</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -19423,7 +19423,7 @@
         <v>44497</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -19496,7 +19496,7 @@
         <v>44848</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -19569,7 +19569,7 @@
         <v>44776</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -19642,7 +19642,7 @@
         <v>44826</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -19715,7 +19715,7 @@
         <v>44791</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -19788,7 +19788,7 @@
         <v>44498</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -19861,7 +19861,7 @@
         <v>44638</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -19934,7 +19934,7 @@
         <v>44812</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -20007,7 +20007,7 @@
         <v>44796</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -20085,7 +20085,7 @@
         <v>44794</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -20158,7 +20158,7 @@
         <v>45274</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -20231,7 +20231,7 @@
         <v>45236</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -20309,7 +20309,7 @@
         <v>45477</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -20387,7 +20387,7 @@
         <v>44945</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -20460,7 +20460,7 @@
         <v>45728</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -20533,7 +20533,7 @@
         <v>45435</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -20606,7 +20606,7 @@
         <v>45457</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -20679,7 +20679,7 @@
         <v>45294</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -20752,7 +20752,7 @@
         <v>45089</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -20830,7 +20830,7 @@
         <v>45140</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -20903,7 +20903,7 @@
         <v>44767</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -20976,7 +20976,7 @@
         <v>44767</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -21049,7 +21049,7 @@
         <v>44897</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -21127,7 +21127,7 @@
         <v>44939</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -21200,7 +21200,7 @@
         <v>45217</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -21273,7 +21273,7 @@
         <v>45217</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -21346,7 +21346,7 @@
         <v>45182</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -21419,7 +21419,7 @@
         <v>45238</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -21492,7 +21492,7 @@
         <v>45225</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -21565,7 +21565,7 @@
         <v>45225</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -21638,7 +21638,7 @@
         <v>45142</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -21711,7 +21711,7 @@
         <v>45302</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -21784,7 +21784,7 @@
         <v>45225</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -21862,7 +21862,7 @@
         <v>45623</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -21935,7 +21935,7 @@
         <v>44498</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -22008,7 +22008,7 @@
         <v>44498</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -22081,7 +22081,7 @@
         <v>45275</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -22154,7 +22154,7 @@
         <v>45133</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -22227,7 +22227,7 @@
         <v>45545</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -22300,7 +22300,7 @@
         <v>44909</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -22373,7 +22373,7 @@
         <v>44909</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -22446,7 +22446,7 @@
         <v>44903</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -22519,7 +22519,7 @@
         <v>44930</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -22597,7 +22597,7 @@
         <v>45030</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -22670,7 +22670,7 @@
         <v>45161</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -22743,7 +22743,7 @@
         <v>45309</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -22816,7 +22816,7 @@
         <v>45160</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -22889,7 +22889,7 @@
         <v>45111</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -22962,7 +22962,7 @@
         <v>45755</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -23035,7 +23035,7 @@
         <v>45624</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -23108,7 +23108,7 @@
         <v>45294</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -23181,7 +23181,7 @@
         <v>45111</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -23254,7 +23254,7 @@
         <v>45491</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -23327,7 +23327,7 @@
         <v>44894</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -23400,7 +23400,7 @@
         <v>45750</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -23473,7 +23473,7 @@
         <v>44683</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -23546,7 +23546,7 @@
         <v>45275</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -23619,7 +23619,7 @@
         <v>45274</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -23692,7 +23692,7 @@
         <v>45146</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -23770,7 +23770,7 @@
         <v>44888</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -23843,7 +23843,7 @@
         <v>44487</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -23921,7 +23921,7 @@
         <v>45456</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -23994,7 +23994,7 @@
         <v>45623</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -24067,7 +24067,7 @@
         <v>45623</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -24140,7 +24140,7 @@
         <v>44949</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -24213,7 +24213,7 @@
         <v>45013</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -24286,7 +24286,7 @@
         <v>44558</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -24359,7 +24359,7 @@
         <v>44743</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -24432,7 +24432,7 @@
         <v>45125</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -24505,7 +24505,7 @@
         <v>45610</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -24578,7 +24578,7 @@
         <v>44865</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -24651,7 +24651,7 @@
         <v>45230</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -24724,7 +24724,7 @@
         <v>45678</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -24797,7 +24797,7 @@
         <v>45147</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -24870,7 +24870,7 @@
         <v>45359</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -24943,7 +24943,7 @@
         <v>45208</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -25016,7 +25016,7 @@
         <v>44600</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -25089,7 +25089,7 @@
         <v>45202</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -25162,7 +25162,7 @@
         <v>45729</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -25235,7 +25235,7 @@
         <v>45021</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -25308,7 +25308,7 @@
         <v>45712</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -25381,7 +25381,7 @@
         <v>46099</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -25454,7 +25454,7 @@
         <v>45281</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -25532,7 +25532,7 @@
         <v>44783</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -25605,7 +25605,7 @@
         <v>44928</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -25678,7 +25678,7 @@
         <v>44933</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -25751,7 +25751,7 @@
         <v>44945</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -25824,7 +25824,7 @@
         <v>44768</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -25897,7 +25897,7 @@
         <v>44909</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -25970,7 +25970,7 @@
         <v>44862</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -26043,7 +26043,7 @@
         <v>44498</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -26116,7 +26116,7 @@
         <v>44509</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -26194,7 +26194,7 @@
         <v>44889</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -26272,7 +26272,7 @@
         <v>45203</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -26345,7 +26345,7 @@
         <v>44665</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -26423,7 +26423,7 @@
         <v>44860</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -26496,7 +26496,7 @@
         <v>45905</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -26569,7 +26569,7 @@
         <v>46086</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -26642,7 +26642,7 @@
         <v>46057</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -26715,7 +26715,7 @@
         <v>44795</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -26788,7 +26788,7 @@
         <v>45121</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -26861,7 +26861,7 @@
         <v>44933</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -26934,7 +26934,7 @@
         <v>44942</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -27007,7 +27007,7 @@
         <v>45293</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -27080,7 +27080,7 @@
         <v>45901</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -27153,7 +27153,7 @@
         <v>45195</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -27226,7 +27226,7 @@
         <v>45111</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -27299,7 +27299,7 @@
         <v>45555</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -27377,7 +27377,7 @@
         <v>45082</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -27450,7 +27450,7 @@
         <v>45082</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -27523,7 +27523,7 @@
         <v>45590</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -27596,7 +27596,7 @@
         <v>45244</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -27674,7 +27674,7 @@
         <v>44498</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -27747,7 +27747,7 @@
         <v>45915</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -27820,7 +27820,7 @@
         <v>44936</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -27893,7 +27893,7 @@
         <v>45912</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -27971,7 +27971,7 @@
         <v>44931</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -28044,7 +28044,7 @@
         <v>45912</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -28122,7 +28122,7 @@
         <v>45912</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -28200,7 +28200,7 @@
         <v>45678</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -28273,7 +28273,7 @@
         <v>44623</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -28346,7 +28346,7 @@
         <v>46147</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -28424,7 +28424,7 @@
         <v>45111</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -28502,7 +28502,7 @@
         <v>45919</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -28575,7 +28575,7 @@
         <v>46147</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -28653,7 +28653,7 @@
         <v>44923</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -28731,7 +28731,7 @@
         <v>45489</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -28804,7 +28804,7 @@
         <v>45922</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -28882,7 +28882,7 @@
         <v>45106</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -28955,7 +28955,7 @@
         <v>45106</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -29028,7 +29028,7 @@
         <v>45296</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -29101,7 +29101,7 @@
         <v>46145</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -29174,7 +29174,7 @@
         <v>45069</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -29247,7 +29247,7 @@
         <v>44501</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -29320,7 +29320,7 @@
         <v>45392</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -29393,7 +29393,7 @@
         <v>45555</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -29471,7 +29471,7 @@
         <v>45644</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -29544,7 +29544,7 @@
         <v>44944</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -29617,7 +29617,7 @@
         <v>45928</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -29690,7 +29690,7 @@
         <v>45930</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -29763,7 +29763,7 @@
         <v>45932</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -29841,7 +29841,7 @@
         <v>45105</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -29919,7 +29919,7 @@
         <v>46153</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -29992,7 +29992,7 @@
         <v>45261</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -30065,7 +30065,7 @@
         <v>45237</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -30138,7 +30138,7 @@
         <v>45140</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -30211,7 +30211,7 @@
         <v>44803</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -30284,7 +30284,7 @@
         <v>45941</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -30357,7 +30357,7 @@
         <v>45945</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -30430,7 +30430,7 @@
         <v>45086</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -30503,7 +30503,7 @@
         <v>46154</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -30581,7 +30581,7 @@
         <v>44987</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -30654,7 +30654,7 @@
         <v>46154</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -30732,7 +30732,7 @@
         <v>44565</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -30805,7 +30805,7 @@
         <v>46154</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -30883,7 +30883,7 @@
         <v>44690</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -30956,7 +30956,7 @@
         <v>45952</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -31029,7 +31029,7 @@
         <v>46154</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -31107,7 +31107,7 @@
         <v>44768</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -31180,7 +31180,7 @@
         <v>46154</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -31258,7 +31258,7 @@
         <v>45957</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -31331,7 +31331,7 @@
         <v>46154</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -31409,7 +31409,7 @@
         <v>44888</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -31482,7 +31482,7 @@
         <v>45957</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -31555,7 +31555,7 @@
         <v>45957</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -31628,7 +31628,7 @@
         <v>44986</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -31701,7 +31701,7 @@
         <v>45737</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -31774,7 +31774,7 @@
         <v>45729</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -31852,7 +31852,7 @@
         <v>44967</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -31930,7 +31930,7 @@
         <v>45379</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -32003,7 +32003,7 @@
         <v>45968</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -32076,7 +32076,7 @@
         <v>45968</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -32149,7 +32149,7 @@
         <v>45774</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -32222,7 +32222,7 @@
         <v>45968</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -32295,7 +32295,7 @@
         <v>45177</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -32368,7 +32368,7 @@
         <v>45116</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -32441,7 +32441,7 @@
         <v>45146</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -32519,7 +32519,7 @@
         <v>45973</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -32592,7 +32592,7 @@
         <v>45973</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -32665,7 +32665,7 @@
         <v>45153</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -32743,7 +32743,7 @@
         <v>45230</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -32816,7 +32816,7 @@
         <v>45833</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -32889,7 +32889,7 @@
         <v>45977</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -32967,7 +32967,7 @@
         <v>45306</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -33040,7 +33040,7 @@
         <v>44862</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -33113,7 +33113,7 @@
         <v>45470</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -33191,7 +33191,7 @@
         <v>44911</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -33264,7 +33264,7 @@
         <v>45187</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -33342,7 +33342,7 @@
         <v>44930</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -33420,7 +33420,7 @@
         <v>44994</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -33493,7 +33493,7 @@
         <v>45044</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -33566,7 +33566,7 @@
         <v>45300</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -33644,7 +33644,7 @@
         <v>45392</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -33722,7 +33722,7 @@
         <v>45655</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -33795,7 +33795,7 @@
         <v>45086</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -33868,7 +33868,7 @@
         <v>45989</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -33941,7 +33941,7 @@
         <v>45755</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -34014,7 +34014,7 @@
         <v>45755</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -34087,7 +34087,7 @@
         <v>45755</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -34160,7 +34160,7 @@
         <v>45117</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -34233,7 +34233,7 @@
         <v>45374</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -34306,7 +34306,7 @@
         <v>45996</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -34384,7 +34384,7 @@
         <v>44498</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -34457,7 +34457,7 @@
         <v>46000</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -34535,7 +34535,7 @@
         <v>45337</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -34608,7 +34608,7 @@
         <v>45294</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -34686,7 +34686,7 @@
         <v>45625</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -34759,7 +34759,7 @@
         <v>44993</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -34832,7 +34832,7 @@
         <v>44508</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -34905,7 +34905,7 @@
         <v>45741</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -34978,7 +34978,7 @@
         <v>45320</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -35051,7 +35051,7 @@
         <v>45266</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -35129,7 +35129,7 @@
         <v>45695</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -35202,7 +35202,7 @@
         <v>45231</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -35275,7 +35275,7 @@
         <v>44949</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -35348,7 +35348,7 @@
         <v>44882</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -35421,7 +35421,7 @@
         <v>44882</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -35494,7 +35494,7 @@
         <v>46010</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -35567,7 +35567,7 @@
         <v>44930</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -35645,7 +35645,7 @@
         <v>45268</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -35718,7 +35718,7 @@
         <v>45005</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -35791,7 +35791,7 @@
         <v>45092</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -35864,7 +35864,7 @@
         <v>46030</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -35937,7 +35937,7 @@
         <v>46030</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -36010,7 +36010,7 @@
         <v>46030</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -36083,7 +36083,7 @@
         <v>45275</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -36156,7 +36156,7 @@
         <v>46030</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -36229,7 +36229,7 @@
         <v>46030</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -36302,7 +36302,7 @@
         <v>46035</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -36375,7 +36375,7 @@
         <v>45275</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -36453,7 +36453,7 @@
         <v>45275</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -36531,7 +36531,7 @@
         <v>46035</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -36604,7 +36604,7 @@
         <v>46038</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -36677,7 +36677,7 @@
         <v>45411</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -36750,7 +36750,7 @@
         <v>44658</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -36823,7 +36823,7 @@
         <v>45217</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -36896,7 +36896,7 @@
         <v>46181</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -36969,7 +36969,7 @@
         <v>44873</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -37047,7 +37047,7 @@
         <v>45096</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -37125,7 +37125,7 @@
         <v>46055</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -37198,7 +37198,7 @@
         <v>46055</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -37271,7 +37271,7 @@
         <v>46181</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -37344,7 +37344,7 @@
         <v>45741</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -37417,7 +37417,7 @@
         <v>44775</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -37490,7 +37490,7 @@
         <v>45655</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -37563,7 +37563,7 @@
         <v>45037</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -37641,7 +37641,7 @@
         <v>45271</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -37714,7 +37714,7 @@
         <v>45177</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -37787,7 +37787,7 @@
         <v>45161</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -37860,7 +37860,7 @@
         <v>44958</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -37933,7 +37933,7 @@
         <v>44936</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -38006,7 +38006,7 @@
         <v>46077</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -38079,7 +38079,7 @@
         <v>46079</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -38152,7 +38152,7 @@
         <v>44638</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -38225,7 +38225,7 @@
         <v>46087</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -38298,7 +38298,7 @@
         <v>45453</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -38371,7 +38371,7 @@
         <v>45293</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -38444,7 +38444,7 @@
         <v>44599</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -38517,7 +38517,7 @@
         <v>46085</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -38590,7 +38590,7 @@
         <v>44776</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -38663,7 +38663,7 @@
         <v>46098</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -38736,7 +38736,7 @@
         <v>46094</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -38809,7 +38809,7 @@
         <v>44970</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -38887,7 +38887,7 @@
         <v>46099</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -38965,7 +38965,7 @@
         <v>45120</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -39038,7 +39038,7 @@
         <v>44608</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -39116,7 +39116,7 @@
         <v>45475</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -39189,7 +39189,7 @@
         <v>44824</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -39262,7 +39262,7 @@
         <v>45604</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -39340,7 +39340,7 @@
         <v>44865</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -39418,7 +39418,7 @@
         <v>45268</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -39491,7 +39491,7 @@
         <v>45106</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -39564,7 +39564,7 @@
         <v>45090</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -39637,7 +39637,7 @@
         <v>44937</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -39710,7 +39710,7 @@
         <v>45111</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -39788,7 +39788,7 @@
         <v>44994</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -39861,7 +39861,7 @@
         <v>46120</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -39934,7 +39934,7 @@
         <v>44945</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -40007,7 +40007,7 @@
         <v>45596</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -40080,7 +40080,7 @@
         <v>46199</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -40153,7 +40153,7 @@
         <v>45077</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -40226,7 +40226,7 @@
         <v>46203</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -40299,7 +40299,7 @@
         <v>45579</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -40372,7 +40372,7 @@
         <v>46154</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -40450,7 +40450,7 @@
         <v>44966</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -40523,7 +40523,7 @@
         <v>45774</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -40596,7 +40596,7 @@
         <v>46134</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -40669,7 +40669,7 @@
         <v>45774</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -40742,7 +40742,7 @@
         <v>45147</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -40815,7 +40815,7 @@
         <v>45967</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -40888,7 +40888,7 @@
         <v>46086</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -40961,7 +40961,7 @@
         <v>45579</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -41034,7 +41034,7 @@
         <v>46086</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -41107,7 +41107,7 @@
         <v>45155</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -41180,7 +41180,7 @@
         <v>46206</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -41253,7 +41253,7 @@
         <v>46205</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -41326,7 +41326,7 @@
         <v>45231</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -41399,7 +41399,7 @@
         <v>45230</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -41472,7 +41472,7 @@
         <v>46206</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -41545,7 +41545,7 @@
         <v>46206</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -41618,7 +41618,7 @@
         <v>45231</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -41691,7 +41691,7 @@
         <v>46206</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -41764,7 +41764,7 @@
         <v>44509</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -41842,7 +41842,7 @@
         <v>46206</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -41915,7 +41915,7 @@
         <v>45938</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -41993,7 +41993,7 @@
         <v>46008</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -42066,7 +42066,7 @@
         <v>45341</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -42139,7 +42139,7 @@
         <v>46206</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -42212,7 +42212,7 @@
         <v>46206</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -42285,7 +42285,7 @@
         <v>46206</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -42358,7 +42358,7 @@
         <v>46206</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -42431,7 +42431,7 @@
         <v>45483</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -42504,7 +42504,7 @@
         <v>45229</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -42577,7 +42577,7 @@
         <v>44740</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -42650,7 +42650,7 @@
         <v>45245</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -42728,7 +42728,7 @@
         <v>45082</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -42801,7 +42801,7 @@
         <v>45655</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -42874,7 +42874,7 @@
         <v>44988</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -42952,7 +42952,7 @@
         <v>45568</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -43025,7 +43025,7 @@
         <v>45568</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -43098,7 +43098,7 @@
         <v>45485</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -43171,7 +43171,7 @@
         <v>45579</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -43244,7 +43244,7 @@
         <v>45748</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -43317,7 +43317,7 @@
         <v>45492</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -43390,7 +43390,7 @@
         <v>45230</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -43463,7 +43463,7 @@
         <v>46147</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -43541,7 +43541,7 @@
         <v>44986</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -43614,7 +43614,7 @@
         <v>44953</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -43687,7 +43687,7 @@
         <v>46272</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -43765,7 +43765,7 @@
         <v>46272</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -43843,7 +43843,7 @@
         <v>45092</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -43916,7 +43916,7 @@
         <v>45142</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -43989,7 +43989,7 @@
         <v>45300</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -44067,7 +44067,7 @@
         <v>44509</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -44140,7 +44140,7 @@
         <v>46272</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -44218,7 +44218,7 @@
         <v>45152</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -44291,7 +44291,7 @@
         <v>45209</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -44364,7 +44364,7 @@
         <v>46275</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -44437,7 +44437,7 @@
         <v>46274</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -44515,7 +44515,7 @@
         <v>46275</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -44588,7 +44588,7 @@
         <v>46275</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -44661,7 +44661,7 @@
         <v>44858</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -44734,7 +44734,7 @@
         <v>45275</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -44812,7 +44812,7 @@
         <v>45639</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -44885,7 +44885,7 @@
         <v>46272</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -44963,7 +44963,7 @@
         <v>45427</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -45036,7 +45036,7 @@
         <v>44628</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -45109,7 +45109,7 @@
         <v>46272</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -45187,7 +45187,7 @@
         <v>46279</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -45260,7 +45260,7 @@
         <v>44986</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -45333,7 +45333,7 @@
         <v>44944</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -45406,7 +45406,7 @@
         <v>45655</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -45479,7 +45479,7 @@
         <v>45655</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -45552,7 +45552,7 @@
         <v>46239</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -45625,7 +45625,7 @@
         <v>46239</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -45698,7 +45698,7 @@
         <v>45597</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -45771,7 +45771,7 @@
         <v>46240</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -45849,7 +45849,7 @@
         <v>45219</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -45927,7 +45927,7 @@
         <v>44994</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -46000,7 +46000,7 @@
         <v>45555</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -46073,7 +46073,7 @@
         <v>45703</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -46146,7 +46146,7 @@
         <v>45205</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -46219,7 +46219,7 @@
         <v>44641</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -46297,7 +46297,7 @@
         <v>45655</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -46370,7 +46370,7 @@
         <v>44767</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -46443,7 +46443,7 @@
         <v>44909</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -46516,7 +46516,7 @@
         <v>44909</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -46589,7 +46589,7 @@
         <v>45230</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -46662,7 +46662,7 @@
         <v>45265</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -46735,7 +46735,7 @@
         <v>46272</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -46813,7 +46813,7 @@
         <v>45294</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -46886,7 +46886,7 @@
         <v>45429</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -46959,7 +46959,7 @@
         <v>45299</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -47032,7 +47032,7 @@
         <v>46245</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -47105,7 +47105,7 @@
         <v>45491</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -47178,7 +47178,7 @@
         <v>46289</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -47256,7 +47256,7 @@
         <v>46289</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -47334,7 +47334,7 @@
         <v>46288</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -47407,7 +47407,7 @@
         <v>45274</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -47480,7 +47480,7 @@
         <v>46288</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -47553,7 +47553,7 @@
         <v>45266</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -47626,7 +47626,7 @@
         <v>45268</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -47699,7 +47699,7 @@
         <v>46288</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -47772,7 +47772,7 @@
         <v>45300</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -47850,7 +47850,7 @@
         <v>46245</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -47923,7 +47923,7 @@
         <v>46288</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -47996,7 +47996,7 @@
         <v>45342</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -48069,7 +48069,7 @@
         <v>45364</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -48147,7 +48147,7 @@
         <v>45275</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -48220,7 +48220,7 @@
         <v>45275</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -48298,7 +48298,7 @@
         <v>45275</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -48371,7 +48371,7 @@
         <v>45153</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -48449,7 +48449,7 @@
         <v>45397</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -48522,7 +48522,7 @@
         <v>46248</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -48600,7 +48600,7 @@
         <v>46248</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -48678,7 +48678,7 @@
         <v>46248</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -48756,7 +48756,7 @@
         <v>46248</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -48834,7 +48834,7 @@
         <v>46290</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -48907,7 +48907,7 @@
         <v>46290</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -48980,7 +48980,7 @@
         <v>45404</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -49053,7 +49053,7 @@
         <v>44810</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -49126,7 +49126,7 @@
         <v>45491</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -49199,7 +49199,7 @@
         <v>46248</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -49277,7 +49277,7 @@
         <v>46248</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -49355,7 +49355,7 @@
         <v>44812</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -49428,7 +49428,7 @@
         <v>44794</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -49501,7 +49501,7 @@
         <v>44643</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -49574,7 +49574,7 @@
         <v>45299</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -49647,7 +49647,7 @@
         <v>46294</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -49725,7 +49725,7 @@
         <v>46294</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -49803,7 +49803,7 @@
         <v>46294</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -49881,7 +49881,7 @@
         <v>46294</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -49954,7 +49954,7 @@
         <v>45049</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -50027,7 +50027,7 @@
         <v>45048</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -50100,7 +50100,7 @@
         <v>46294</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -50178,7 +50178,7 @@
         <v>46294</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -50256,7 +50256,7 @@
         <v>45774</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -50329,7 +50329,7 @@
         <v>44859</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -50407,7 +50407,7 @@
         <v>46254</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -50480,7 +50480,7 @@
         <v>45275</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -50558,7 +50558,7 @@
         <v>45671</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -50631,7 +50631,7 @@
         <v>45779</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -50704,7 +50704,7 @@
         <v>45779</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -50777,7 +50777,7 @@
         <v>45785</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -50850,7 +50850,7 @@
         <v>46301</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -50923,7 +50923,7 @@
         <v>45359</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -50996,7 +50996,7 @@
         <v>45342</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -51069,7 +51069,7 @@
         <v>45573</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -51142,7 +51142,7 @@
         <v>46303</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -51215,7 +51215,7 @@
         <v>46030</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -51293,7 +51293,7 @@
         <v>46259</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -51371,7 +51371,7 @@
         <v>46259</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -51449,7 +51449,7 @@
         <v>46030</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -51527,7 +51527,7 @@
         <v>45664</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -51600,7 +51600,7 @@
         <v>46302</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -51673,7 +51673,7 @@
         <v>45546</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -51746,7 +51746,7 @@
         <v>45246</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -51819,7 +51819,7 @@
         <v>45483</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -51892,7 +51892,7 @@
         <v>46303</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -51965,7 +51965,7 @@
         <v>45793</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -52038,7 +52038,7 @@
         <v>46307</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -52116,7 +52116,7 @@
         <v>45593</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -52189,7 +52189,7 @@
         <v>46264</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -52262,7 +52262,7 @@
         <v>45737</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -52335,7 +52335,7 @@
         <v>46307</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -52413,7 +52413,7 @@
         <v>45573</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -52486,7 +52486,7 @@
         <v>46293</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -52559,7 +52559,7 @@
         <v>46266</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -52632,7 +52632,7 @@
         <v>46266</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -52705,7 +52705,7 @@
         <v>46267</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -52783,7 +52783,7 @@
         <v>46267</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -52861,7 +52861,7 @@
         <v>45804</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -52934,7 +52934,7 @@
         <v>46309</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -53012,7 +53012,7 @@
         <v>46265</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -53085,7 +53085,7 @@
         <v>46309</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -53163,7 +53163,7 @@
         <v>46265</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -53236,7 +53236,7 @@
         <v>46310</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -53309,7 +53309,7 @@
         <v>46269</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -53387,7 +53387,7 @@
         <v>46269</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -53465,7 +53465,7 @@
         <v>46269</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -53543,7 +53543,7 @@
         <v>45816</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -53616,7 +53616,7 @@
         <v>46275</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -53689,7 +53689,7 @@
         <v>46267</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -53767,7 +53767,7 @@
         <v>46269</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -53845,7 +53845,7 @@
         <v>45821</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -53918,7 +53918,7 @@
         <v>46267</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -53996,7 +53996,7 @@
         <v>46269</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -54074,7 +54074,7 @@
         <v>46269</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -54152,7 +54152,7 @@
         <v>46267</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -54230,7 +54230,7 @@
         <v>46269</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -54308,7 +54308,7 @@
         <v>45614</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -54381,7 +54381,7 @@
         <v>45655</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -54454,7 +54454,7 @@
         <v>45852</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -54527,7 +54527,7 @@
         <v>45860</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -54600,7 +54600,7 @@
         <v>45860</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -54673,7 +54673,7 @@
         <v>45804</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -54746,7 +54746,7 @@
         <v>45541</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -54819,7 +54819,7 @@
         <v>44855</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -54892,7 +54892,7 @@
         <v>45133</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -54965,7 +54965,7 @@
         <v>45541</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -55038,7 +55038,7 @@
         <v>45699</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -55111,7 +55111,7 @@
         <v>46040</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -55184,7 +55184,7 @@
         <v>46108</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -55257,7 +55257,7 @@
         <v>46183</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -55330,7 +55330,7 @@
         <v>46307</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>

--- a/Översikt LINKÖPING.xlsx
+++ b/Översikt LINKÖPING.xlsx
@@ -601,7 +601,7 @@
         <v>45756</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -741,7 +741,7 @@
         <v>45644</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>44679</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>46090</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>45293</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>44855</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
         <v>45278</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1505,7 +1505,7 @@
         <v>46275</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1634,7 +1634,7 @@
         <v>44368</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1750,7 +1750,7 @@
         <v>46090</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1863,7 +1863,7 @@
         <v>45720</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1975,7 +1975,7 @@
         <v>45720</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         <v>46206</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2206,7 +2206,7 @@
         <v>45860</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2317,7 +2317,7 @@
         <v>45804</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2432,7 +2432,7 @@
         <v>45280</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2548,7 +2548,7 @@
         <v>45756</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2662,7 +2662,7 @@
         <v>46090</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2772,7 +2772,7 @@
         <v>46275</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2890,7 +2890,7 @@
         <v>44949</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2999,7 +2999,7 @@
         <v>45068</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3113,7 +3113,7 @@
         <v>46146</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3222,7 +3222,7 @@
         <v>44679</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3336,7 +3336,7 @@
         <v>44588</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3449,7 +3449,7 @@
         <v>43997</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3558,7 +3558,7 @@
         <v>44679</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3675,7 +3675,7 @@
         <v>45943</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3783,7 +3783,7 @@
         <v>46050</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3891,7 +3891,7 @@
         <v>46079</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3999,7 +3999,7 @@
         <v>46107</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4116,7 +4116,7 @@
         <v>45714</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4229,7 +4229,7 @@
         <v>45932</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4342,7 +4342,7 @@
         <v>44745</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4450,7 +4450,7 @@
         <v>45555</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4563,7 +4563,7 @@
         <v>45089</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4671,7 +4671,7 @@
         <v>44834</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4779,7 +4779,7 @@
         <v>44679</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4891,7 +4891,7 @@
         <v>44679</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5003,7 +5003,7 @@
         <v>44855</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5114,7 +5114,7 @@
         <v>45621</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5221,7 +5221,7 @@
         <v>45941</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5332,7 +5332,7 @@
         <v>45294</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5439,7 +5439,7 @@
         <v>46206</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5546,7 +5546,7 @@
         <v>45664</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5653,7 +5653,7 @@
         <v>46087</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5764,7 +5764,7 @@
         <v>45774</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5875,7 +5875,7 @@
         <v>44930</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5991,7 +5991,7 @@
         <v>46289</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6111,7 +6111,7 @@
         <v>46146</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6222,7 +6222,7 @@
         <v>45217</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6334,7 +6334,7 @@
         <v>44916</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6446,7 +6446,7 @@
         <v>45153</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6558,7 +6558,7 @@
         <v>45236</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6669,7 +6669,7 @@
         <v>45163</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6776,7 +6776,7 @@
         <v>44830</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6883,7 +6883,7 @@
         <v>44848</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6989,7 +6989,7 @@
         <v>44498</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7099,7 +7099,7 @@
         <v>45554</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7214,7 +7214,7 @@
         <v>45774</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7320,7 +7320,7 @@
         <v>45461</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7426,7 +7426,7 @@
         <v>45621</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7532,7 +7532,7 @@
         <v>45595</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7638,7 +7638,7 @@
         <v>44930</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7749,7 +7749,7 @@
         <v>45216</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7855,7 +7855,7 @@
         <v>46043</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7970,7 +7970,7 @@
         <v>46178</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8076,7 +8076,7 @@
         <v>46259</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8187,7 +8187,7 @@
         <v>45804</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8293,7 +8293,7 @@
         <v>45639</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8399,7 +8399,7 @@
         <v>45745</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8509,7 +8509,7 @@
         <v>45932</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8620,7 +8620,7 @@
         <v>45572</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8726,7 +8726,7 @@
         <v>45244</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8837,7 +8837,7 @@
         <v>46107</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8948,7 +8948,7 @@
         <v>44936</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9054,7 +9054,7 @@
         <v>46153</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9160,7 +9160,7 @@
         <v>45547</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9270,7 +9270,7 @@
         <v>44597</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9376,7 +9376,7 @@
         <v>45140</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9486,7 +9486,7 @@
         <v>45191</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9597,7 +9597,7 @@
         <v>45774</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9707,7 +9707,7 @@
         <v>45148</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9813,7 +9813,7 @@
         <v>45071</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9924,7 +9924,7 @@
         <v>44909</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10034,7 +10034,7 @@
         <v>45176</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10140,7 +10140,7 @@
         <v>45712</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10251,7 +10251,7 @@
         <v>44159</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10362,7 +10362,7 @@
         <v>44537</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10472,7 +10472,7 @@
         <v>45071</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10582,7 +10582,7 @@
         <v>45222</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10696,7 +10696,7 @@
         <v>45412</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10801,7 +10801,7 @@
         <v>45915</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10911,7 +10911,7 @@
         <v>46175</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11016,7 +11016,7 @@
         <v>45941</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11121,7 +11121,7 @@
         <v>45554</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11231,7 +11231,7 @@
         <v>45460</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11336,7 +11336,7 @@
         <v>44938</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11441,7 +11441,7 @@
         <v>45665</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11551,7 +11551,7 @@
         <v>45308</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11661,7 +11661,7 @@
         <v>44949</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11766,7 +11766,7 @@
         <v>45968</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11871,7 +11871,7 @@
         <v>45442</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11980,7 +11980,7 @@
         <v>45463</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12085,7 +12085,7 @@
         <v>45988</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12195,7 +12195,7 @@
         <v>45604</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12305,7 +12305,7 @@
         <v>45369</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12410,7 +12410,7 @@
         <v>45176</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12515,7 +12515,7 @@
         <v>46206</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12620,7 +12620,7 @@
         <v>46289</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12730,7 +12730,7 @@
         <v>45812</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12835,7 +12835,7 @@
         <v>45816</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12940,7 +12940,7 @@
         <v>46079</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13045,7 +13045,7 @@
         <v>44929</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13150,7 +13150,7 @@
         <v>45604</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13260,7 +13260,7 @@
         <v>46259</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13370,7 +13370,7 @@
         <v>46302</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13475,7 +13475,7 @@
         <v>45153</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13585,7 +13585,7 @@
         <v>44881</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13690,7 +13690,7 @@
         <v>45994</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13795,7 +13795,7 @@
         <v>46264</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13900,7 +13900,7 @@
         <v>45246</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14010,7 +14010,7 @@
         <v>46308</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14124,7 +14124,7 @@
         <v>45965</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14234,7 +14234,7 @@
         <v>44945</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14339,7 +14339,7 @@
         <v>44950</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14444,7 +14444,7 @@
         <v>44496</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14554,7 +14554,7 @@
         <v>45294</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14664,7 +14664,7 @@
         <v>45141</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14769,7 +14769,7 @@
         <v>44768</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14874,7 +14874,7 @@
         <v>45111</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14979,7 +14979,7 @@
         <v>44889</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -15084,7 +15084,7 @@
         <v>45491</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15189,7 +15189,7 @@
         <v>45579</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15294,7 +15294,7 @@
         <v>45541</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15399,7 +15399,7 @@
         <v>45244</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15509,7 +15509,7 @@
         <v>45243</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -15619,7 +15619,7 @@
         <v>45266</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -15724,7 +15724,7 @@
         <v>45244</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -15834,7 +15834,7 @@
         <v>44945</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -15939,7 +15939,7 @@
         <v>44523</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -16012,7 +16012,7 @@
         <v>44608</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -16085,7 +16085,7 @@
         <v>44510</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -16158,7 +16158,7 @@
         <v>44764</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -16231,7 +16231,7 @@
         <v>44855</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -16309,7 +16309,7 @@
         <v>44573</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -16382,7 +16382,7 @@
         <v>44846</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -16455,7 +16455,7 @@
         <v>44496</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -16528,7 +16528,7 @@
         <v>44782</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -16601,7 +16601,7 @@
         <v>44853</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -16674,7 +16674,7 @@
         <v>44679</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -16752,7 +16752,7 @@
         <v>44777</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -16825,7 +16825,7 @@
         <v>44753</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -16903,7 +16903,7 @@
         <v>44510</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -16976,7 +16976,7 @@
         <v>44823</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -17049,7 +17049,7 @@
         <v>44515</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -17127,7 +17127,7 @@
         <v>44767</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -17200,7 +17200,7 @@
         <v>44719</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -17278,7 +17278,7 @@
         <v>44776</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -17351,7 +17351,7 @@
         <v>44692</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -17424,7 +17424,7 @@
         <v>44882</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -17502,7 +17502,7 @@
         <v>44588</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -17575,7 +17575,7 @@
         <v>44803</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -17648,7 +17648,7 @@
         <v>44743</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -17721,7 +17721,7 @@
         <v>44574</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -17794,7 +17794,7 @@
         <v>44571</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -17867,7 +17867,7 @@
         <v>44841</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -17940,7 +17940,7 @@
         <v>44537</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -18013,7 +18013,7 @@
         <v>44809</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -18086,7 +18086,7 @@
         <v>44884</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -18159,7 +18159,7 @@
         <v>44884</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -18232,7 +18232,7 @@
         <v>44628</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -18305,7 +18305,7 @@
         <v>44525</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -18378,7 +18378,7 @@
         <v>44525</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -18451,7 +18451,7 @@
         <v>44627</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -18524,7 +18524,7 @@
         <v>44785</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -18597,7 +18597,7 @@
         <v>44643</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -18670,7 +18670,7 @@
         <v>44595</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -18748,7 +18748,7 @@
         <v>44720</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -18821,7 +18821,7 @@
         <v>44743</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -18894,7 +18894,7 @@
         <v>44497</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -18967,7 +18967,7 @@
         <v>44848</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -19040,7 +19040,7 @@
         <v>44776</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -19113,7 +19113,7 @@
         <v>44826</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -19186,7 +19186,7 @@
         <v>44791</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -19259,7 +19259,7 @@
         <v>44498</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -19332,7 +19332,7 @@
         <v>44638</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -19405,7 +19405,7 @@
         <v>44812</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -19478,7 +19478,7 @@
         <v>44796</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -19556,7 +19556,7 @@
         <v>45579</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -19629,7 +19629,7 @@
         <v>45728</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -19702,7 +19702,7 @@
         <v>45147</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -19775,7 +19775,7 @@
         <v>44945</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -19848,7 +19848,7 @@
         <v>44994</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -19921,7 +19921,7 @@
         <v>44882</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -19994,7 +19994,7 @@
         <v>45111</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -20067,7 +20067,7 @@
         <v>45359</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -20140,7 +20140,7 @@
         <v>44498</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -20213,7 +20213,7 @@
         <v>45275</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -20291,7 +20291,7 @@
         <v>45275</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -20369,7 +20369,7 @@
         <v>45275</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -20442,7 +20442,7 @@
         <v>44740</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -20515,7 +20515,7 @@
         <v>44509</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -20593,7 +20593,7 @@
         <v>44794</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -20666,7 +20666,7 @@
         <v>45901</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -20739,7 +20739,7 @@
         <v>44658</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -20812,7 +20812,7 @@
         <v>45237</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -20885,7 +20885,7 @@
         <v>44930</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -20963,7 +20963,7 @@
         <v>45281</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -21041,7 +21041,7 @@
         <v>45737</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -21114,7 +21114,7 @@
         <v>45274</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -21187,7 +21187,7 @@
         <v>45912</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -21265,7 +21265,7 @@
         <v>45833</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -21338,7 +21338,7 @@
         <v>45912</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -21416,7 +21416,7 @@
         <v>45912</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -21494,7 +21494,7 @@
         <v>45915</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -21567,7 +21567,7 @@
         <v>45435</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -21640,7 +21640,7 @@
         <v>45111</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -21713,7 +21713,7 @@
         <v>45392</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -21791,7 +21791,7 @@
         <v>45919</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -21864,7 +21864,7 @@
         <v>44508</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -21937,7 +21937,7 @@
         <v>45049</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -22010,7 +22010,7 @@
         <v>45922</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -22088,7 +22088,7 @@
         <v>45146</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -22166,7 +22166,7 @@
         <v>44665</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -22244,7 +22244,7 @@
         <v>45597</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -22317,7 +22317,7 @@
         <v>45930</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -22390,7 +22390,7 @@
         <v>45928</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -22463,7 +22463,7 @@
         <v>45236</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -22541,7 +22541,7 @@
         <v>45932</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -22619,7 +22619,7 @@
         <v>44767</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -22692,7 +22692,7 @@
         <v>44931</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -22765,7 +22765,7 @@
         <v>45475</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -22838,7 +22838,7 @@
         <v>44882</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -22911,7 +22911,7 @@
         <v>44988</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -22989,7 +22989,7 @@
         <v>45579</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -23062,7 +23062,7 @@
         <v>45266</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -23135,7 +23135,7 @@
         <v>45302</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -23208,7 +23208,7 @@
         <v>45374</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -23281,7 +23281,7 @@
         <v>44860</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -23354,7 +23354,7 @@
         <v>45941</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -23427,7 +23427,7 @@
         <v>45082</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -23500,7 +23500,7 @@
         <v>45590</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -23573,7 +23573,7 @@
         <v>44498</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -23646,7 +23646,7 @@
         <v>45427</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -23719,7 +23719,7 @@
         <v>45755</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -23792,7 +23792,7 @@
         <v>45755</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -23865,7 +23865,7 @@
         <v>45755</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -23938,7 +23938,7 @@
         <v>45945</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -24011,7 +24011,7 @@
         <v>45411</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -24084,7 +24084,7 @@
         <v>44768</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -24157,7 +24157,7 @@
         <v>45364</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -24235,7 +24235,7 @@
         <v>45457</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -24308,7 +24308,7 @@
         <v>46181</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -24381,7 +24381,7 @@
         <v>45655</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -24454,7 +24454,7 @@
         <v>45655</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -24527,7 +24527,7 @@
         <v>45655</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -24600,7 +24600,7 @@
         <v>46181</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -24673,7 +24673,7 @@
         <v>45952</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -24746,7 +24746,7 @@
         <v>44909</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -24819,7 +24819,7 @@
         <v>45678</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -24892,7 +24892,7 @@
         <v>45140</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -24965,7 +24965,7 @@
         <v>45957</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -25038,7 +25038,7 @@
         <v>45957</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -25111,7 +25111,7 @@
         <v>45957</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -25184,7 +25184,7 @@
         <v>44794</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -25257,7 +25257,7 @@
         <v>45294</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -25335,7 +25335,7 @@
         <v>45021</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -25408,7 +25408,7 @@
         <v>45268</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -25481,7 +25481,7 @@
         <v>44903</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -25554,7 +25554,7 @@
         <v>45491</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -25627,7 +25627,7 @@
         <v>44865</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -25705,7 +25705,7 @@
         <v>45217</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -25778,7 +25778,7 @@
         <v>45217</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -25851,7 +25851,7 @@
         <v>45429</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -25924,7 +25924,7 @@
         <v>45177</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -25997,7 +25997,7 @@
         <v>46085</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -26070,7 +26070,7 @@
         <v>45299</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -26143,7 +26143,7 @@
         <v>45968</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -26216,7 +26216,7 @@
         <v>45968</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -26289,7 +26289,7 @@
         <v>45968</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -26362,7 +26362,7 @@
         <v>45230</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -26435,7 +26435,7 @@
         <v>45973</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -26508,7 +26508,7 @@
         <v>45973</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -26581,7 +26581,7 @@
         <v>45977</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -26659,7 +26659,7 @@
         <v>44986</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -26732,7 +26732,7 @@
         <v>45623</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -26805,7 +26805,7 @@
         <v>45623</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -26878,7 +26878,7 @@
         <v>45203</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -26951,7 +26951,7 @@
         <v>45604</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -27029,7 +27029,7 @@
         <v>46199</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -27102,7 +27102,7 @@
         <v>44923</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -27180,7 +27180,7 @@
         <v>45748</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -27253,7 +27253,7 @@
         <v>46154</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -27331,7 +27331,7 @@
         <v>44953</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -27404,7 +27404,7 @@
         <v>45161</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -27477,7 +27477,7 @@
         <v>45741</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -27550,7 +27550,7 @@
         <v>45265</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -27623,7 +27623,7 @@
         <v>46203</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -27696,7 +27696,7 @@
         <v>45261</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -27769,7 +27769,7 @@
         <v>45296</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -27842,7 +27842,7 @@
         <v>45219</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -27920,7 +27920,7 @@
         <v>45230</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -27993,7 +27993,7 @@
         <v>45082</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -28066,7 +28066,7 @@
         <v>46205</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -28139,7 +28139,7 @@
         <v>46206</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -28212,7 +28212,7 @@
         <v>44933</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -28285,7 +28285,7 @@
         <v>45268</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -28358,7 +28358,7 @@
         <v>46206</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -28431,7 +28431,7 @@
         <v>44986</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -28504,7 +28504,7 @@
         <v>46206</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -28577,7 +28577,7 @@
         <v>46206</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -28650,7 +28650,7 @@
         <v>46206</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -28723,7 +28723,7 @@
         <v>46206</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -28796,7 +28796,7 @@
         <v>46206</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -28869,7 +28869,7 @@
         <v>46206</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -28942,7 +28942,7 @@
         <v>45655</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -29015,7 +29015,7 @@
         <v>46206</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -29088,7 +29088,7 @@
         <v>45266</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -29166,7 +29166,7 @@
         <v>45989</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -29239,7 +29239,7 @@
         <v>44970</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -29317,7 +29317,7 @@
         <v>45300</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -29395,7 +29395,7 @@
         <v>45182</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -29468,7 +29468,7 @@
         <v>45579</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -29541,7 +29541,7 @@
         <v>45695</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -29614,7 +29614,7 @@
         <v>45320</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -29687,7 +29687,7 @@
         <v>45996</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -29765,7 +29765,7 @@
         <v>45245</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -29843,7 +29843,7 @@
         <v>45655</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -29916,7 +29916,7 @@
         <v>45545</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -29989,7 +29989,7 @@
         <v>46147</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -30067,7 +30067,7 @@
         <v>46000</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -30145,7 +30145,7 @@
         <v>45208</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -30218,7 +30218,7 @@
         <v>45671</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -30291,7 +30291,7 @@
         <v>45779</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -30364,7 +30364,7 @@
         <v>45779</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -30437,7 +30437,7 @@
         <v>46010</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -30510,7 +30510,7 @@
         <v>45246</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -30583,7 +30583,7 @@
         <v>46279</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -30656,7 +30656,7 @@
         <v>45359</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -30729,7 +30729,7 @@
         <v>45785</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -30802,7 +30802,7 @@
         <v>45271</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -30875,7 +30875,7 @@
         <v>46239</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -30948,7 +30948,7 @@
         <v>46239</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -31021,7 +31021,7 @@
         <v>45342</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -31094,7 +31094,7 @@
         <v>45546</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -31167,7 +31167,7 @@
         <v>45664</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -31240,7 +31240,7 @@
         <v>45573</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -31313,7 +31313,7 @@
         <v>46030</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -31386,7 +31386,7 @@
         <v>46030</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -31459,7 +31459,7 @@
         <v>46030</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -31532,7 +31532,7 @@
         <v>45483</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -31605,7 +31605,7 @@
         <v>46030</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -31678,7 +31678,7 @@
         <v>46030</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -31751,7 +31751,7 @@
         <v>46240</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -31829,7 +31829,7 @@
         <v>46035</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -31902,7 +31902,7 @@
         <v>46035</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -31975,7 +31975,7 @@
         <v>45274</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -32048,7 +32048,7 @@
         <v>45593</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -32121,7 +32121,7 @@
         <v>46038</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -32194,7 +32194,7 @@
         <v>45737</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -32267,7 +32267,7 @@
         <v>45793</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -32340,7 +32340,7 @@
         <v>46245</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -32413,7 +32413,7 @@
         <v>46245</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -32486,7 +32486,7 @@
         <v>46288</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -32559,7 +32559,7 @@
         <v>46288</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -32632,7 +32632,7 @@
         <v>46288</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -32705,7 +32705,7 @@
         <v>46288</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -32778,7 +32778,7 @@
         <v>45573</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -32851,7 +32851,7 @@
         <v>45804</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -32924,7 +32924,7 @@
         <v>45293</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -32997,7 +32997,7 @@
         <v>46290</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -33070,7 +33070,7 @@
         <v>46290</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -33143,7 +33143,7 @@
         <v>46055</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -33216,7 +33216,7 @@
         <v>46055</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -33289,7 +33289,7 @@
         <v>46289</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -33367,7 +33367,7 @@
         <v>46289</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -33445,7 +33445,7 @@
         <v>46248</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -33523,7 +33523,7 @@
         <v>46294</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -33601,7 +33601,7 @@
         <v>46294</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -33679,7 +33679,7 @@
         <v>45342</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -33752,7 +33752,7 @@
         <v>46248</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -33830,7 +33830,7 @@
         <v>46248</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -33908,7 +33908,7 @@
         <v>46248</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -33986,7 +33986,7 @@
         <v>46248</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -34064,7 +34064,7 @@
         <v>46294</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -34142,7 +34142,7 @@
         <v>46294</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -34215,7 +34215,7 @@
         <v>46294</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -34293,7 +34293,7 @@
         <v>45299</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -34366,7 +34366,7 @@
         <v>45300</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -34444,7 +34444,7 @@
         <v>45816</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -34517,7 +34517,7 @@
         <v>44873</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -34595,7 +34595,7 @@
         <v>46294</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -34673,7 +34673,7 @@
         <v>46248</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -34751,7 +34751,7 @@
         <v>45821</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -34824,7 +34824,7 @@
         <v>46077</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -34897,7 +34897,7 @@
         <v>46079</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -34970,7 +34970,7 @@
         <v>46087</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -35043,7 +35043,7 @@
         <v>46094</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -35116,7 +35116,7 @@
         <v>46254</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -35189,7 +35189,7 @@
         <v>45485</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -35262,7 +35262,7 @@
         <v>46098</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -35335,7 +35335,7 @@
         <v>45294</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -35408,7 +35408,7 @@
         <v>45294</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -35481,7 +35481,7 @@
         <v>46099</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -35559,7 +35559,7 @@
         <v>45655</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -35632,7 +35632,7 @@
         <v>45614</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -35705,7 +35705,7 @@
         <v>46301</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -35778,7 +35778,7 @@
         <v>46302</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -35851,7 +35851,7 @@
         <v>44894</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -35924,7 +35924,7 @@
         <v>46259</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -36002,7 +36002,7 @@
         <v>46259</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -36080,7 +36080,7 @@
         <v>45852</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -36153,7 +36153,7 @@
         <v>45860</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -36226,7 +36226,7 @@
         <v>45860</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -36299,7 +36299,7 @@
         <v>44936</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -36372,7 +36372,7 @@
         <v>46303</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -36445,7 +36445,7 @@
         <v>46120</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -36518,7 +36518,7 @@
         <v>44599</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -36591,7 +36591,7 @@
         <v>45086</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -36664,7 +36664,7 @@
         <v>46030</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -36742,7 +36742,7 @@
         <v>46303</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -36815,7 +36815,7 @@
         <v>46030</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -36893,7 +36893,7 @@
         <v>46264</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -36966,7 +36966,7 @@
         <v>45804</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -37039,7 +37039,7 @@
         <v>46265</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -37112,7 +37112,7 @@
         <v>46307</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -37190,7 +37190,7 @@
         <v>45610</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -37263,7 +37263,7 @@
         <v>46134</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -37336,7 +37336,7 @@
         <v>44945</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -37409,7 +37409,7 @@
         <v>45774</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -37482,7 +37482,7 @@
         <v>46265</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -37555,7 +37555,7 @@
         <v>44888</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -37628,7 +37628,7 @@
         <v>45967</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -37701,7 +37701,7 @@
         <v>46086</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -37774,7 +37774,7 @@
         <v>45491</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -37847,7 +37847,7 @@
         <v>46307</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -37925,7 +37925,7 @@
         <v>45712</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -37998,7 +37998,7 @@
         <v>45905</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -38071,7 +38071,7 @@
         <v>45938</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -38149,7 +38149,7 @@
         <v>46310</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -38222,7 +38222,7 @@
         <v>46008</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -38295,7 +38295,7 @@
         <v>46057</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -38368,7 +38368,7 @@
         <v>46099</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -38441,7 +38441,7 @@
         <v>46086</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -38514,7 +38514,7 @@
         <v>46086</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -38587,7 +38587,7 @@
         <v>45774</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -38660,7 +38660,7 @@
         <v>44628</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -38733,7 +38733,7 @@
         <v>46266</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -38806,7 +38806,7 @@
         <v>46266</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -38879,7 +38879,7 @@
         <v>46267</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -38957,7 +38957,7 @@
         <v>44897</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -39035,7 +39035,7 @@
         <v>46267</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -39113,7 +39113,7 @@
         <v>46267</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -39191,7 +39191,7 @@
         <v>45741</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -39264,7 +39264,7 @@
         <v>46309</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -39342,7 +39342,7 @@
         <v>46309</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -39420,7 +39420,7 @@
         <v>46267</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -39498,7 +39498,7 @@
         <v>46267</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -39576,7 +39576,7 @@
         <v>44498</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -39649,7 +39649,7 @@
         <v>44889</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -39727,7 +39727,7 @@
         <v>46269</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -39805,7 +39805,7 @@
         <v>46269</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -39883,7 +39883,7 @@
         <v>46269</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -39961,7 +39961,7 @@
         <v>45555</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -40039,7 +40039,7 @@
         <v>46269</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -40117,7 +40117,7 @@
         <v>46269</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -40195,7 +40195,7 @@
         <v>46269</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -40273,7 +40273,7 @@
         <v>46269</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -40351,7 +40351,7 @@
         <v>46272</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -40429,7 +40429,7 @@
         <v>46272</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -40507,7 +40507,7 @@
         <v>46272</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -40585,7 +40585,7 @@
         <v>46272</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -40663,7 +40663,7 @@
         <v>46272</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -40741,7 +40741,7 @@
         <v>46272</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -40819,7 +40819,7 @@
         <v>45121</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -40892,7 +40892,7 @@
         <v>46275</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -40965,7 +40965,7 @@
         <v>45392</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -41038,7 +41038,7 @@
         <v>46274</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -41116,7 +41116,7 @@
         <v>46275</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -41189,7 +41189,7 @@
         <v>45397</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -41262,7 +41262,7 @@
         <v>44944</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -41335,7 +41335,7 @@
         <v>45230</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -41408,7 +41408,7 @@
         <v>46275</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -41481,7 +41481,7 @@
         <v>45202</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -41554,7 +41554,7 @@
         <v>45229</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -41627,7 +41627,7 @@
         <v>45244</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -41705,7 +41705,7 @@
         <v>45555</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -41778,7 +41778,7 @@
         <v>44945</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -41851,7 +41851,7 @@
         <v>45623</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -41924,7 +41924,7 @@
         <v>46293</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -41997,7 +41997,7 @@
         <v>46145</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -42070,7 +42070,7 @@
         <v>46275</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -42143,7 +42143,7 @@
         <v>44939</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -42216,7 +42216,7 @@
         <v>44944</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -42289,7 +42289,7 @@
         <v>44986</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -42362,7 +42362,7 @@
         <v>46147</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -42440,7 +42440,7 @@
         <v>45142</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -42513,7 +42513,7 @@
         <v>46147</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -42591,7 +42591,7 @@
         <v>46154</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -42669,7 +42669,7 @@
         <v>45596</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -42742,7 +42742,7 @@
         <v>46154</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -42820,7 +42820,7 @@
         <v>46154</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -42898,7 +42898,7 @@
         <v>44776</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -42971,7 +42971,7 @@
         <v>46154</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -43049,7 +43049,7 @@
         <v>45105</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -43127,7 +43127,7 @@
         <v>46154</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -43205,7 +43205,7 @@
         <v>46154</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -43283,7 +43283,7 @@
         <v>46153</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -43356,7 +43356,7 @@
         <v>44942</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -43429,7 +43429,7 @@
         <v>44690</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -43502,7 +43502,7 @@
         <v>45729</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -43580,7 +43580,7 @@
         <v>45379</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -43653,7 +43653,7 @@
         <v>45774</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -43726,7 +43726,7 @@
         <v>45092</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -43799,7 +43799,7 @@
         <v>45624</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -43872,7 +43872,7 @@
         <v>44933</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -43945,7 +43945,7 @@
         <v>45089</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -44023,7 +44023,7 @@
         <v>44909</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -44096,7 +44096,7 @@
         <v>44994</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -44169,7 +44169,7 @@
         <v>44936</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -44242,7 +44242,7 @@
         <v>44967</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -44320,7 +44320,7 @@
         <v>45300</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -44398,7 +44398,7 @@
         <v>45275</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -44471,7 +44471,7 @@
         <v>45153</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -44549,7 +44549,7 @@
         <v>45096</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -44627,7 +44627,7 @@
         <v>45225</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -44705,7 +44705,7 @@
         <v>45142</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -44778,7 +44778,7 @@
         <v>45639</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -44851,7 +44851,7 @@
         <v>45086</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -44924,7 +44924,7 @@
         <v>45147</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -44997,7 +44997,7 @@
         <v>44767</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -45070,7 +45070,7 @@
         <v>45187</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -45148,7 +45148,7 @@
         <v>44509</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -45226,7 +45226,7 @@
         <v>44824</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -45299,7 +45299,7 @@
         <v>45013</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -45372,7 +45372,7 @@
         <v>45729</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -45445,7 +45445,7 @@
         <v>45568</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -45518,7 +45518,7 @@
         <v>45755</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -45591,7 +45591,7 @@
         <v>44862</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -45664,7 +45664,7 @@
         <v>45069</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -45737,7 +45737,7 @@
         <v>45111</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -45815,7 +45815,7 @@
         <v>45077</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -45888,7 +45888,7 @@
         <v>44565</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -45961,7 +45961,7 @@
         <v>45090</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -46034,7 +46034,7 @@
         <v>45133</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -46107,7 +46107,7 @@
         <v>45082</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -46180,7 +46180,7 @@
         <v>45209</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -46253,7 +46253,7 @@
         <v>44812</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -46326,7 +46326,7 @@
         <v>44862</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -46399,7 +46399,7 @@
         <v>45555</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -46477,7 +46477,7 @@
         <v>44928</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -46550,7 +46550,7 @@
         <v>45092</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -46623,7 +46623,7 @@
         <v>45275</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -46696,7 +46696,7 @@
         <v>45491</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -46769,7 +46769,7 @@
         <v>45231</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -46842,7 +46842,7 @@
         <v>44966</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -46915,7 +46915,7 @@
         <v>45568</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -46988,7 +46988,7 @@
         <v>44501</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -47061,7 +47061,7 @@
         <v>44949</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -47134,7 +47134,7 @@
         <v>45294</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -47207,7 +47207,7 @@
         <v>45341</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -47280,7 +47280,7 @@
         <v>45231</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -47353,7 +47353,7 @@
         <v>44909</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -47426,7 +47426,7 @@
         <v>45217</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -47499,7 +47499,7 @@
         <v>45195</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -47572,7 +47572,7 @@
         <v>45275</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -47645,7 +47645,7 @@
         <v>45489</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -47718,7 +47718,7 @@
         <v>45337</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -47791,7 +47791,7 @@
         <v>45404</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -47864,7 +47864,7 @@
         <v>45111</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -47942,7 +47942,7 @@
         <v>44558</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -48015,7 +48015,7 @@
         <v>45275</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -48088,7 +48088,7 @@
         <v>45453</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -48161,7 +48161,7 @@
         <v>45483</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -48234,7 +48234,7 @@
         <v>45106</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -48307,7 +48307,7 @@
         <v>45106</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -48380,7 +48380,7 @@
         <v>45106</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -48453,7 +48453,7 @@
         <v>45456</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -48526,7 +48526,7 @@
         <v>44509</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -48599,7 +48599,7 @@
         <v>45037</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -48677,7 +48677,7 @@
         <v>45120</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -48750,7 +48750,7 @@
         <v>44937</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -48823,7 +48823,7 @@
         <v>45030</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -48896,7 +48896,7 @@
         <v>45644</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -48969,7 +48969,7 @@
         <v>45117</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -49042,7 +49042,7 @@
         <v>45750</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -49115,7 +49115,7 @@
         <v>45140</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -49188,7 +49188,7 @@
         <v>45125</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -49261,7 +49261,7 @@
         <v>45678</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -49334,7 +49334,7 @@
         <v>45116</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -49407,7 +49407,7 @@
         <v>45470</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -49485,7 +49485,7 @@
         <v>45155</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -49558,7 +49558,7 @@
         <v>44993</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -49631,7 +49631,7 @@
         <v>45177</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -49704,7 +49704,7 @@
         <v>44783</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -49777,7 +49777,7 @@
         <v>45005</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -49850,7 +49850,7 @@
         <v>45274</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -49923,7 +49923,7 @@
         <v>45275</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -50001,7 +50001,7 @@
         <v>45275</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -50079,7 +50079,7 @@
         <v>44608</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -50157,7 +50157,7 @@
         <v>45152</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -50230,7 +50230,7 @@
         <v>45625</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -50303,7 +50303,7 @@
         <v>44643</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -50376,7 +50376,7 @@
         <v>44803</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -50449,7 +50449,7 @@
         <v>44859</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -50527,7 +50527,7 @@
         <v>44600</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -50600,7 +50600,7 @@
         <v>44795</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -50673,7 +50673,7 @@
         <v>45225</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -50746,7 +50746,7 @@
         <v>45230</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -50819,7 +50819,7 @@
         <v>44683</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -50892,7 +50892,7 @@
         <v>45655</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -50965,7 +50965,7 @@
         <v>44638</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -51038,7 +51038,7 @@
         <v>44623</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -51111,7 +51111,7 @@
         <v>45703</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -51184,7 +51184,7 @@
         <v>45146</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -51262,7 +51262,7 @@
         <v>45111</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -51335,7 +51335,7 @@
         <v>45774</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -51408,7 +51408,7 @@
         <v>45231</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -51481,7 +51481,7 @@
         <v>45230</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -51554,7 +51554,7 @@
         <v>45160</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -51627,7 +51627,7 @@
         <v>44743</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -51700,7 +51700,7 @@
         <v>45205</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -51773,7 +51773,7 @@
         <v>44909</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -51846,7 +51846,7 @@
         <v>45306</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -51919,7 +51919,7 @@
         <v>44768</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -51992,7 +51992,7 @@
         <v>44767</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -52065,7 +52065,7 @@
         <v>44858</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -52138,7 +52138,7 @@
         <v>45477</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -52216,7 +52216,7 @@
         <v>44775</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -52289,7 +52289,7 @@
         <v>44930</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -52367,7 +52367,7 @@
         <v>44865</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -52440,7 +52440,7 @@
         <v>44888</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -52513,7 +52513,7 @@
         <v>45275</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -52591,7 +52591,7 @@
         <v>45153</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -52669,7 +52669,7 @@
         <v>45044</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -52742,7 +52742,7 @@
         <v>44930</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -52820,7 +52820,7 @@
         <v>45309</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -52893,7 +52893,7 @@
         <v>45293</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -52966,7 +52966,7 @@
         <v>45238</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -53039,7 +53039,7 @@
         <v>45048</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -53112,7 +53112,7 @@
         <v>45225</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -53185,7 +53185,7 @@
         <v>45268</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -53258,7 +53258,7 @@
         <v>45161</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -53331,7 +53331,7 @@
         <v>44994</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -53404,7 +53404,7 @@
         <v>44987</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -53477,7 +53477,7 @@
         <v>44498</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -53550,7 +53550,7 @@
         <v>44498</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -53623,7 +53623,7 @@
         <v>44909</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -53696,7 +53696,7 @@
         <v>45492</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -53769,7 +53769,7 @@
         <v>44958</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -53842,7 +53842,7 @@
         <v>44810</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -53915,7 +53915,7 @@
         <v>44949</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -53988,7 +53988,7 @@
         <v>44911</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -54061,7 +54061,7 @@
         <v>44641</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -54139,7 +54139,7 @@
         <v>45541</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -54212,7 +54212,7 @@
         <v>44855</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -54285,7 +54285,7 @@
         <v>45133</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -54358,7 +54358,7 @@
         <v>45541</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -54431,7 +54431,7 @@
         <v>45699</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -54504,7 +54504,7 @@
         <v>46040</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -54577,7 +54577,7 @@
         <v>46108</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -54650,7 +54650,7 @@
         <v>46183</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -54723,7 +54723,7 @@
         <v>46307</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>

--- a/Översikt LINKÖPING.xlsx
+++ b/Översikt LINKÖPING.xlsx
@@ -601,7 +601,7 @@
         <v>45756</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -741,7 +741,7 @@
         <v>45644</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>44679</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>46090</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>45293</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>44855</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
         <v>45278</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1505,7 +1505,7 @@
         <v>46275</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1634,7 +1634,7 @@
         <v>44368</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1750,7 +1750,7 @@
         <v>46090</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1863,7 +1863,7 @@
         <v>45720</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1975,7 +1975,7 @@
         <v>45720</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         <v>46206</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2206,7 +2206,7 @@
         <v>45860</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2317,7 +2317,7 @@
         <v>45804</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2432,7 +2432,7 @@
         <v>45280</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2548,7 +2548,7 @@
         <v>45756</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2662,7 +2662,7 @@
         <v>46090</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2772,7 +2772,7 @@
         <v>46275</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2890,7 +2890,7 @@
         <v>44949</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2999,7 +2999,7 @@
         <v>45068</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3113,7 +3113,7 @@
         <v>46146</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3222,7 +3222,7 @@
         <v>44679</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3336,7 +3336,7 @@
         <v>44588</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3449,7 +3449,7 @@
         <v>43997</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3558,7 +3558,7 @@
         <v>44679</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3675,7 +3675,7 @@
         <v>45943</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3783,7 +3783,7 @@
         <v>46050</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3891,7 +3891,7 @@
         <v>46079</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3999,7 +3999,7 @@
         <v>46107</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4116,7 +4116,7 @@
         <v>45714</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4229,7 +4229,7 @@
         <v>45932</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4342,7 +4342,7 @@
         <v>44745</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4450,7 +4450,7 @@
         <v>45555</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4563,7 +4563,7 @@
         <v>45089</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4671,7 +4671,7 @@
         <v>44834</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4779,7 +4779,7 @@
         <v>44679</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4891,7 +4891,7 @@
         <v>44679</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5003,7 +5003,7 @@
         <v>44855</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5114,7 +5114,7 @@
         <v>45621</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5221,7 +5221,7 @@
         <v>45941</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5332,7 +5332,7 @@
         <v>45294</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5439,7 +5439,7 @@
         <v>46206</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5546,7 +5546,7 @@
         <v>45664</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5653,7 +5653,7 @@
         <v>46087</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5764,7 +5764,7 @@
         <v>45774</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5875,7 +5875,7 @@
         <v>44930</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5991,7 +5991,7 @@
         <v>46289</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6111,7 +6111,7 @@
         <v>46146</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6222,7 +6222,7 @@
         <v>45217</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6334,7 +6334,7 @@
         <v>44916</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6446,7 +6446,7 @@
         <v>45153</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6558,7 +6558,7 @@
         <v>45236</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6669,7 +6669,7 @@
         <v>45163</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6776,7 +6776,7 @@
         <v>44830</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6883,7 +6883,7 @@
         <v>44848</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6989,7 +6989,7 @@
         <v>44498</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7099,7 +7099,7 @@
         <v>45554</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7214,7 +7214,7 @@
         <v>45774</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7320,7 +7320,7 @@
         <v>45461</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7426,7 +7426,7 @@
         <v>45621</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7532,7 +7532,7 @@
         <v>45595</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7638,7 +7638,7 @@
         <v>44930</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7749,7 +7749,7 @@
         <v>45216</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7855,7 +7855,7 @@
         <v>46043</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7970,7 +7970,7 @@
         <v>46178</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8076,7 +8076,7 @@
         <v>46259</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8187,7 +8187,7 @@
         <v>45804</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8293,7 +8293,7 @@
         <v>45639</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8399,7 +8399,7 @@
         <v>45745</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8509,7 +8509,7 @@
         <v>45932</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8620,7 +8620,7 @@
         <v>45572</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8726,7 +8726,7 @@
         <v>45244</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8837,7 +8837,7 @@
         <v>46107</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8948,7 +8948,7 @@
         <v>44936</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9054,7 +9054,7 @@
         <v>46153</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9160,7 +9160,7 @@
         <v>45547</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9270,7 +9270,7 @@
         <v>44597</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9376,7 +9376,7 @@
         <v>45140</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9486,7 +9486,7 @@
         <v>45191</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9597,7 +9597,7 @@
         <v>45774</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9707,7 +9707,7 @@
         <v>45148</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9813,7 +9813,7 @@
         <v>45071</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9924,7 +9924,7 @@
         <v>44909</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10034,7 +10034,7 @@
         <v>45176</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10140,7 +10140,7 @@
         <v>45712</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10251,7 +10251,7 @@
         <v>44159</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10362,7 +10362,7 @@
         <v>44537</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10472,7 +10472,7 @@
         <v>45071</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10582,7 +10582,7 @@
         <v>45222</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10696,7 +10696,7 @@
         <v>45412</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10801,7 +10801,7 @@
         <v>45915</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10911,7 +10911,7 @@
         <v>46175</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11016,7 +11016,7 @@
         <v>45941</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11121,7 +11121,7 @@
         <v>45554</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11231,7 +11231,7 @@
         <v>45460</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11336,7 +11336,7 @@
         <v>44938</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11441,7 +11441,7 @@
         <v>45665</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11551,7 +11551,7 @@
         <v>45308</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11661,7 +11661,7 @@
         <v>44949</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11766,7 +11766,7 @@
         <v>45968</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11871,7 +11871,7 @@
         <v>45442</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11980,7 +11980,7 @@
         <v>45463</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12085,7 +12085,7 @@
         <v>45988</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12195,7 +12195,7 @@
         <v>45604</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12305,7 +12305,7 @@
         <v>45369</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12410,7 +12410,7 @@
         <v>45176</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12515,7 +12515,7 @@
         <v>46206</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12620,7 +12620,7 @@
         <v>46289</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12730,7 +12730,7 @@
         <v>45812</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12835,7 +12835,7 @@
         <v>45816</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12940,7 +12940,7 @@
         <v>46079</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13045,7 +13045,7 @@
         <v>44929</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13150,7 +13150,7 @@
         <v>45604</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13260,7 +13260,7 @@
         <v>46259</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13370,7 +13370,7 @@
         <v>46302</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13475,7 +13475,7 @@
         <v>45153</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13585,7 +13585,7 @@
         <v>44881</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13690,7 +13690,7 @@
         <v>45994</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13795,7 +13795,7 @@
         <v>46264</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13900,7 +13900,7 @@
         <v>45246</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14010,7 +14010,7 @@
         <v>46308</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14124,7 +14124,7 @@
         <v>45965</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14234,7 +14234,7 @@
         <v>44945</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14339,7 +14339,7 @@
         <v>44950</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14444,7 +14444,7 @@
         <v>44496</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14554,7 +14554,7 @@
         <v>45294</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14664,7 +14664,7 @@
         <v>45141</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14769,7 +14769,7 @@
         <v>44768</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14874,7 +14874,7 @@
         <v>45111</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14979,7 +14979,7 @@
         <v>44889</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -15084,7 +15084,7 @@
         <v>45491</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15189,7 +15189,7 @@
         <v>45579</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15294,7 +15294,7 @@
         <v>45541</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15399,7 +15399,7 @@
         <v>45244</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15509,7 +15509,7 @@
         <v>45243</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -15619,7 +15619,7 @@
         <v>45266</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -15724,7 +15724,7 @@
         <v>45244</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -15834,7 +15834,7 @@
         <v>44945</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -15939,7 +15939,7 @@
         <v>44523</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -16012,7 +16012,7 @@
         <v>44608</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -16085,7 +16085,7 @@
         <v>44510</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -16158,7 +16158,7 @@
         <v>44764</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -16231,7 +16231,7 @@
         <v>44855</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -16309,7 +16309,7 @@
         <v>44573</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -16382,7 +16382,7 @@
         <v>44846</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -16455,7 +16455,7 @@
         <v>44496</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -16528,7 +16528,7 @@
         <v>44782</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -16601,7 +16601,7 @@
         <v>44853</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -16674,7 +16674,7 @@
         <v>44679</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -16752,7 +16752,7 @@
         <v>44777</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -16825,7 +16825,7 @@
         <v>44753</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -16903,7 +16903,7 @@
         <v>44510</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -16976,7 +16976,7 @@
         <v>44823</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -17049,7 +17049,7 @@
         <v>44515</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -17127,7 +17127,7 @@
         <v>44767</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -17200,7 +17200,7 @@
         <v>44719</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -17278,7 +17278,7 @@
         <v>44776</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -17351,7 +17351,7 @@
         <v>44692</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -17424,7 +17424,7 @@
         <v>44882</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -17502,7 +17502,7 @@
         <v>44588</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -17575,7 +17575,7 @@
         <v>44803</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -17648,7 +17648,7 @@
         <v>44743</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -17721,7 +17721,7 @@
         <v>44574</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -17794,7 +17794,7 @@
         <v>44571</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -17867,7 +17867,7 @@
         <v>44841</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -17940,7 +17940,7 @@
         <v>44537</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -18013,7 +18013,7 @@
         <v>44809</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -18086,7 +18086,7 @@
         <v>44884</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -18159,7 +18159,7 @@
         <v>44884</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -18232,7 +18232,7 @@
         <v>44628</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -18305,7 +18305,7 @@
         <v>44525</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -18378,7 +18378,7 @@
         <v>44525</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -18451,7 +18451,7 @@
         <v>44627</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -18524,7 +18524,7 @@
         <v>44785</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -18597,7 +18597,7 @@
         <v>44643</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -18670,7 +18670,7 @@
         <v>44595</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -18748,7 +18748,7 @@
         <v>44720</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -18821,7 +18821,7 @@
         <v>44743</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -18894,7 +18894,7 @@
         <v>44497</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -18967,7 +18967,7 @@
         <v>44848</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -19040,7 +19040,7 @@
         <v>44776</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -19113,7 +19113,7 @@
         <v>44826</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -19186,7 +19186,7 @@
         <v>44791</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -19259,7 +19259,7 @@
         <v>44498</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -19332,7 +19332,7 @@
         <v>44638</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -19405,7 +19405,7 @@
         <v>44812</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -19478,7 +19478,7 @@
         <v>44796</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -19556,7 +19556,7 @@
         <v>45579</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -19629,7 +19629,7 @@
         <v>45728</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -19702,7 +19702,7 @@
         <v>45147</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -19775,7 +19775,7 @@
         <v>44945</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -19848,7 +19848,7 @@
         <v>44994</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -19921,7 +19921,7 @@
         <v>44882</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -19994,7 +19994,7 @@
         <v>45111</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -20067,7 +20067,7 @@
         <v>45359</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -20140,7 +20140,7 @@
         <v>44498</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -20213,7 +20213,7 @@
         <v>45275</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -20291,7 +20291,7 @@
         <v>45275</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -20369,7 +20369,7 @@
         <v>45275</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -20442,7 +20442,7 @@
         <v>44740</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -20515,7 +20515,7 @@
         <v>44509</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -20593,7 +20593,7 @@
         <v>44794</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -20666,7 +20666,7 @@
         <v>45901</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -20739,7 +20739,7 @@
         <v>44658</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -20812,7 +20812,7 @@
         <v>45237</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -20885,7 +20885,7 @@
         <v>44930</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -20963,7 +20963,7 @@
         <v>45281</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -21041,7 +21041,7 @@
         <v>45737</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -21114,7 +21114,7 @@
         <v>45274</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -21187,7 +21187,7 @@
         <v>45912</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -21265,7 +21265,7 @@
         <v>45833</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -21338,7 +21338,7 @@
         <v>45912</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -21416,7 +21416,7 @@
         <v>45912</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -21494,7 +21494,7 @@
         <v>45915</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -21567,7 +21567,7 @@
         <v>45435</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -21640,7 +21640,7 @@
         <v>45111</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -21713,7 +21713,7 @@
         <v>45392</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -21791,7 +21791,7 @@
         <v>45919</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -21864,7 +21864,7 @@
         <v>44508</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -21937,7 +21937,7 @@
         <v>45049</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -22010,7 +22010,7 @@
         <v>45922</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -22088,7 +22088,7 @@
         <v>45146</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -22166,7 +22166,7 @@
         <v>44665</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -22244,7 +22244,7 @@
         <v>45597</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -22317,7 +22317,7 @@
         <v>45930</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -22390,7 +22390,7 @@
         <v>45928</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -22463,7 +22463,7 @@
         <v>45236</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -22541,7 +22541,7 @@
         <v>45932</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -22619,7 +22619,7 @@
         <v>44767</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -22692,7 +22692,7 @@
         <v>44931</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -22765,7 +22765,7 @@
         <v>45475</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -22838,7 +22838,7 @@
         <v>44882</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -22911,7 +22911,7 @@
         <v>44988</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -22989,7 +22989,7 @@
         <v>45579</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -23062,7 +23062,7 @@
         <v>45266</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -23135,7 +23135,7 @@
         <v>45302</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -23208,7 +23208,7 @@
         <v>45374</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -23281,7 +23281,7 @@
         <v>44860</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -23354,7 +23354,7 @@
         <v>45941</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -23427,7 +23427,7 @@
         <v>45082</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -23500,7 +23500,7 @@
         <v>45590</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -23573,7 +23573,7 @@
         <v>44498</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -23646,7 +23646,7 @@
         <v>45427</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -23719,7 +23719,7 @@
         <v>45755</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -23792,7 +23792,7 @@
         <v>45755</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -23865,7 +23865,7 @@
         <v>45755</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -23938,7 +23938,7 @@
         <v>45945</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -24011,7 +24011,7 @@
         <v>45411</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -24084,7 +24084,7 @@
         <v>44768</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -24157,7 +24157,7 @@
         <v>45364</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -24235,7 +24235,7 @@
         <v>45457</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -24308,7 +24308,7 @@
         <v>46181</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -24381,7 +24381,7 @@
         <v>45655</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -24454,7 +24454,7 @@
         <v>45655</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -24527,7 +24527,7 @@
         <v>45655</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -24600,7 +24600,7 @@
         <v>46181</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -24673,7 +24673,7 @@
         <v>45952</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -24746,7 +24746,7 @@
         <v>44909</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -24819,7 +24819,7 @@
         <v>45678</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -24892,7 +24892,7 @@
         <v>45140</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -24965,7 +24965,7 @@
         <v>45957</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -25038,7 +25038,7 @@
         <v>45957</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -25111,7 +25111,7 @@
         <v>45957</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -25184,7 +25184,7 @@
         <v>44794</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -25257,7 +25257,7 @@
         <v>45294</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -25335,7 +25335,7 @@
         <v>45021</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -25408,7 +25408,7 @@
         <v>45268</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -25481,7 +25481,7 @@
         <v>44903</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -25554,7 +25554,7 @@
         <v>45491</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -25627,7 +25627,7 @@
         <v>44865</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -25705,7 +25705,7 @@
         <v>45217</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -25778,7 +25778,7 @@
         <v>45217</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -25851,7 +25851,7 @@
         <v>45429</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -25924,7 +25924,7 @@
         <v>45177</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -25997,7 +25997,7 @@
         <v>46085</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -26070,7 +26070,7 @@
         <v>45299</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -26143,7 +26143,7 @@
         <v>45968</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -26216,7 +26216,7 @@
         <v>45968</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -26289,7 +26289,7 @@
         <v>45968</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -26362,7 +26362,7 @@
         <v>45230</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -26435,7 +26435,7 @@
         <v>45973</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -26508,7 +26508,7 @@
         <v>45973</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -26581,7 +26581,7 @@
         <v>45977</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -26659,7 +26659,7 @@
         <v>44986</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -26732,7 +26732,7 @@
         <v>45623</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -26805,7 +26805,7 @@
         <v>45623</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -26878,7 +26878,7 @@
         <v>45203</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -26951,7 +26951,7 @@
         <v>45604</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -27029,7 +27029,7 @@
         <v>46199</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -27102,7 +27102,7 @@
         <v>44923</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -27180,7 +27180,7 @@
         <v>45748</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -27253,7 +27253,7 @@
         <v>46154</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -27331,7 +27331,7 @@
         <v>44953</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -27404,7 +27404,7 @@
         <v>45161</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -27477,7 +27477,7 @@
         <v>45741</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -27550,7 +27550,7 @@
         <v>45265</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -27623,7 +27623,7 @@
         <v>46203</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -27696,7 +27696,7 @@
         <v>45261</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -27769,7 +27769,7 @@
         <v>45296</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -27842,7 +27842,7 @@
         <v>45219</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -27920,7 +27920,7 @@
         <v>45230</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -27993,7 +27993,7 @@
         <v>45082</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -28066,7 +28066,7 @@
         <v>46205</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -28139,7 +28139,7 @@
         <v>46206</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -28212,7 +28212,7 @@
         <v>44933</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -28285,7 +28285,7 @@
         <v>45268</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -28358,7 +28358,7 @@
         <v>46206</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -28431,7 +28431,7 @@
         <v>44986</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -28504,7 +28504,7 @@
         <v>46206</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -28577,7 +28577,7 @@
         <v>46206</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -28650,7 +28650,7 @@
         <v>46206</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -28723,7 +28723,7 @@
         <v>46206</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -28796,7 +28796,7 @@
         <v>46206</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -28869,7 +28869,7 @@
         <v>46206</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -28942,7 +28942,7 @@
         <v>45655</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -29015,7 +29015,7 @@
         <v>46206</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -29088,7 +29088,7 @@
         <v>45266</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -29166,7 +29166,7 @@
         <v>45989</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -29239,7 +29239,7 @@
         <v>44970</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -29317,7 +29317,7 @@
         <v>45300</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -29395,7 +29395,7 @@
         <v>45182</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -29468,7 +29468,7 @@
         <v>45579</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -29541,7 +29541,7 @@
         <v>45695</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -29614,7 +29614,7 @@
         <v>45320</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -29687,7 +29687,7 @@
         <v>45996</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -29765,7 +29765,7 @@
         <v>45245</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -29843,7 +29843,7 @@
         <v>45655</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -29916,7 +29916,7 @@
         <v>45545</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -29989,7 +29989,7 @@
         <v>46147</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -30067,7 +30067,7 @@
         <v>46000</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -30145,7 +30145,7 @@
         <v>45208</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -30218,7 +30218,7 @@
         <v>45671</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -30291,7 +30291,7 @@
         <v>45779</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -30364,7 +30364,7 @@
         <v>45779</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -30437,7 +30437,7 @@
         <v>46010</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -30510,7 +30510,7 @@
         <v>45246</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -30583,7 +30583,7 @@
         <v>46279</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -30656,7 +30656,7 @@
         <v>45359</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -30729,7 +30729,7 @@
         <v>45785</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -30802,7 +30802,7 @@
         <v>45271</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -30875,7 +30875,7 @@
         <v>46239</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -30948,7 +30948,7 @@
         <v>46239</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -31021,7 +31021,7 @@
         <v>45342</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -31094,7 +31094,7 @@
         <v>45546</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -31167,7 +31167,7 @@
         <v>45664</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -31240,7 +31240,7 @@
         <v>45573</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -31313,7 +31313,7 @@
         <v>46030</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -31386,7 +31386,7 @@
         <v>46030</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -31459,7 +31459,7 @@
         <v>46030</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -31532,7 +31532,7 @@
         <v>45483</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -31605,7 +31605,7 @@
         <v>46030</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -31678,7 +31678,7 @@
         <v>46030</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -31751,7 +31751,7 @@
         <v>46240</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -31829,7 +31829,7 @@
         <v>46035</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -31902,7 +31902,7 @@
         <v>46035</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -31975,7 +31975,7 @@
         <v>45274</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -32048,7 +32048,7 @@
         <v>45593</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -32121,7 +32121,7 @@
         <v>46038</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -32194,7 +32194,7 @@
         <v>45737</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -32267,7 +32267,7 @@
         <v>45793</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -32340,7 +32340,7 @@
         <v>46245</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -32413,7 +32413,7 @@
         <v>46245</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -32486,7 +32486,7 @@
         <v>46288</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -32559,7 +32559,7 @@
         <v>46288</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -32632,7 +32632,7 @@
         <v>46288</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -32705,7 +32705,7 @@
         <v>46288</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -32778,7 +32778,7 @@
         <v>45573</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -32851,7 +32851,7 @@
         <v>45804</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -32924,7 +32924,7 @@
         <v>45293</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -32997,7 +32997,7 @@
         <v>46290</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -33070,7 +33070,7 @@
         <v>46290</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -33143,7 +33143,7 @@
         <v>46055</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -33216,7 +33216,7 @@
         <v>46055</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -33289,7 +33289,7 @@
         <v>46289</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -33367,7 +33367,7 @@
         <v>46289</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -33445,7 +33445,7 @@
         <v>46248</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -33523,7 +33523,7 @@
         <v>46294</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -33601,7 +33601,7 @@
         <v>46294</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -33679,7 +33679,7 @@
         <v>45342</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -33752,7 +33752,7 @@
         <v>46248</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -33830,7 +33830,7 @@
         <v>46248</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -33908,7 +33908,7 @@
         <v>46248</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -33986,7 +33986,7 @@
         <v>46248</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -34064,7 +34064,7 @@
         <v>46294</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -34142,7 +34142,7 @@
         <v>46294</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -34215,7 +34215,7 @@
         <v>46294</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -34293,7 +34293,7 @@
         <v>45299</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -34366,7 +34366,7 @@
         <v>45300</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -34444,7 +34444,7 @@
         <v>45816</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -34517,7 +34517,7 @@
         <v>44873</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -34595,7 +34595,7 @@
         <v>46294</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -34673,7 +34673,7 @@
         <v>46248</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -34751,7 +34751,7 @@
         <v>45821</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -34824,7 +34824,7 @@
         <v>46077</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -34897,7 +34897,7 @@
         <v>46079</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -34970,7 +34970,7 @@
         <v>46087</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -35043,7 +35043,7 @@
         <v>46094</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -35116,7 +35116,7 @@
         <v>46254</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -35189,7 +35189,7 @@
         <v>45485</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -35262,7 +35262,7 @@
         <v>46098</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -35335,7 +35335,7 @@
         <v>45294</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -35408,7 +35408,7 @@
         <v>45294</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -35481,7 +35481,7 @@
         <v>46099</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -35559,7 +35559,7 @@
         <v>45655</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -35632,7 +35632,7 @@
         <v>45614</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -35705,7 +35705,7 @@
         <v>46301</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -35778,7 +35778,7 @@
         <v>46302</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -35851,7 +35851,7 @@
         <v>44894</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -35924,7 +35924,7 @@
         <v>46259</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -36002,7 +36002,7 @@
         <v>46259</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -36080,7 +36080,7 @@
         <v>45852</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -36153,7 +36153,7 @@
         <v>45860</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -36226,7 +36226,7 @@
         <v>45860</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -36299,7 +36299,7 @@
         <v>44936</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -36372,7 +36372,7 @@
         <v>46303</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -36445,7 +36445,7 @@
         <v>46120</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -36518,7 +36518,7 @@
         <v>44599</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -36591,7 +36591,7 @@
         <v>45086</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -36664,7 +36664,7 @@
         <v>46030</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -36742,7 +36742,7 @@
         <v>46303</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -36815,7 +36815,7 @@
         <v>46030</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -36893,7 +36893,7 @@
         <v>46264</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -36966,7 +36966,7 @@
         <v>45804</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -37039,7 +37039,7 @@
         <v>46265</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -37112,7 +37112,7 @@
         <v>46307</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -37190,7 +37190,7 @@
         <v>45610</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -37263,7 +37263,7 @@
         <v>46134</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -37336,7 +37336,7 @@
         <v>44945</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -37409,7 +37409,7 @@
         <v>45774</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -37482,7 +37482,7 @@
         <v>46265</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -37555,7 +37555,7 @@
         <v>44888</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -37628,7 +37628,7 @@
         <v>45967</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -37701,7 +37701,7 @@
         <v>46086</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -37774,7 +37774,7 @@
         <v>45491</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -37847,7 +37847,7 @@
         <v>46307</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -37925,7 +37925,7 @@
         <v>45712</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -37998,7 +37998,7 @@
         <v>45905</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -38071,7 +38071,7 @@
         <v>45938</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -38149,7 +38149,7 @@
         <v>46310</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -38222,7 +38222,7 @@
         <v>46008</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -38295,7 +38295,7 @@
         <v>46057</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -38368,7 +38368,7 @@
         <v>46099</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -38441,7 +38441,7 @@
         <v>46086</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -38514,7 +38514,7 @@
         <v>46086</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -38587,7 +38587,7 @@
         <v>45774</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -38660,7 +38660,7 @@
         <v>44628</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -38733,7 +38733,7 @@
         <v>46266</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -38806,7 +38806,7 @@
         <v>46266</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -38879,7 +38879,7 @@
         <v>46267</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -38957,7 +38957,7 @@
         <v>44897</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -39035,7 +39035,7 @@
         <v>46267</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -39113,7 +39113,7 @@
         <v>46267</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -39191,7 +39191,7 @@
         <v>45741</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -39264,7 +39264,7 @@
         <v>46309</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -39342,7 +39342,7 @@
         <v>46309</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -39420,7 +39420,7 @@
         <v>46267</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -39498,7 +39498,7 @@
         <v>46267</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -39576,7 +39576,7 @@
         <v>44498</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -39649,7 +39649,7 @@
         <v>44889</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -39727,7 +39727,7 @@
         <v>46269</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -39805,7 +39805,7 @@
         <v>46269</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -39883,7 +39883,7 @@
         <v>46269</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -39961,7 +39961,7 @@
         <v>45555</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -40039,7 +40039,7 @@
         <v>46269</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -40117,7 +40117,7 @@
         <v>46269</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -40195,7 +40195,7 @@
         <v>46269</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -40273,7 +40273,7 @@
         <v>46269</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -40351,7 +40351,7 @@
         <v>46272</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -40429,7 +40429,7 @@
         <v>46272</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -40507,7 +40507,7 @@
         <v>46272</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -40585,7 +40585,7 @@
         <v>46272</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -40663,7 +40663,7 @@
         <v>46272</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -40741,7 +40741,7 @@
         <v>46272</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -40819,7 +40819,7 @@
         <v>45121</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -40892,7 +40892,7 @@
         <v>46275</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -40965,7 +40965,7 @@
         <v>45392</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -41038,7 +41038,7 @@
         <v>46274</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -41116,7 +41116,7 @@
         <v>46275</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -41189,7 +41189,7 @@
         <v>45397</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -41262,7 +41262,7 @@
         <v>44944</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -41335,7 +41335,7 @@
         <v>45230</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -41408,7 +41408,7 @@
         <v>46275</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -41481,7 +41481,7 @@
         <v>45202</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -41554,7 +41554,7 @@
         <v>45229</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -41627,7 +41627,7 @@
         <v>45244</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -41705,7 +41705,7 @@
         <v>45555</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -41778,7 +41778,7 @@
         <v>44945</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -41851,7 +41851,7 @@
         <v>45623</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -41924,7 +41924,7 @@
         <v>46293</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -41997,7 +41997,7 @@
         <v>46145</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -42070,7 +42070,7 @@
         <v>46275</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -42143,7 +42143,7 @@
         <v>44939</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -42216,7 +42216,7 @@
         <v>44944</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -42289,7 +42289,7 @@
         <v>44986</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -42362,7 +42362,7 @@
         <v>46147</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -42440,7 +42440,7 @@
         <v>45142</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -42513,7 +42513,7 @@
         <v>46147</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -42591,7 +42591,7 @@
         <v>46154</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -42669,7 +42669,7 @@
         <v>45596</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -42742,7 +42742,7 @@
         <v>46154</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -42820,7 +42820,7 @@
         <v>46154</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -42898,7 +42898,7 @@
         <v>44776</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -42971,7 +42971,7 @@
         <v>46154</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -43049,7 +43049,7 @@
         <v>45105</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -43127,7 +43127,7 @@
         <v>46154</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -43205,7 +43205,7 @@
         <v>46154</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -43283,7 +43283,7 @@
         <v>46153</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -43356,7 +43356,7 @@
         <v>44942</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -43429,7 +43429,7 @@
         <v>44690</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -43502,7 +43502,7 @@
         <v>45729</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -43580,7 +43580,7 @@
         <v>45379</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -43653,7 +43653,7 @@
         <v>45774</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -43726,7 +43726,7 @@
         <v>45092</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -43799,7 +43799,7 @@
         <v>45624</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -43872,7 +43872,7 @@
         <v>44933</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -43945,7 +43945,7 @@
         <v>45089</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -44023,7 +44023,7 @@
         <v>44909</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -44096,7 +44096,7 @@
         <v>44994</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -44169,7 +44169,7 @@
         <v>44936</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -44242,7 +44242,7 @@
         <v>44967</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -44320,7 +44320,7 @@
         <v>45300</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -44398,7 +44398,7 @@
         <v>45275</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -44471,7 +44471,7 @@
         <v>45153</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -44549,7 +44549,7 @@
         <v>45096</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -44627,7 +44627,7 @@
         <v>45225</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -44705,7 +44705,7 @@
         <v>45142</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -44778,7 +44778,7 @@
         <v>45639</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -44851,7 +44851,7 @@
         <v>45086</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -44924,7 +44924,7 @@
         <v>45147</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -44997,7 +44997,7 @@
         <v>44767</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -45070,7 +45070,7 @@
         <v>45187</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -45148,7 +45148,7 @@
         <v>44509</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -45226,7 +45226,7 @@
         <v>44824</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -45299,7 +45299,7 @@
         <v>45013</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -45372,7 +45372,7 @@
         <v>45729</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -45445,7 +45445,7 @@
         <v>45568</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -45518,7 +45518,7 @@
         <v>45755</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -45591,7 +45591,7 @@
         <v>44862</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -45664,7 +45664,7 @@
         <v>45069</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -45737,7 +45737,7 @@
         <v>45111</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -45815,7 +45815,7 @@
         <v>45077</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -45888,7 +45888,7 @@
         <v>44565</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -45961,7 +45961,7 @@
         <v>45090</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -46034,7 +46034,7 @@
         <v>45133</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -46107,7 +46107,7 @@
         <v>45082</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -46180,7 +46180,7 @@
         <v>45209</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -46253,7 +46253,7 @@
         <v>44812</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -46326,7 +46326,7 @@
         <v>44862</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -46399,7 +46399,7 @@
         <v>45555</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -46477,7 +46477,7 @@
         <v>44928</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -46550,7 +46550,7 @@
         <v>45092</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -46623,7 +46623,7 @@
         <v>45275</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -46696,7 +46696,7 @@
         <v>45491</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -46769,7 +46769,7 @@
         <v>45231</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -46842,7 +46842,7 @@
         <v>44966</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -46915,7 +46915,7 @@
         <v>45568</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -46988,7 +46988,7 @@
         <v>44501</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -47061,7 +47061,7 @@
         <v>44949</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -47134,7 +47134,7 @@
         <v>45294</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -47207,7 +47207,7 @@
         <v>45341</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -47280,7 +47280,7 @@
         <v>45231</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -47353,7 +47353,7 @@
         <v>44909</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -47426,7 +47426,7 @@
         <v>45217</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -47499,7 +47499,7 @@
         <v>45195</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -47572,7 +47572,7 @@
         <v>45275</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -47645,7 +47645,7 @@
         <v>45489</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -47718,7 +47718,7 @@
         <v>45337</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -47791,7 +47791,7 @@
         <v>45404</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -47864,7 +47864,7 @@
         <v>45111</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -47942,7 +47942,7 @@
         <v>44558</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -48015,7 +48015,7 @@
         <v>45275</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -48088,7 +48088,7 @@
         <v>45453</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -48161,7 +48161,7 @@
         <v>45483</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -48234,7 +48234,7 @@
         <v>45106</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -48307,7 +48307,7 @@
         <v>45106</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -48380,7 +48380,7 @@
         <v>45106</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -48453,7 +48453,7 @@
         <v>45456</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -48526,7 +48526,7 @@
         <v>44509</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -48599,7 +48599,7 @@
         <v>45037</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -48677,7 +48677,7 @@
         <v>45120</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -48750,7 +48750,7 @@
         <v>44937</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -48823,7 +48823,7 @@
         <v>45030</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -48896,7 +48896,7 @@
         <v>45644</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -48969,7 +48969,7 @@
         <v>45117</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -49042,7 +49042,7 @@
         <v>45750</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -49115,7 +49115,7 @@
         <v>45140</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -49188,7 +49188,7 @@
         <v>45125</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -49261,7 +49261,7 @@
         <v>45678</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -49334,7 +49334,7 @@
         <v>45116</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -49407,7 +49407,7 @@
         <v>45470</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -49485,7 +49485,7 @@
         <v>45155</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -49558,7 +49558,7 @@
         <v>44993</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -49631,7 +49631,7 @@
         <v>45177</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -49704,7 +49704,7 @@
         <v>44783</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -49777,7 +49777,7 @@
         <v>45005</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -49850,7 +49850,7 @@
         <v>45274</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -49923,7 +49923,7 @@
         <v>45275</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -50001,7 +50001,7 @@
         <v>45275</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -50079,7 +50079,7 @@
         <v>44608</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -50157,7 +50157,7 @@
         <v>45152</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -50230,7 +50230,7 @@
         <v>45625</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -50303,7 +50303,7 @@
         <v>44643</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -50376,7 +50376,7 @@
         <v>44803</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -50449,7 +50449,7 @@
         <v>44859</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -50527,7 +50527,7 @@
         <v>44600</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -50600,7 +50600,7 @@
         <v>44795</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -50673,7 +50673,7 @@
         <v>45225</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -50746,7 +50746,7 @@
         <v>45230</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -50819,7 +50819,7 @@
         <v>44683</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -50892,7 +50892,7 @@
         <v>45655</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -50965,7 +50965,7 @@
         <v>44638</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -51038,7 +51038,7 @@
         <v>44623</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -51111,7 +51111,7 @@
         <v>45703</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -51184,7 +51184,7 @@
         <v>45146</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -51262,7 +51262,7 @@
         <v>45111</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -51335,7 +51335,7 @@
         <v>45774</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -51408,7 +51408,7 @@
         <v>45231</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -51481,7 +51481,7 @@
         <v>45230</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -51554,7 +51554,7 @@
         <v>45160</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -51627,7 +51627,7 @@
         <v>44743</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -51700,7 +51700,7 @@
         <v>45205</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -51773,7 +51773,7 @@
         <v>44909</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -51846,7 +51846,7 @@
         <v>45306</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -51919,7 +51919,7 @@
         <v>44768</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -51992,7 +51992,7 @@
         <v>44767</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -52065,7 +52065,7 @@
         <v>44858</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -52138,7 +52138,7 @@
         <v>45477</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -52216,7 +52216,7 @@
         <v>44775</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -52289,7 +52289,7 @@
         <v>44930</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -52367,7 +52367,7 @@
         <v>44865</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -52440,7 +52440,7 @@
         <v>44888</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -52513,7 +52513,7 @@
         <v>45275</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -52591,7 +52591,7 @@
         <v>45153</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -52669,7 +52669,7 @@
         <v>45044</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -52742,7 +52742,7 @@
         <v>44930</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -52820,7 +52820,7 @@
         <v>45309</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -52893,7 +52893,7 @@
         <v>45293</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -52966,7 +52966,7 @@
         <v>45238</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -53039,7 +53039,7 @@
         <v>45048</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -53112,7 +53112,7 @@
         <v>45225</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -53185,7 +53185,7 @@
         <v>45268</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -53258,7 +53258,7 @@
         <v>45161</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -53331,7 +53331,7 @@
         <v>44994</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -53404,7 +53404,7 @@
         <v>44987</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -53477,7 +53477,7 @@
         <v>44498</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -53550,7 +53550,7 @@
         <v>44498</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -53623,7 +53623,7 @@
         <v>44909</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -53696,7 +53696,7 @@
         <v>45492</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -53769,7 +53769,7 @@
         <v>44958</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -53842,7 +53842,7 @@
         <v>44810</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -53915,7 +53915,7 @@
         <v>44949</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -53988,7 +53988,7 @@
         <v>44911</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -54061,7 +54061,7 @@
         <v>44641</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -54139,7 +54139,7 @@
         <v>45541</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -54212,7 +54212,7 @@
         <v>44855</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -54285,7 +54285,7 @@
         <v>45133</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -54358,7 +54358,7 @@
         <v>45541</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -54431,7 +54431,7 @@
         <v>45699</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -54504,7 +54504,7 @@
         <v>46040</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -54577,7 +54577,7 @@
         <v>46108</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -54650,7 +54650,7 @@
         <v>46183</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -54723,7 +54723,7 @@
         <v>46307</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
